--- a/Abid — Fall 2026 Training Block.xlsx
+++ b/Abid — Fall 2026 Training Block.xlsx
@@ -12385,7 +12385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>First CSS test. The 400/200 ratio is 2.13, inside the normal 2.10–2.20 band, so the number is internally consistent and the speed-to-endurance balance is healthy.</t>
+          <t>First CSS test. The 400/200 ratio is 2.13, inside the normal 2.10–2.20 band, so the number is internally consistent. What the ratio cannot detect is both swims being submaximal together, and that now looks like what happened: on Oct 5 the warm-up 400 came in at 7:07.5 and the 5 × 200 that followed averaged 1:47.6/100 without fading. Treat 1:53 as a soft floor rather than a true threshold until Nov 9 re-measures it.</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Now (Sep 21)</t>
+          <t>Sep 21 baseline</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12572,29 +12572,29 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Good — 4 s/100 faster</t>
+          <t>Floor — an honest test, no fitness gained</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>6:58</t>
+          <t>7:00</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>3:20</t>
+          <t>3:18</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1:49</t>
+          <t>1:51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Strong — 6 s/100 faster</t>
+          <t>Good — the number to aim at</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12604,427 +12604,449 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>3:18</t>
+          <t>3:16</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>1:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>Run the protocol identically — 400 first, 5 min full rest, then 200 — or the comparison means nothing. A sandbagged 200 inflates CSS and makes the block look better than it was, so both efforts have to be genuine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+          <t>1:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>6:44</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>3:12</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>1:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>Two execution notes, both learned the hard way. First, warm up genuinely easy — 2:08–2:13/100, not the 1:45s of the last two sessions — because a 400 TT off a hard warm-up is just a second hard swim. Second, pace the 400 off the clock and not off feel: 1:42 for the first 100, 1:43s through the middle, empty the tank on the last 50. Then 5 min full rest before the 200. Run the protocol identically or the comparison means nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Pace zones (recalculate off your measured CSS)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Cue</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Easy / recovery</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2:08–2:13</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>CSS + 15–20 s. Conversational. Warm-up, cool-down, and the technique swim.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Aerobic (Z2)</t>
+          <t>Easy / recovery</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2:01–2:05</t>
+          <t>2:08–2:13</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>CSS + 8–12 s. What a long continuous swim should feel like. Nose-breathing calm.</t>
+          <t>CSS + 15–20 s. Conversational. Warm-up, cool-down, and the technique swim.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>CSS / threshold</t>
+          <t>Aerobic (Z2)</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>1:51–1:55</t>
+          <t>2:01–2:05</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Your tested 1:53, give or take 2 s. The engine of this block — comfortably hard, repeatable for 20–40 min of work.</t>
+          <t>CSS + 8–12 s. What a long continuous swim should feel like. Nose-breathing calm.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Fast (VO2)</t>
+          <t>CSS / threshold</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>1:45–1:48</t>
+          <t>1:51–1:55</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>CSS −5 to −8 s. 50s and short 100s, still with a clean catch and a long stroke.</t>
+          <t>Your tested 1:53, give or take 2 s. The engine of this block — comfortably hard, repeatable for 20–40 min of work.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>Fast (VO2)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>1:45–1:48</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>CSS −5 to −8 s. 50s and short 100s, still with a clean catch and a long stroke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>1:35–1:40</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>25s and the last 50 of a set. 1:40 is your 200 TT pace — anything quicker is a genuine sprint, so use it sparingly.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Send-offs</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Send-off</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Rest</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>100 aerobic</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>~27 s</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>100 threshold (CSS)</t>
+          <t>100 aerobic</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2:15</t>
+          <t>2:30</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>~22 s</t>
+          <t>~27 s</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>100 fast</t>
+          <t>100 threshold (CSS)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2:30</t>
+          <t>2:15</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>~43 s</t>
+          <t>~22 s</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>50 aerobic</t>
+          <t>100 fast</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>1:15</t>
+          <t>2:30</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>~13 s</t>
+          <t>~43 s</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>50 threshold (CSS)</t>
+          <t>50 aerobic</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>1:05</t>
+          <t>1:15</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>~8 s</t>
+          <t>~13 s</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>50 fast</t>
+          <t>50 threshold (CSS)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>1:15</t>
+          <t>1:05</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>~22 s</t>
+          <t>~8 s</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>50 fast</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>1:15</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>~22 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>200 threshold (CSS)</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>4:25</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>~39 s</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>Drill progression</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Focus</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Drills</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Weeks 1–3</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Body position + the send-off habit</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Get the new gear working and stop the sessions from being rest-dominated. Snorkel removes breathing as a variable so body and head position can actually be felt.</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Snorkel + fins, 6 × 50: flutter kick on front, eyes down, hips high. · 6-1-6 with fins, 4 × 50 per side: six kicks on the side, one stroke, six on the other. · Catch-up, 4 × 50: patient lead arm, long body line, no crossover. · Fingertip drag, 4 × 50: relaxed recovery, high elbow, unhurried rotation. · Breathe-3 on easy 50s only — warm-up and cool-down, never inside a hard set. · Left-side ladder starts here: side kick (left) until stable, then side kick + breathe.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Weeks 4–7</t>
+          <t>Weeks 1–3</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Catch + symmetry</t>
+          <t>Body position + the send-off habit</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Build an earlier, higher-elbow catch and start balancing the stroke. Paddles arrive in Week 5 and stay capped.</t>
+          <t>Get the new gear working and stop the sessions from being rest-dominated. Snorkel removes breathing as a variable so body and head position can actually be felt.</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Front scull, 3 × 50 with snorkel: forearm vertical, pressure back not down. · Single-arm freestyle, 4 × 50 per side: the weak (left-breathing) side gets the extra 50. · Left-breathing single-arm, 4 × 50 with fins: right arm as a rail, breathe left every stroke. · Closed-fist, 4 × 50, then 50 normal — the contrast teaches the forearm to grip water. · 3/5/3 breathing pattern through warm-ups: three strokes, five strokes, three. · Small paddles + pull buoy, max 400 yd: hold the catch, stop if the shoulder complains. · Breaststroke timing, 4 × 50: pull, breathe, kick, glide — one thing at a time.</t>
+          <t>Snorkel + fins, 6 × 50: flutter kick on front, eyes down, hips high. · 6-1-6 with fins, 4 × 50 per side: six kicks on the side, one stroke, six on the other. · Catch-up, 4 × 50: patient lead arm, long body line, no crossover. · Fingertip drag, 4 × 50: relaxed recovery, high elbow, unhurried rotation. · Breathe-3 on easy 50s only — warm-up and cool-down, never inside a hard set. · Left-side ladder starts here: side kick (left) until stable, then side kick + breathe.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>Weeks 4–7</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Catch + symmetry</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Build an earlier, higher-elbow catch and start balancing the stroke. Paddles arrive in Week 5 and stay capped.</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Front scull, 3 × 50 with snorkel: forearm vertical, pressure back not down. · Single-arm freestyle, 4 × 50 per side: the weak (left-breathing) side gets the extra 50. · Left-breathing single-arm, 4 × 50 with fins: right arm as a rail, breathe left every stroke. · Closed-fist, 4 × 50, then 50 normal — the contrast teaches the forearm to grip water. · 3/5/3 breathing pattern through warm-ups: three strokes, five strokes, three. · Small paddles + pull buoy, max 400 yd: hold the catch, stop if the shoulder complains. · Breaststroke timing, 4 × 50: pull, breathe, kick, glide — one thing at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>Weeks 8–15</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Hold form under fatigue</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Technique that survives a hard set is the only technique that counts. Stroke count and SWOLF become the feedback loop since there is no coach on deck.</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Stroke-count ladder, 4 × 50: hold a fixed count per length, then drop it by one. · Descending 100s at a fixed stroke count — get faster without adding strokes. · Breathe-3 on easy 50s with rest, and only inside continuous swimming once the left breath survives those. · Sighting, 6 × 50: eyes just above the water every 6–8 strokes, ahead of open water next year. · Breaststroke 200 continuous — an honest second stroke, not a novelty. · Self-check every Monday: log the 100 that felt best and its stroke count.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Before every swim</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Fins and center-mount snorkel in the bag from Week 1; small paddles bought before Week 5, which is when they enter.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Know your CSS number and carry the send-off table on your phone.</t>
+          <t>Fins and center-mount snorkel in the bag from Week 1; small paddles bought before Week 5, which is when they enter.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Every main set leaves on the clock — if you are resting until you feel ready, the set is wrong.</t>
+          <t>Know your CSS number and carry the send-off table on your phone.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Stroke count per 25 yd logged on the best 100 of each Monday session.</t>
+          <t>Every main set leaves on the clock — if you are resting until you feel ready, the set is wrong.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Left-side breathing competent — calm on easy 50s with rest by Week 7, inside continuous swimming by Week 10.</t>
+          <t>Stroke count per 25 yd logged on the best 100 of each Monday session.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Breaststroke 200 continuous, relaxed, by Week 12.</t>
+          <t>Left-side breathing competent — calm on easy 50s with rest by Week 7, inside continuous swimming by Week 10.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Breaststroke 200 continuous, relaxed, by Week 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Shoulder pain stays ≤ 2/10 — paddles are the first thing to drop if it does not.</t>
         </is>
@@ -13033,8 +13055,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Abid — Fall 2026 Training Block.xlsx
+++ b/Abid — Fall 2026 Training Block.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Log'!$A$4:$P$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Log'!$A$4:$P$219</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P221"/>
+  <dimension ref="A1:P219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2971,22 +2971,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="n"/>
+          <t>1,200 yd · 27–35 min</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>1200</v>
+      </c>
       <c r="I50" s="9" t="n"/>
       <c r="J50" s="10" t="n"/>
       <c r="K50" s="11" t="n"/>
@@ -2996,19 +2998,19 @@
       <c r="O50" s="13" t="n"/>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>About 1,200 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
@@ -3019,24 +3021,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 4 × (4 × 50)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>1,900 yd · 42–56 min</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>1900</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n"/>
       <c r="I51" s="9" t="n"/>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="11" t="n"/>
@@ -3046,7 +3046,7 @@
       <c r="O51" s="13" t="n"/>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, left-side ladder week two: left-breathing single-arm ×3 / side kick + breathe (left) ×1 / front scull ×2 / 6-1-6 ×2. Fins throughout; snorkel on for front scull only. The left-breathing single-arm takes the biggest share now — it is the rung where the left breath starts happening at something close to real stroke rate, and side kick + breathe drops to a single 50 as a check rather than a lesson. Main: 4 rounds of 4 × 50 on 1:05, descending 1 to 4 within each round, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
@@ -3069,22 +3069,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — sweet spot 3 × 10 min</t>
+          <t>Swim — speed 4 × (4 × 50)</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>55 min</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="n"/>
+          <t>1,900 yd · 42–56 min</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>1900</v>
+      </c>
       <c r="I52" s="9" t="n"/>
       <c r="J52" s="10" t="n"/>
       <c r="K52" s="11" t="n"/>
@@ -3094,19 +3096,19 @@
       <c r="O52" s="13" t="n"/>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>3 × 10 min at 164–173 W, 4 min easy between. Hold cadence above 85.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, left-side ladder week two: left-breathing single-arm ×3 / side kick + breathe (left) ×1 / front scull ×2 / 6-1-6 ×2. Fins throughout; snorkel on for front scull only. The left-breathing single-arm takes the biggest share now — it is the rung where the left breath starts happening at something close to real stroke rate, and side kick + breathe drops to a single 50 as a check rather than a lesson. Main: 4 rounds of 4 × 50 on 1:05, descending 1 to 4 within each round, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
@@ -3117,25 +3119,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 6 km</t>
+          <t>Spin bike — sweet spot 3 × 10 min</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>38–42 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="H53" s="8" t="n"/>
-      <c r="I53" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="I53" s="9" t="n"/>
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="11" t="n"/>
       <c r="L53" s="12" t="n"/>
@@ -3144,7 +3144,7 @@
       <c r="O53" s="13" t="n"/>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>Long run of the week. Flat, soft surface, conversational the whole way. Do not let a good day turn this into 8 km.</t>
+          <t>3 × 10 min at 164–173 W, 4 min easy between. Hold cadence above 85.</t>
         </is>
       </c>
     </row>
@@ -3167,23 +3167,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Easy run — 6 km</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>38–42 min</t>
         </is>
       </c>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="9" t="n"/>
+      <c r="I54" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="J54" s="10" t="n"/>
       <c r="K54" s="11" t="n"/>
       <c r="L54" s="12" t="n"/>
@@ -3192,19 +3194,19 @@
       <c r="O54" s="13" t="n"/>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>Progress the split squat. Copenhagen planks should be getting easier — extend the lever (foot on bench) when 30 s feels controlled.</t>
+          <t>Long run of the week. Flat, soft surface, conversational the whole way. Do not let a good day turn this into 8 km.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
@@ -3215,24 +3217,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,600</t>
+          <t>Strength B — Bulgarian split squat + hips and core</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>2,800 yd · 62–82 min</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="n">
-        <v>2800</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n"/>
       <c r="I55" s="9" t="n"/>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="11" t="n"/>
@@ -3242,7 +3242,7 @@
       <c r="O55" s="13" t="n"/>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,600 continuous, then 6 × 100 at CSS on 2:20. Cool-down 300. First time over 1,500 continuous in a 25 yd pool — settle in and let it be boring.</t>
+          <t>Progress the split squat. Copenhagen planks should be getting easier — extend the lever (foot on bench) when 30 s feels controlled.</t>
         </is>
       </c>
     </row>
@@ -3265,22 +3265,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Swim — long aerobic 1,600</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="n"/>
+          <t>2,800 yd · 62–82 min</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="I56" s="9" t="n"/>
       <c r="J56" s="10" t="n"/>
       <c r="K56" s="11" t="n"/>
@@ -3290,7 +3292,7 @@
       <c r="O56" s="13" t="n"/>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>Pressing day again. Compare the dumbbell bench load to Week 2 — if rep 8 is still clean, go up 5 lb a hand. The band pull-aparts at the end are not filler: they are the direct antidote to swimming's forward-shoulder posture.</t>
+          <t>Warm-up 300. Main: 1,600 continuous, then 6 × 100 at CSS on 2:20. Cool-down 300. First time over 1,500 continuous in a 25 yd pool — settle in and let it be boring.</t>
         </is>
       </c>
     </row>
@@ -3313,19 +3315,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Chest and shoulders</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H57" s="8" t="n"/>
@@ -3338,19 +3340,19 @@
       <c r="O57" s="13" t="n"/>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Pressing day again. Compare the dumbbell bench load to Week 2 — if rep 8 is still clean, go up 5 lb a hand. The band pull-aparts at the end are not filler: they are the direct antidote to swimming's forward-shoulder posture.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -3363,17 +3365,17 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>cardio</t>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Stairmaster + 15 lb pack</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H58" s="8" t="n"/>
@@ -3386,7 +3388,7 @@
       <c r="O58" s="13" t="n"/>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>Steady 45 min at 15 lb. Rainier maintenance continues biweekly through the block.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
@@ -3409,24 +3411,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Stairmaster + 15 lb pack</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>1,200 yd · 27–35 min</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="n">
-        <v>1200</v>
-      </c>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n"/>
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="11" t="n"/>
@@ -3436,7 +3436,7 @@
       <c r="O59" s="13" t="n"/>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>About 1,200 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Steady 45 min at 15 lb. Rainier maintenance continues biweekly through the block.</t>
         </is>
       </c>
     </row>
@@ -3703,22 +3703,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="n"/>
+          <t>1,200 yd · 27–35 min</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>1200</v>
+      </c>
       <c r="I65" s="9" t="n"/>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="11" t="n"/>
@@ -3728,19 +3730,19 @@
       <c r="O65" s="13" t="n"/>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>About 1,200 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
@@ -3751,24 +3753,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 24 × 50 + first paddles</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H66" s="8" t="n">
-        <v>2300</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="n"/>
       <c r="I66" s="9" t="n"/>
       <c r="J66" s="10" t="n"/>
       <c r="K66" s="11" t="n"/>
@@ -3778,7 +3778,7 @@
       <c r="O66" s="13" t="n"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: closed-fist / catch-up / 6-1-6 / breaststroke timing. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. PADDLES: 400 pull with small paddles and buoy, easy, holding the catch — stop immediately if the shoulder complains. Main: 24 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
@@ -3801,22 +3801,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — threshold 4 × 8 min</t>
+          <t>Swim — speed 24 × 50 + first paddles</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>55 min</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="n"/>
+          <t>2,300 yd · 51–68 min</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I67" s="9" t="n"/>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="11" t="n"/>
@@ -3826,19 +3828,19 @@
       <c r="O67" s="13" t="n"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>4 × 8 min at 177–186 W (95–100% FTP), 3 min easy between. 155–165 bpm. First time at threshold rather than sweet spot — the difference is only about 15 W but it is the difference between repeatable and not, so start at 177 W and only drift up if the fourth interval still looks safe.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: closed-fist / catch-up / 6-1-6 / breaststroke timing. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. PADDLES: 400 pull with small paddles and buoy, easy, holding the catch — stop immediately if the shoulder complains. Main: 24 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
@@ -3849,25 +3851,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km + strides</t>
+          <t>Spin bike — threshold 4 × 8 min</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>28–30 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="H68" s="8" t="n"/>
-      <c r="I68" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I68" s="9" t="n"/>
       <c r="J68" s="10" t="n"/>
       <c r="K68" s="11" t="n"/>
       <c r="L68" s="12" t="n"/>
@@ -3876,7 +3876,7 @@
       <c r="O68" s="13" t="n"/>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>Second short run. Finish with 6 × 20 s strides on grass.</t>
+          <t>4 × 8 min at 177–186 W (95–100% FTP), 3 min easy between. 155–165 bpm. First time at threshold rather than sweet spot — the difference is only about 15 W but it is the difference between repeatable and not, so start at 177 W and only drift up if the fourth interval still looks safe.</t>
         </is>
       </c>
     </row>
@@ -3899,23 +3899,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E69" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Easy run — 4 km + strides</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>28–30 min</t>
         </is>
       </c>
       <c r="H69" s="8" t="n"/>
-      <c r="I69" s="9" t="n"/>
+      <c r="I69" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="11" t="n"/>
       <c r="L69" s="12" t="n"/>
@@ -3924,19 +3926,19 @@
       <c r="O69" s="13" t="n"/>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Second short run. Finish with 6 × 20 s strides on grass.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
@@ -3947,24 +3949,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Strength B — Bulgarian split squat + hips and core</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>3,000 yd · 67–88 min</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>3000</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="n"/>
       <c r="I70" s="9" t="n"/>
       <c r="J70" s="10" t="n"/>
       <c r="K70" s="11" t="n"/>
@@ -3974,7 +3974,7 @@
       <c r="O70" s="13" t="n"/>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous, then 6 × 100 at CSS on 2:20. Cool-down 300. Biggest swim week so far — roughly 8,800 yd. If the shoulders are tired, drop the 6 × 100 rather than the continuous swim.</t>
+          <t>Standard Strength B.</t>
         </is>
       </c>
     </row>
@@ -3997,22 +3997,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E71" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="n"/>
+          <t>3,000 yd · 67–88 min</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>3000</v>
+      </c>
       <c r="I71" s="9" t="n"/>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="11" t="n"/>
@@ -4022,7 +4024,7 @@
       <c r="O71" s="13" t="n"/>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>Pulling day. Do this after the long swim, not before — a fatigued lat rows fine but swims badly. If the pull-ups are gone by now, switch to lat pull-downs and chase the same rep target.</t>
+          <t>Warm-up 300. Main: 1,800 continuous, then 6 × 100 at CSS on 2:20. Cool-down 300. Biggest swim week so far — roughly 8,800 yd. If the shoulders are tired, drop the 6 × 100 rather than the continuous swim.</t>
         </is>
       </c>
     </row>
@@ -4045,19 +4047,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Back and biceps</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H72" s="8" t="n"/>
@@ -4070,19 +4072,19 @@
       <c r="O72" s="13" t="n"/>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Pulling day. Do this after the long swim, not before — a fatigued lat rows fine but swims badly. If the pull-ups are gone by now, switch to lat pull-downs and chase the same rep target.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
@@ -4095,17 +4097,17 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>cardio</t>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Weekend aerobic — long ride or hike</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>2.5–3.5 hr</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H73" s="8" t="n"/>
@@ -4118,7 +4120,7 @@
       <c r="O73" s="13" t="n"/>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>Pack 15 lb if hiking.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
@@ -4141,24 +4143,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Weekend aerobic — long ride or hike</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>1,200 yd · 27–35 min</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>1200</v>
-      </c>
+          <t>2.5–3.5 hr</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n"/>
       <c r="I74" s="9" t="n"/>
       <c r="J74" s="10" t="n"/>
       <c r="K74" s="11" t="n"/>
@@ -4168,7 +4168,7 @@
       <c r="O74" s="13" t="n"/>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>About 1,200 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Pack 15 lb if hiking.</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Swim — technique + light speed</t>
+          <t>Swim — technique + threshold</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>1,800 yd · 40–53 min</t>
+          <t>2,400 yd · 53–71 min</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="I96" s="9" t="n"/>
       <c r="J96" s="10" t="n"/>
@@ -5242,7 +5242,7 @@
       <c r="O96" s="13" t="n"/>
       <c r="P96" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 500 as 10 × 50, each drill twice: catch-up / 6-1-6 / 3/5/3 breathing / left-breathing single-arm / breathe-3. Fins throughout; snorkel off for everything except catch-up. This is the ladder's graduation test — five weeks after the left side sank in the Oct 2 long swim, breathe-3 reappears, but only as a 50 with rest on either end. The question to answer honestly: do the hips stay up for a full 50? If yes, the ladder worked and Week 10 puts it back inside continuous swimming. If no, drop back to left-breathing single-arm and there is no cost to doing so. Main 12 × 50 on 1:15 aerobic, every third one fast. Then 4 × 50 breaststroke. Cool-down 200.</t>
+          <t>Warm-up 300. Drill 500 as 10 × 50, each drill twice: catch-up / 6-1-6 / 3/5/3 breathing / left-breathing single-arm / breathe-3. Fins throughout; snorkel off for everything except catch-up. This is the ladder's graduation test — five weeks after the left side sank in the Oct 2 long swim, breathe-3 reappears, but only as a 50 with rest on either end. The question to answer honestly: do the hips stay up for a full 50? If yes, the ladder worked and Week 10 puts it back inside continuous swimming. If no, drop back to left-breathing single-arm and there is no cost to doing so. Main 12 × 50 on 1:15 aerobic, every third one fast. Then 6 × 100 at CSS on 2:15 — this is the week's threshold work, moved here off the old Friday slot so the weekend stays free. Then 4 × 50 breaststroke. Cool-down 200.</t>
         </is>
       </c>
     </row>
@@ -5320,16 +5320,16 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold returns</t>
+          <t>Swim — long aerobic 1,400</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>1,800 yd · 40–53 min</t>
+          <t>2,800 yd · 62–82 min</t>
         </is>
       </c>
       <c r="H98" s="8" t="n">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="I98" s="9" t="n"/>
       <c r="J98" s="10" t="n"/>
@@ -5340,7 +5340,7 @@
       <c r="O98" s="13" t="n"/>
       <c r="P98" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: catch-up / 6-1-6 / breaststroke timing. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. Main: 8 × 100 at CSS on 2:15. Cool-down 300. Third swim in three days — if the shoulders are heavy, cut to 6 × 100.</t>
+          <t>Warm-up 400. Main: 1,400 continuous, then 6 × 100 at CSS on 2:20. Cool-down 400. Third swim in three days and the biggest of the week — it sits on Friday now rather than Saturday, so the weekend is yours. If the shoulders are heavy, drop the 6 × 100 rather than the continuous swim.</t>
         </is>
       </c>
     </row>
@@ -5413,24 +5413,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,400</t>
+          <t>Endurance ride</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H100" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>75 min</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="n"/>
       <c r="I100" s="9" t="n"/>
       <c r="J100" s="10" t="n"/>
       <c r="K100" s="11" t="n"/>
@@ -5440,19 +5438,19 @@
       <c r="O100" s="13" t="n"/>
       <c r="P100" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,400 continuous, then 4 × 100 at CSS on 2:20. Cool-down 300. Fourth swim in four days brings the week to about 7,800 yd — streak protected on the back half.</t>
+          <t>Z2, indoors or out depending on weather. Winter is arriving; start getting comfortable on the spin bike.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
@@ -5463,23 +5461,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Endurance ride</t>
+          <t>Long run — 5 km</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>75 min</t>
+          <t>34–38 min</t>
         </is>
       </c>
       <c r="H101" s="8" t="n"/>
-      <c r="I101" s="9" t="n"/>
+      <c r="I101" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="11" t="n"/>
       <c r="L101" s="12" t="n"/>
@@ -5488,7 +5488,7 @@
       <c r="O101" s="13" t="n"/>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>Z2, indoors or out depending on weather. Winter is arriving; start getting comfortable on the spin bike.</t>
+          <t>Easy long run to close a down week. Soft surface. Next week the long run steps up to race distance.</t>
         </is>
       </c>
     </row>
@@ -5511,25 +5511,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Long run — 5 km</t>
+          <t>Chest and shoulders</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>34–38 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H102" s="8" t="n"/>
-      <c r="I102" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I102" s="9" t="n"/>
       <c r="J102" s="10" t="n"/>
       <c r="K102" s="11" t="n"/>
       <c r="L102" s="12" t="n"/>
@@ -5538,7 +5536,7 @@
       <c r="O102" s="13" t="n"/>
       <c r="P102" s="7" t="inlineStr">
         <is>
-          <t>Easy long run to close a down week. Soft surface. Next week the long run steps up to race distance.</t>
+          <t>Upper day, and the first one since New York. After two weeks of bands your pressing strength will feel low — start conservative and rebuild. Nothing here touches the legs, so it sits safely on the same day as the long run.</t>
         </is>
       </c>
     </row>
@@ -5561,19 +5559,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H103" s="8" t="n"/>
@@ -5586,45 +5584,47 @@
       <c r="O103" s="13" t="n"/>
       <c r="P103" s="7" t="inlineStr">
         <is>
-          <t>Upper day, and the first one since New York. After two weeks of bands your pressing strength will feel low — start conservative and rebuild. Nothing here touches the legs, so it sits safely on the same day as the long run.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>build1</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>build2</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — CSS RETEST (400 + 200 TT)</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H104" s="8" t="n"/>
+          <t>1,600 yd · 36–47 min</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>1600</v>
+      </c>
       <c r="I104" s="9" t="n"/>
       <c r="J104" s="10" t="n"/>
       <c r="K104" s="11" t="n"/>
@@ -5634,7 +5634,7 @@
       <c r="O104" s="13" t="n"/>
       <c r="P104" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics.</t>
+          <t>Same protocol as Week 1. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. Recalculate CSS and reset every send-off in the second half of the block. Seven weeks of threshold work should show up here — 4–6 s/100 faster is a good outcome, which from the Week 1 baseline of 1:53 means landing between 1:49 and 1:47. CSS is hypersensitive to the 400: hold the 200 at 3:20, take eight seconds off the 400, and you are already at 1:49. Run it identically to Week 1 or the comparison means nothing, and give both efforts everything — an easy 200 flatters the number.</t>
         </is>
       </c>
     </row>
@@ -5657,24 +5657,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Swim — CSS RETEST (400 + 200 TT)</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>1,600 yd · 36–47 min</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="n">
-        <v>1600</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n"/>
       <c r="I105" s="9" t="n"/>
       <c r="J105" s="10" t="n"/>
       <c r="K105" s="11" t="n"/>
@@ -5684,19 +5682,19 @@
       <c r="O105" s="13" t="n"/>
       <c r="P105" s="7" t="inlineStr">
         <is>
-          <t>Same protocol as Week 1. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. Recalculate CSS and reset every send-off in the second half of the block. Seven weeks of threshold work should show up here — 4–6 s/100 faster is a good outcome, which from the Week 1 baseline of 1:53 means landing between 1:49 and 1:47. CSS is hypersensitive to the 400: hold the 200 at 3:20, take eight seconds off the 400, and you are already at 1:49. Run it identically to Week 1 or the comparison means nothing, and give both efforts everything — an easy 200 flatters the number.</t>
+          <t>Standard Strength A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
@@ -5707,23 +5705,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E106" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Easy run — 3 km</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>22–25 min</t>
         </is>
       </c>
       <c r="H106" s="8" t="n"/>
-      <c r="I106" s="9" t="n"/>
+      <c r="I106" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="J106" s="10" t="n"/>
       <c r="K106" s="11" t="n"/>
       <c r="L106" s="12" t="n"/>
@@ -5732,7 +5732,7 @@
       <c r="O106" s="13" t="n"/>
       <c r="P106" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>Easy. The long run is Sunday and it is the big one this week.</t>
         </is>
       </c>
     </row>
@@ -5755,25 +5755,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E107" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 3 km</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>22–25 min</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I107" s="9" t="n"/>
       <c r="J107" s="10" t="n"/>
       <c r="K107" s="11" t="n"/>
       <c r="L107" s="12" t="n"/>
@@ -5782,7 +5782,7 @@
       <c r="O107" s="13" t="n"/>
       <c r="P107" s="7" t="inlineStr">
         <is>
-          <t>Easy. The long run is Sunday and it is the big one this week.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
@@ -5805,19 +5805,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H108" s="8" t="n"/>
@@ -5830,19 +5830,19 @@
       <c r="O108" s="13" t="n"/>
       <c r="P108" s="7" t="inlineStr">
         <is>
-          <t>Second ride of the week, easy Z2 at 130–145 bpm. Stacked after a 3 km run so the hard days stay hard and the easy days stay genuinely easy — this is aerobic volume, not a workout.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
@@ -5853,22 +5853,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — speed 6 × (4 × 50)</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="n"/>
+          <t>2,300 yd · 51–68 min</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I109" s="9" t="n"/>
       <c r="J109" s="10" t="n"/>
       <c r="K109" s="11" t="n"/>
@@ -5878,7 +5880,7 @@
       <c r="O109" s="13" t="n"/>
       <c r="P109" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Paddles 400 pull. Main: 6 rounds of 4 × 50 on 1:00, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200. Tighter send-off than Week 5 — this is where density shows up.</t>
         </is>
       </c>
     </row>
@@ -5901,24 +5903,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 6 × (4 × 50)</t>
+          <t>Spin bike — 20 min FTP RETEST</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H110" s="8" t="n">
-        <v>2300</v>
-      </c>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="n"/>
       <c r="I110" s="9" t="n"/>
       <c r="J110" s="10" t="n"/>
       <c r="K110" s="11" t="n"/>
@@ -5928,19 +5928,19 @@
       <c r="O110" s="13" t="n"/>
       <c r="P110" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Paddles 400 pull. Main: 6 rounds of 4 × 50 on 1:00, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200. Tighter send-off than Week 5 — this is where density shows up.</t>
+          <t>Same protocol as Week 2: 15 min warm-up with 3 × 1 min builds, 20 min all-out, 10 min easy. Same Keiser, because the number only compares to itself. Six weeks of sweet spot from a base this low usually returns 5–10%, so 195 W is a good outcome and 205 W a strong one. The one thing to do differently: pace it evenly. Last time you opened at 205 and finished at 180, which is why 186 W was probably a slight underestimate — open at your target instead of at what feels good in minute two, and let the last five minutes be the ones that hurt. Re-cut every bike watt target in the second half of the block off whatever this gives.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
@@ -5951,23 +5951,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E111" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — 20 min FTP RETEST</t>
+          <t>Quality run — 6 × 1 min (≈5 km)</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>32–35 min</t>
         </is>
       </c>
       <c r="H111" s="8" t="n"/>
-      <c r="I111" s="9" t="n"/>
+      <c r="I111" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J111" s="10" t="n"/>
       <c r="K111" s="11" t="n"/>
       <c r="L111" s="12" t="n"/>
@@ -5976,7 +5978,7 @@
       <c r="O111" s="13" t="n"/>
       <c r="P111" s="7" t="inlineStr">
         <is>
-          <t>Same protocol as Week 2: 15 min warm-up with 3 × 1 min builds, 20 min all-out, 10 min easy. Same Keiser, because the number only compares to itself. Six weeks of sweet spot from a base this low usually returns 5–10%, so 195 W is a good outcome and 205 W a strong one. The one thing to do differently: pace it evenly. Last time you opened at 205 and finished at 180, which is why 186 W was probably a slight underestimate — open at your target instead of at what feels good in minute two, and let the last five minutes be the ones that hurt. Re-cut every bike watt target in the second half of the block off whatever this gives.</t>
+          <t>Warm-up 10 min easy. Then 6 × 1 min at 5k effort with 2 min easy jog between. Cool-down 10 min. Short reps on a track or soft trail — first real intensity of the block, and it stays short on purpose.</t>
         </is>
       </c>
     </row>
@@ -5999,25 +6001,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Quality run — 6 × 1 min (≈5 km)</t>
+          <t>Strength B — Bulgarian split squat + hips and core</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>32–35 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H112" s="8" t="n"/>
-      <c r="I112" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I112" s="9" t="n"/>
       <c r="J112" s="10" t="n"/>
       <c r="K112" s="11" t="n"/>
       <c r="L112" s="12" t="n"/>
@@ -6026,19 +6026,19 @@
       <c r="O112" s="13" t="n"/>
       <c r="P112" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 10 min easy. Then 6 × 1 min at 5k effort with 2 min easy jog between. Cool-down 10 min. Short reps on a track or soft trail — first real intensity of the block, and it stays short on purpose.</t>
+          <t>Standard Strength B.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
@@ -6049,22 +6049,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E113" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="n"/>
+          <t>3,000 yd · 67–88 min</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>3000</v>
+      </c>
       <c r="I113" s="9" t="n"/>
       <c r="J113" s="10" t="n"/>
       <c r="K113" s="11" t="n"/>
@@ -6074,7 +6076,7 @@
       <c r="O113" s="13" t="n"/>
       <c r="P113" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Warm-up 300. Main: 1,800 continuous at the NEW aerobic pace from Monday's retest, then 6 × 100 at the new CSS on the new send-off. Cool-down 300.</t>
         </is>
       </c>
     </row>
@@ -6097,24 +6099,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Back and biceps</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>3,000 yd · 67–88 min</t>
-        </is>
-      </c>
-      <c r="H114" s="8" t="n">
-        <v>3000</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="n"/>
       <c r="I114" s="9" t="n"/>
       <c r="J114" s="10" t="n"/>
       <c r="K114" s="11" t="n"/>
@@ -6124,7 +6124,7 @@
       <c r="O114" s="13" t="n"/>
       <c r="P114" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous at the NEW aerobic pace from Monday's retest, then 6 × 100 at the new CSS on the new send-off. Cool-down 300.</t>
+          <t>Pulling day. Rows and pull-downs after a long aerobic swim — the lats are warm, so quality is usually good here. Keep the seated row strict; no torso swing.</t>
         </is>
       </c>
     </row>
@@ -6147,19 +6147,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E115" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H115" s="8" t="n"/>
@@ -6172,19 +6172,19 @@
       <c r="O115" s="13" t="n"/>
       <c r="P115" s="7" t="inlineStr">
         <is>
-          <t>Pulling day. Rows and pull-downs after a long aerobic swim — the lats are warm, so quality is usually good here. Keep the seated row strict; no torso swing.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
@@ -6197,17 +6197,17 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>mobility</t>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Stairmaster + 20 lb pack</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45–50 min</t>
         </is>
       </c>
       <c r="H116" s="8" t="n"/>
@@ -6220,7 +6220,7 @@
       <c r="O116" s="13" t="n"/>
       <c r="P116" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Biweekly Rainier maintenance, now at 20 lb.</t>
         </is>
       </c>
     </row>
@@ -6243,19 +6243,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Stairmaster + 20 lb pack</t>
+          <t>Spin bike — Z2</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>45–50 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H117" s="8" t="n"/>
@@ -6268,19 +6268,19 @@
       <c r="O117" s="13" t="n"/>
       <c r="P117" s="7" t="inlineStr">
         <is>
-          <t>Biweekly Rainier maintenance, now at 20 lb.</t>
+          <t>Second ride of the week, easy Z2 at 130–145 bpm. Off Tuesday now — it was sitting the day before the FTP retest, which is the one place an easy ride is not free. Pure aerobic volume, not a workout, so swap it for an outdoor ride with your partner if the weather allows.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
@@ -6291,25 +6291,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I118" s="9" t="n"/>
+          <t>50–55 min</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J118" s="10" t="n"/>
       <c r="K118" s="11" t="n"/>
       <c r="L118" s="12" t="n"/>
@@ -6318,7 +6318,7 @@
       <c r="O118" s="13" t="n"/>
       <c r="P118" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Race distance for the first time. Easy pace throughout, soft surface, cadence 175–180. If the shins are tight the next morning and still tight 48 hours later, next week's long run gets cut.</t>
         </is>
       </c>
     </row>
@@ -6341,25 +6341,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E119" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>50–55 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H119" s="8" t="n"/>
-      <c r="I119" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I119" s="9" t="n"/>
       <c r="J119" s="10" t="n"/>
       <c r="K119" s="11" t="n"/>
       <c r="L119" s="12" t="n"/>
@@ -6368,45 +6366,47 @@
       <c r="O119" s="13" t="n"/>
       <c r="P119" s="7" t="inlineStr">
         <is>
-          <t>Race distance for the first time. Easy pace throughout, soft surface, cadence 175–180. If the shins are tight the next morning and still tight 48 hours later, next week's long run gets cut.</t>
+          <t>Thorough post-long-run mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — threshold 6 × 200</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="n"/>
+          <t>2,300 yd · 51–68 min</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I120" s="9" t="n"/>
       <c r="J120" s="10" t="n"/>
       <c r="K120" s="11" t="n"/>
@@ -6416,7 +6416,7 @@
       <c r="O120" s="13" t="n"/>
       <c r="P120" s="7" t="inlineStr">
         <is>
-          <t>Thorough post-long-run mobility plus foot intrinsics.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 6 × 200 at the new CSS on 4:25 (adjust to the retest). Cool-down 300. 1,200 yd of threshold — the biggest threshold block of the block.</t>
         </is>
       </c>
     </row>
@@ -6439,24 +6439,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 6 × 200</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="n">
-        <v>2300</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="n"/>
       <c r="I121" s="9" t="n"/>
       <c r="J121" s="10" t="n"/>
       <c r="K121" s="11" t="n"/>
@@ -6466,19 +6464,19 @@
       <c r="O121" s="13" t="n"/>
       <c r="P121" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 6 × 200 at the new CSS on 4:25 (adjust to the retest). Cool-down 300. 1,200 yd of threshold — the biggest threshold block of the block.</t>
+          <t>Standard Strength A. This is a big week; if you are flat, cut a set rather than skipping.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
@@ -6489,23 +6487,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Easy run — 3 km</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>22–25 min</t>
         </is>
       </c>
       <c r="H122" s="8" t="n"/>
-      <c r="I122" s="9" t="n"/>
+      <c r="I122" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="J122" s="10" t="n"/>
       <c r="K122" s="11" t="n"/>
       <c r="L122" s="12" t="n"/>
@@ -6514,7 +6514,7 @@
       <c r="O122" s="13" t="n"/>
       <c r="P122" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A. This is a big week; if you are flat, cut a set rather than skipping.</t>
+          <t>Easy. Save it for Sunday.</t>
         </is>
       </c>
     </row>
@@ -6537,25 +6537,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E123" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 3 km</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>22–25 min</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I123" s="9" t="n"/>
       <c r="J123" s="10" t="n"/>
       <c r="K123" s="11" t="n"/>
       <c r="L123" s="12" t="n"/>
@@ -6564,7 +6564,7 @@
       <c r="O123" s="13" t="n"/>
       <c r="P123" s="7" t="inlineStr">
         <is>
-          <t>Easy. Save it for Sunday.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
@@ -7025,25 +7025,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E133" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Long run — 10 km</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I133" s="9" t="n"/>
+          <t>62–68 min</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="J133" s="10" t="n"/>
       <c r="K133" s="11" t="n"/>
       <c r="L133" s="12" t="n"/>
@@ -7052,7 +7052,7 @@
       <c r="O133" s="13" t="n"/>
       <c r="P133" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Peak long run, comfortably over race distance. Easy pace, soft surface. This is the run that makes Dec 5 feel short — and the last long one before the race.</t>
         </is>
       </c>
     </row>
@@ -7075,25 +7075,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E134" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Long run — 10 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>62–68 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H134" s="8" t="n"/>
-      <c r="I134" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="I134" s="9" t="n"/>
       <c r="J134" s="10" t="n"/>
       <c r="K134" s="11" t="n"/>
       <c r="L134" s="12" t="n"/>
@@ -7102,45 +7100,47 @@
       <c r="O134" s="13" t="n"/>
       <c r="P134" s="7" t="inlineStr">
         <is>
-          <t>Peak long run, comfortably over race distance. Easy pace, soft surface. This is the run that makes Dec 5 feel short — and the last long one before the race.</t>
+          <t>Full mobility. Pack for Edmonton.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — threshold 3 × 400</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="n"/>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="n">
+        <v>2400</v>
+      </c>
       <c r="I135" s="9" t="n"/>
       <c r="J135" s="10" t="n"/>
       <c r="K135" s="11" t="n"/>
@@ -7150,7 +7150,7 @@
       <c r="O135" s="13" t="n"/>
       <c r="P135" s="7" t="inlineStr">
         <is>
-          <t>Full mobility. Pack for Edmonton.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 3 × 400 at CSS on 8:45. Cool-down 400. Longest threshold reps of the block — essentially a rehearsal for the 70.3 swim distance, broken.</t>
         </is>
       </c>
     </row>
@@ -7173,24 +7173,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 3 × 400</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H136" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="n"/>
       <c r="I136" s="9" t="n"/>
       <c r="J136" s="10" t="n"/>
       <c r="K136" s="11" t="n"/>
@@ -7200,19 +7198,19 @@
       <c r="O136" s="13" t="n"/>
       <c r="P136" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 3 × 400 at CSS on 8:45. Cool-down 400. Longest threshold reps of the block — essentially a rehearsal for the 70.3 swim distance, broken.</t>
+          <t>Standard Strength A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
@@ -7223,23 +7221,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E137" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E137" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>28–30 min</t>
         </is>
       </c>
       <c r="H137" s="8" t="n"/>
-      <c r="I137" s="9" t="n"/>
+      <c r="I137" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J137" s="10" t="n"/>
       <c r="K137" s="11" t="n"/>
       <c r="L137" s="12" t="n"/>
@@ -7248,7 +7248,7 @@
       <c r="O137" s="13" t="n"/>
       <c r="P137" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>Last Seattle run before the flight. Soft surface.</t>
         </is>
       </c>
     </row>
@@ -7271,25 +7271,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E138" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>28–30 min</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I138" s="9" t="n"/>
       <c r="J138" s="10" t="n"/>
       <c r="K138" s="11" t="n"/>
       <c r="L138" s="12" t="n"/>
@@ -7298,7 +7298,7 @@
       <c r="O138" s="13" t="n"/>
       <c r="P138" s="7" t="inlineStr">
         <is>
-          <t>Last Seattle run before the flight. Soft surface.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
@@ -7321,19 +7321,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E139" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H139" s="8" t="n"/>
@@ -7346,19 +7346,19 @@
       <c r="O139" s="13" t="n"/>
       <c r="P139" s="7" t="inlineStr">
         <is>
-          <t>Upper day, and the last lift before the flight. Pressing pairs cleanly with an easy run and leaves Thursday's Strength B with fresh legs.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
@@ -7369,22 +7369,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — speed (Edmonton)</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H140" s="8" t="n"/>
+          <t>2,100 yd · 47–62 min</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="n">
+        <v>2100</v>
+      </c>
       <c r="I140" s="9" t="n"/>
       <c r="J140" s="10" t="n"/>
       <c r="K140" s="11" t="n"/>
@@ -7394,7 +7396,7 @@
       <c r="O140" s="13" t="n"/>
       <c r="P140" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Travel day. Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 200. Fit it around the flight — same gym, so no adaptation needed.</t>
         </is>
       </c>
     </row>
@@ -7417,24 +7419,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed (Edmonton)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2,100 yd · 47–62 min</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="n">
-        <v>2100</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="n"/>
       <c r="I141" s="9" t="n"/>
       <c r="J141" s="10" t="n"/>
       <c r="K141" s="11" t="n"/>
@@ -7444,7 +7444,7 @@
       <c r="O141" s="13" t="n"/>
       <c r="P141" s="7" t="inlineStr">
         <is>
-          <t>Travel day. Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 200. Fit it around the flight — same gym, so no adaptation needed.</t>
+          <t>Travel mobility.</t>
         </is>
       </c>
     </row>
@@ -7467,19 +7467,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — Z2</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H142" s="8" t="n"/>
@@ -7492,19 +7492,19 @@
       <c r="O142" s="13" t="n"/>
       <c r="P142" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility.</t>
+          <t>Second ride of the week, easy. Edmonton is icy in late November, so all riding this week is indoors. Forty minutes at 130–145 bpm is enough to hold the aerobic base.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
@@ -7515,23 +7515,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E143" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E143" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>28–30 min</t>
         </is>
       </c>
       <c r="H143" s="8" t="n"/>
-      <c r="I143" s="9" t="n"/>
+      <c r="I143" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J143" s="10" t="n"/>
       <c r="K143" s="11" t="n"/>
       <c r="L143" s="12" t="n"/>
@@ -7540,7 +7542,7 @@
       <c r="O143" s="13" t="n"/>
       <c r="P143" s="7" t="inlineStr">
         <is>
-          <t>Second ride of the week, easy. Edmonton is icy in late November, so all riding this week is indoors. Forty minutes at 130–145 bpm is enough to hold the aerobic base.</t>
+          <t>Indoor track or treadmill. Edmonton in late November is icy and dark — this is the week to accept the treadmill rather than risk a fall.</t>
         </is>
       </c>
     </row>
@@ -7563,25 +7565,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E144" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Strength B — Bulgarian split squat + hips and core</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>28–30 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H144" s="8" t="n"/>
-      <c r="I144" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I144" s="9" t="n"/>
       <c r="J144" s="10" t="n"/>
       <c r="K144" s="11" t="n"/>
       <c r="L144" s="12" t="n"/>
@@ -7590,19 +7590,19 @@
       <c r="O144" s="13" t="n"/>
       <c r="P144" s="7" t="inlineStr">
         <is>
-          <t>Indoor track or treadmill. Edmonton in late November is icy and dark — this is the week to accept the treadmill rather than risk a fall.</t>
+          <t>Standard Strength B.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
@@ -7613,22 +7613,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E145" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="n"/>
+          <t>3,000 yd · 67–88 min</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="n">
+        <v>3000</v>
+      </c>
       <c r="I145" s="9" t="n"/>
       <c r="J145" s="10" t="n"/>
       <c r="K145" s="11" t="n"/>
@@ -7638,7 +7640,7 @@
       <c r="O145" s="13" t="n"/>
       <c r="P145" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Warm-up 300. Main: 1,800 continuous, then 6 × 100 at CSS. Cool-down 300. Left breathing returns to continuous swimming here, eight weeks after Oct 2 and only if the Week 7 graduation test went well — one 25 breathing left at the start of every 300, and nothing more. Twenty-five yards is short enough that you can bail onto your right side before anything sinks, which is the whole reason the dose is that small. If the hips drop even once, stop doing it for the rest of the swim and keep it in drills a while longer; the 1,800 is the session and the breathing is a passenger.</t>
         </is>
       </c>
     </row>
@@ -7661,24 +7663,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Spin bike — Z2</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>3,000 yd · 67–88 min</t>
-        </is>
-      </c>
-      <c r="H146" s="8" t="n">
-        <v>3000</v>
-      </c>
+          <t>50 min</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="n"/>
       <c r="I146" s="9" t="n"/>
       <c r="J146" s="10" t="n"/>
       <c r="K146" s="11" t="n"/>
@@ -7688,19 +7688,19 @@
       <c r="O146" s="13" t="n"/>
       <c r="P146" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous, then 6 × 100 at CSS. Cool-down 300. Left breathing returns to continuous swimming here, eight weeks after Oct 2 and only if the Week 7 graduation test went well — one 25 breathing left at the start of every 300, and nothing more. Twenty-five yards is short enough that you can bail onto your right side before anything sinks, which is the whole reason the dose is that small. If the hips drop even once, stop doing it for the rest of the swim and keep it in drills a while longer; the 1,800 is the session and the breathing is a passenger.</t>
+          <t>Easy aerobic hour on the spin bike.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
@@ -7711,19 +7711,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E147" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Stairmaster + 20 lb pack</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H147" s="8" t="n"/>
@@ -7736,7 +7736,7 @@
       <c r="O147" s="13" t="n"/>
       <c r="P147" s="7" t="inlineStr">
         <is>
-          <t>Easy aerobic hour on the spin bike.</t>
+          <t>Biweekly Rainier maintenance.</t>
         </is>
       </c>
     </row>
@@ -7759,24 +7759,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Chest and shoulders</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H148" s="8" t="n">
-        <v>1400</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="n"/>
       <c r="I148" s="9" t="n"/>
       <c r="J148" s="10" t="n"/>
       <c r="K148" s="11" t="n"/>
@@ -7786,19 +7784,19 @@
       <c r="O148" s="13" t="n"/>
       <c r="P148" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Upper day, in the Edmonton gym. Every weekday this week is already at the two-session cap, so the pressing day lands here — it is the one strength session that does nothing to the legs, which is what makes it safe the day before a 7 km long run.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
@@ -7809,23 +7807,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Stairmaster + 20 lb pack</t>
+          <t>Long run — 7 km</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>45–50 min</t>
         </is>
       </c>
       <c r="H149" s="8" t="n"/>
-      <c r="I149" s="9" t="n"/>
+      <c r="I149" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="J149" s="10" t="n"/>
       <c r="K149" s="11" t="n"/>
       <c r="L149" s="12" t="n"/>
@@ -7834,7 +7834,7 @@
       <c r="O149" s="13" t="n"/>
       <c r="P149" s="7" t="inlineStr">
         <is>
-          <t>Biweekly Rainier maintenance.</t>
+          <t>Down-week long run, shorter than last week on purpose. Indoor track if the footing is bad.</t>
         </is>
       </c>
     </row>
@@ -7857,25 +7857,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E150" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Long run — 7 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>45–50 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H150" s="8" t="n"/>
-      <c r="I150" s="9" t="n">
-        <v>7</v>
-      </c>
+      <c r="I150" s="9" t="n"/>
       <c r="J150" s="10" t="n"/>
       <c r="K150" s="11" t="n"/>
       <c r="L150" s="12" t="n"/>
@@ -7884,45 +7882,47 @@
       <c r="O150" s="13" t="n"/>
       <c r="P150" s="7" t="inlineStr">
         <is>
-          <t>Down-week long run, shorter than last week on purpose. Indoor track if the footing is bad.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — threshold 10 × 100 (Edmonton)</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="n"/>
+          <t>2,000 yd · 44–59 min</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="n">
+        <v>2000</v>
+      </c>
       <c r="I151" s="9" t="n"/>
       <c r="J151" s="10" t="n"/>
       <c r="K151" s="11" t="n"/>
@@ -7932,7 +7932,7 @@
       <c r="O151" s="13" t="n"/>
       <c r="P151" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics.</t>
+          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 10 × 100 at CSS on 2:10 — the tightest send-off yet. Cool-down 300.</t>
         </is>
       </c>
     </row>
@@ -7955,24 +7955,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 10 × 100 (Edmonton)</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H152" s="8" t="n">
-        <v>2000</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="n"/>
       <c r="I152" s="9" t="n"/>
       <c r="J152" s="10" t="n"/>
       <c r="K152" s="11" t="n"/>
@@ -7982,19 +7980,19 @@
       <c r="O152" s="13" t="n"/>
       <c r="P152" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 10 × 100 at CSS on 2:10 — the tightest send-off yet. Cool-down 300.</t>
+          <t>Last full Strength A before the race. Normal loads — a 5 mile race does not need a strength taper.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
@@ -8005,23 +8003,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E153" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E153" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H153" s="8" t="n"/>
-      <c r="I153" s="9" t="n"/>
+      <c r="I153" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J153" s="10" t="n"/>
       <c r="K153" s="11" t="n"/>
       <c r="L153" s="12" t="n"/>
@@ -8030,7 +8030,7 @@
       <c r="O153" s="13" t="n"/>
       <c r="P153" s="7" t="inlineStr">
         <is>
-          <t>Last full Strength A before the race. Normal loads — a 5 mile race does not need a strength taper.</t>
+          <t>Travel day back to Seattle. Easy shakeout, whenever it fits.</t>
         </is>
       </c>
     </row>
@@ -8053,25 +8053,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E154" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H154" s="8" t="n"/>
-      <c r="I154" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I154" s="9" t="n"/>
       <c r="J154" s="10" t="n"/>
       <c r="K154" s="11" t="n"/>
       <c r="L154" s="12" t="n"/>
@@ -8080,19 +8078,19 @@
       <c r="O154" s="13" t="n"/>
       <c r="P154" s="7" t="inlineStr">
         <is>
-          <t>Travel day back to Seattle. Easy shakeout, whenever it fits.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
@@ -8103,22 +8101,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — speed</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H155" s="8" t="n"/>
+          <t>2,000 yd · 44–59 min</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="n">
+        <v>2000</v>
+      </c>
       <c r="I155" s="9" t="n"/>
       <c r="J155" s="10" t="n"/>
       <c r="K155" s="11" t="n"/>
@@ -8128,7 +8128,7 @@
       <c r="O155" s="13" t="n"/>
       <c r="P155" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull / 6-1-6. Fins throughout; snorkel off for breaststroke timing and 6-1-6. Main: 16 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
         </is>
       </c>
     </row>
@@ -8151,24 +8151,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed</t>
+          <t>Spin bike — easy Z2</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H156" s="8" t="n">
-        <v>2000</v>
-      </c>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="n"/>
       <c r="I156" s="9" t="n"/>
       <c r="J156" s="10" t="n"/>
       <c r="K156" s="11" t="n"/>
@@ -8178,19 +8176,19 @@
       <c r="O156" s="13" t="n"/>
       <c r="P156" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull / 6-1-6. Fins throughout; snorkel off for breaststroke timing and 6-1-6. Main: 16 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
+          <t>Keep it aerobic this week; no threshold work with a race on Saturday.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
@@ -8201,23 +8199,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E157" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — easy Z2</t>
+          <t>Race primer — 4 × 90 s (≈4 km)</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="H157" s="8" t="n"/>
-      <c r="I157" s="9" t="n"/>
+      <c r="I157" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J157" s="10" t="n"/>
       <c r="K157" s="11" t="n"/>
       <c r="L157" s="12" t="n"/>
@@ -8226,7 +8226,7 @@
       <c r="O157" s="13" t="n"/>
       <c r="P157" s="7" t="inlineStr">
         <is>
-          <t>Keep it aerobic this week; no threshold work with a race on Saturday.</t>
+          <t>Warm-up 10 min. Then 4 × 90 s at 5-mile race pace with 90 s easy between. Cool-down 8 min. Short, sharp, and well short of fatiguing — this wakes the legs up rather than tiring them.</t>
         </is>
       </c>
     </row>
@@ -8249,25 +8249,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E158" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Race primer — 4 × 90 s (≈4 km)</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>28 min</t>
-        </is>
-      </c>
-      <c r="H158" s="8" t="n"/>
-      <c r="I158" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>1,600 yd · 36–47 min</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I158" s="9" t="n"/>
       <c r="J158" s="10" t="n"/>
       <c r="K158" s="11" t="n"/>
       <c r="L158" s="12" t="n"/>
@@ -8276,19 +8276,19 @@
       <c r="O158" s="13" t="n"/>
       <c r="P158" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 10 min. Then 4 × 90 s at 5-mile race pace with 90 s easy between. Cool-down 8 min. Short, sharp, and well short of fatiguing — this wakes the legs up rather than tiring them.</t>
+          <t>About 1,600 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
@@ -8306,16 +8306,16 @@
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Swim — easy aerobic</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>1,600 yd · 36–47 min</t>
+          <t>1,700 yd · 38–50 min</t>
         </is>
       </c>
       <c r="H159" s="8" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="I159" s="9" t="n"/>
       <c r="J159" s="10" t="n"/>
@@ -8326,7 +8326,7 @@
       <c r="O159" s="13" t="n"/>
       <c r="P159" s="7" t="inlineStr">
         <is>
-          <t>About 1,600 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Warm-up 300. Main 1,000 easy continuous. 4 × 50 breaststroke. Cool-down 200. Genuinely easy — you race tomorrow.</t>
         </is>
       </c>
     </row>
@@ -8349,24 +8349,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E160" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Swim — easy aerobic</t>
+          <t>Chest and shoulders</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>1,700 yd · 38–50 min</t>
-        </is>
-      </c>
-      <c r="H160" s="8" t="n">
-        <v>1700</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H160" s="8" t="n"/>
       <c r="I160" s="9" t="n"/>
       <c r="J160" s="10" t="n"/>
       <c r="K160" s="11" t="n"/>
@@ -8376,7 +8374,7 @@
       <c r="O160" s="13" t="n"/>
       <c r="P160" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main 1,000 easy continuous. 4 × 50 breaststroke. Cool-down 200. Genuinely easy — you race tomorrow.</t>
+          <t>Upper day the day before a race, deliberately. Nothing here loads the legs, so it costs you nothing on Saturday — but skip the last set of everything and leave the gym feeling like you could have done more. If in doubt, skip it entirely; the race matters more than one session.</t>
         </is>
       </c>
     </row>
@@ -8399,19 +8397,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E161" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H161" s="8" t="n"/>
@@ -8424,19 +8422,19 @@
       <c r="O161" s="13" t="n"/>
       <c r="P161" s="7" t="inlineStr">
         <is>
-          <t>Upper day the day before a race, deliberately. Nothing here loads the legs, so it costs you nothing on Saturday — but skip the last set of everything and leave the gym feeling like you could have done more. If in doubt, skip it entirely; the race matters more than one session.</t>
+          <t>Mobility and foot intrinsics. Lay out race kit; run in the orthotics you have trained in, not new ones.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
@@ -8447,23 +8445,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>RACE — Redmond Reindeer Romp 5 mile (8 km)</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>55–65 min</t>
         </is>
       </c>
       <c r="H162" s="8" t="n"/>
-      <c r="I162" s="9" t="n"/>
+      <c r="I162" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J162" s="10" t="n"/>
       <c r="K162" s="11" t="n"/>
       <c r="L162" s="12" t="n"/>
@@ -8472,19 +8472,19 @@
       <c r="O162" s="13" t="n"/>
       <c r="P162" s="7" t="inlineStr">
         <is>
-          <t>Mobility and foot intrinsics. Lay out race kit; run in the orthotics you have trained in, not new ones.</t>
+          <t>Warm-up 1.5 km easy with 3 strides. Race: go out at 5:10/km for the first mile and let it come down — the classic error here is a first mile 20 s too fast. Target roughly 40–42 min if the shins are quiet; if they are not, run it as a steady effort and enjoy the morning. Cool-down 1 km.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
@@ -8495,25 +8495,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E163" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>RACE — Redmond Reindeer Romp 5 mile (8 km)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>55–65 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H163" s="8" t="n"/>
-      <c r="I163" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I163" s="9" t="n"/>
       <c r="J163" s="10" t="n"/>
       <c r="K163" s="11" t="n"/>
       <c r="L163" s="12" t="n"/>
@@ -8522,27 +8520,27 @@
       <c r="O163" s="13" t="n"/>
       <c r="P163" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 1.5 km easy with 3 strides. Race: go out at 5:10/km for the first mile and let it come down — the classic error here is a first mile 20 s too fast. Target roughly 40–42 min if the shins are quiet; if they are not, run it as a steady effort and enjoy the morning. Cool-down 1 km.</t>
+          <t>Thorough post-race mobility. Calves and shins will be the sorest — be gentle, and do not stretch into compartment pain. The old Sunday recovery swim is gone with the rest of the weekend swims; four swims and about 7,300 yd already clear the streak in a race week, and the day after 8 km is a day the legs want off their feet rather than another session.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -8552,16 +8550,16 @@
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Recovery swim</t>
+          <t>Swim — threshold 8 × 150</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>1,200 yd · 27–35 min</t>
+          <t>2,400 yd · 53–71 min</t>
         </is>
       </c>
       <c r="H164" s="8" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="I164" s="9" t="n"/>
       <c r="J164" s="10" t="n"/>
@@ -8572,42 +8570,42 @@
       <c r="O164" s="13" t="n"/>
       <c r="P164" s="7" t="inlineStr">
         <is>
-          <t>About 1,200 yd total, very easy. Flush the legs, loosen the shoulders, no pace work at all.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: closed-fist / sighting / breaststroke timing / stroke-count ladder. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 8 × 150 at CSS on 3:20. Cool-down 400. Post-race, so the legs are tired but the shoulders are fine — swimming is the perfect recovery training.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Easy spin</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="H165" s="8" t="n"/>
@@ -8620,19 +8618,19 @@
       <c r="O165" s="13" t="n"/>
       <c r="P165" s="7" t="inlineStr">
         <is>
-          <t>Thorough post-race mobility. Calves and shins will be the sorest — be gentle, and do not stretch into compartment pain.</t>
+          <t>Flush the legs after Saturday. No strength this week's start — let the race settle.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
@@ -8650,16 +8648,16 @@
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 8 × 150</t>
+          <t>Swim — speed + breaststroke</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
+          <t>2,000 yd · 44–59 min</t>
         </is>
       </c>
       <c r="H166" s="8" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="I166" s="9" t="n"/>
       <c r="J166" s="10" t="n"/>
@@ -8670,19 +8668,19 @@
       <c r="O166" s="13" t="n"/>
       <c r="P166" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: closed-fist / sighting / breaststroke timing / stroke-count ladder. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 8 × 150 at CSS on 3:20. Cool-down 400. Post-race, so the legs are tired but the shoulders are fine — swimming is the perfect recovery training.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: front scull / 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous — the Week 12 checkpoint. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
@@ -8693,23 +8691,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E167" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E167" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Easy spin</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="H167" s="8" t="n"/>
-      <c r="I167" s="9" t="n"/>
+      <c r="I167" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J167" s="10" t="n"/>
       <c r="K167" s="11" t="n"/>
       <c r="L167" s="12" t="n"/>
@@ -8718,19 +8718,19 @@
       <c r="O167" s="13" t="n"/>
       <c r="P167" s="7" t="inlineStr">
         <is>
-          <t>Flush the legs after Saturday. No strength this week's start — let the race settle.</t>
+          <t>First run back after the race. Easy, short, soft surface.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
@@ -8748,16 +8748,16 @@
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed + breaststroke</t>
+          <t>Swim — long aerobic 1,400</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
+          <t>2,400 yd · 53–71 min</t>
         </is>
       </c>
       <c r="H168" s="8" t="n">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="I168" s="9" t="n"/>
       <c r="J168" s="10" t="n"/>
@@ -8768,19 +8768,19 @@
       <c r="O168" s="13" t="n"/>
       <c r="P168" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: front scull / 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous — the Week 12 checkpoint. Cool-down 300.</t>
+          <t>Warm-up 300. Main: 1,400 continuous, then 4 × 100 at CSS. Cool-down 300. Morning session — flight is at 4:30 pm. Three swims brings the week to about 6,800 yd, so the streak holds through the trip.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
@@ -8791,25 +8791,23 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E169" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>28 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H169" s="8" t="n"/>
-      <c r="I169" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I169" s="9" t="n"/>
       <c r="J169" s="10" t="n"/>
       <c r="K169" s="11" t="n"/>
       <c r="L169" s="12" t="n"/>
@@ -8818,19 +8816,19 @@
       <c r="O169" s="13" t="n"/>
       <c r="P169" s="7" t="inlineStr">
         <is>
-          <t>First run back after the race. Easy, short, soft surface.</t>
+          <t>Pre-flight mobility.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
@@ -8841,25 +8839,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E170" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,400</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H170" s="8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I170" s="9" t="n"/>
+          <t>35 min</t>
+        </is>
+      </c>
+      <c r="H170" s="8" t="n"/>
+      <c r="I170" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J170" s="10" t="n"/>
       <c r="K170" s="11" t="n"/>
       <c r="L170" s="12" t="n"/>
@@ -8868,19 +8866,19 @@
       <c r="O170" s="13" t="n"/>
       <c r="P170" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,400 continuous, then 4 × 100 at CSS. Cool-down 300. Morning session — flight is at 4:30 pm. Three swims brings the week to about 6,800 yd, so the streak holds through the trip.</t>
+          <t>Orlando, wedding day one. Get it done early — Florida in December is pleasant at 7 am and the day will get away from you. Easy pace.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
@@ -8916,19 +8914,19 @@
       <c r="O171" s="13" t="n"/>
       <c r="P171" s="7" t="inlineStr">
         <is>
-          <t>Pre-flight mobility.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
@@ -8939,25 +8937,23 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E172" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E172" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Bands + bodyweight circuit</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H172" s="8" t="n"/>
-      <c r="I172" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I172" s="9" t="n"/>
       <c r="J172" s="10" t="n"/>
       <c r="K172" s="11" t="n"/>
       <c r="L172" s="12" t="n"/>
@@ -8966,19 +8962,19 @@
       <c r="O172" s="13" t="n"/>
       <c r="P172" s="7" t="inlineStr">
         <is>
-          <t>Orlando, wedding day one. Get it done early — Florida in December is pleasant at 7 am and the day will get away from you. Easy pace.</t>
+          <t>Orlando, wedding day two. Short bands-and-bodyweight session in the room before the day starts: 2 rounds of banded RDL 15, split squat 10/leg, banded lateral walk 15/side, calf raise 20, tibialis raise 20, dead bug 10/side. Twenty-five minutes, no equipment, and it keeps the lower-leg work unbroken through the one week that would otherwise lose it.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
@@ -8996,12 +8992,12 @@
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Walk + mobility</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H173" s="8" t="n"/>
@@ -9014,19 +9010,19 @@
       <c r="O173" s="13" t="n"/>
       <c r="P173" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Mobility and a walk rather than a run — you ran yesterday and the week's third run is Sunday in Miami. Three runs, 15 km, is the cap for a travel week.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
@@ -9044,12 +9040,12 @@
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Bands + bodyweight circuit</t>
+          <t>Hotel gym / bodyweight circuit</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>35–40 min</t>
         </is>
       </c>
       <c r="H174" s="8" t="n"/>
@@ -9062,19 +9058,19 @@
       <c r="O174" s="13" t="n"/>
       <c r="P174" s="7" t="inlineStr">
         <is>
-          <t>Orlando, wedding day two. Short bands-and-bodyweight session in the room before the day starts: 2 rounds of banded RDL 15, split squat 10/leg, banded lateral walk 15/side, calf raise 20, tibialis raise 20, dead bug 10/side. Twenty-five minutes, no equipment, and it keeps the lower-leg work unbroken through the one week that would otherwise lose it.</t>
+          <t>Miami. 3 rounds of split squat 10/leg, banded RDL 15, calf raise 20, tibialis raise 20, Copenhagen plank 20 s/side, dead bug 10/side, plank 45 s. If the hotel gym has weights, swap in RDLs.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
@@ -9092,12 +9088,12 @@
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Walk + mobility</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H175" s="8" t="n"/>
@@ -9110,19 +9106,19 @@
       <c r="O175" s="13" t="n"/>
       <c r="P175" s="7" t="inlineStr">
         <is>
-          <t>Mobility and a walk rather than a run — you ran yesterday and the week's third run is Sunday in Miami. Three runs, 15 km, is the cap for a travel week.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
@@ -9133,23 +9129,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E176" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E176" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Hotel gym / bodyweight circuit</t>
+          <t>Easy run — 6 km</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>35–40 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H176" s="8" t="n"/>
-      <c r="I176" s="9" t="n"/>
+      <c r="I176" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="J176" s="10" t="n"/>
       <c r="K176" s="11" t="n"/>
       <c r="L176" s="12" t="n"/>
@@ -9158,19 +9156,19 @@
       <c r="O176" s="13" t="n"/>
       <c r="P176" s="7" t="inlineStr">
         <is>
-          <t>Miami. 3 rounds of split squat 10/leg, banded RDL 15, calf raise 20, tibialis raise 20, Copenhagen plank 20 s/side, dead bug 10/side, plank 45 s. If the hotel gym has weights, swap in RDLs.</t>
+          <t>Miami. Beach path or boardwalk, easy. If the hotel has a pool worth swimming in, an easy 800–1,000 yd afterwards is a bonus, not a requirement.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
@@ -9206,48 +9204,48 @@
       <c r="O177" s="13" t="n"/>
       <c r="P177" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Mobility and foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E178" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 6 km</t>
+          <t>Swim — threshold 5 × 200</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
-        </is>
-      </c>
-      <c r="H178" s="8" t="n"/>
-      <c r="I178" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>2,000 yd · 44–59 min</t>
+        </is>
+      </c>
+      <c r="H178" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I178" s="9" t="n"/>
       <c r="J178" s="10" t="n"/>
       <c r="K178" s="11" t="n"/>
       <c r="L178" s="12" t="n"/>
@@ -9256,42 +9254,42 @@
       <c r="O178" s="13" t="n"/>
       <c r="P178" s="7" t="inlineStr">
         <is>
-          <t>Miami. Beach path or boardwalk, easy. If the hotel has a pool worth swimming in, an easy 800–1,000 yd afterwards is a bonus, not a requirement.</t>
+          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for breaststroke timing. Main: 5 × 200 at CSS on 4:25. Cool-down 300. Back in a pool after four days off — ease into the first 200.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E179" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H179" s="8" t="n"/>
@@ -9304,19 +9302,19 @@
       <c r="O179" s="13" t="n"/>
       <c r="P179" s="7" t="inlineStr">
         <is>
-          <t>Mobility and foot intrinsics.</t>
+          <t>First full lift since race week. Back the loads off slightly and rebuild.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
@@ -9327,25 +9325,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E180" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 5 × 200</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H180" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I180" s="9" t="n"/>
+          <t>35 min</t>
+        </is>
+      </c>
+      <c r="H180" s="8" t="n"/>
+      <c r="I180" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J180" s="10" t="n"/>
       <c r="K180" s="11" t="n"/>
       <c r="L180" s="12" t="n"/>
@@ -9354,19 +9352,19 @@
       <c r="O180" s="13" t="n"/>
       <c r="P180" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for breaststroke timing. Main: 5 × 200 at CSS on 4:25. Cool-down 300. Back in a pool after four days off — ease into the first 200.</t>
+          <t>North Carolina. Explore — trails if there are any nearby.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
@@ -9384,7 +9382,7 @@
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Back and biceps</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -9402,7 +9400,7 @@
       <c r="O181" s="13" t="n"/>
       <c r="P181" s="7" t="inlineStr">
         <is>
-          <t>First full lift since race week. Back the loads off slightly and rebuild.</t>
+          <t>Upper day. The North Carolina gym has full equipment, so nothing needs substituting. Pulling pairs well with an easy run and keeps Friday's Strength B on fresh legs.</t>
         </is>
       </c>
     </row>
@@ -9425,25 +9423,23 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E182" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H182" s="8" t="n"/>
-      <c r="I182" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I182" s="9" t="n"/>
       <c r="J182" s="10" t="n"/>
       <c r="K182" s="11" t="n"/>
       <c r="L182" s="12" t="n"/>
@@ -9452,19 +9448,19 @@
       <c r="O182" s="13" t="n"/>
       <c r="P182" s="7" t="inlineStr">
         <is>
-          <t>North Carolina. Explore — trails if there are any nearby.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
@@ -9475,22 +9471,24 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E183" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Swim — speed 20 × 50</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H183" s="8" t="n"/>
+          <t>2,200 yd · 49–65 min</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="n">
+        <v>2200</v>
+      </c>
       <c r="I183" s="9" t="n"/>
       <c r="J183" s="10" t="n"/>
       <c r="K183" s="11" t="n"/>
@@ -9500,19 +9498,19 @@
       <c r="O183" s="13" t="n"/>
       <c r="P183" s="7" t="inlineStr">
         <is>
-          <t>Upper day. The North Carolina gym has full equipment, so nothing needs substituting. Pulling pairs well with an easy run and keeps Friday's Strength B on fresh legs.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
@@ -9523,19 +9521,19 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — sweet spot 3 × 10 min</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="H184" s="8" t="n"/>
@@ -9548,19 +9546,19 @@
       <c r="O184" s="13" t="n"/>
       <c r="P184" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>3 × 10 min at sweet spot, 4 min easy between.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
@@ -9571,25 +9569,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E185" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 20 × 50</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>2,200 yd · 49–65 min</t>
-        </is>
-      </c>
-      <c r="H185" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I185" s="9" t="n"/>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="H185" s="8" t="n"/>
+      <c r="I185" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J185" s="10" t="n"/>
       <c r="K185" s="11" t="n"/>
       <c r="L185" s="12" t="n"/>
@@ -9598,19 +9596,19 @@
       <c r="O185" s="13" t="n"/>
       <c r="P185" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
+          <t>Travel day home. Morning run before the flight.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
@@ -9621,22 +9619,24 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E186" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — sweet spot 3 × 10 min</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="H186" s="8" t="n"/>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H186" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="I186" s="9" t="n"/>
       <c r="J186" s="10" t="n"/>
       <c r="K186" s="11" t="n"/>
@@ -9646,7 +9646,7 @@
       <c r="O186" s="13" t="n"/>
       <c r="P186" s="7" t="inlineStr">
         <is>
-          <t>3 × 10 min at sweet spot, 4 min easy between.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived. This moved off Saturday with the rest of the weekend swims, so it lands on a travel morning — if the flight is early, this is the most droppable session of the week. Let it go rather than rushing it.</t>
         </is>
       </c>
     </row>
@@ -9669,25 +9669,23 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E187" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H187" s="8" t="n"/>
-      <c r="I187" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I187" s="9" t="n"/>
       <c r="J187" s="10" t="n"/>
       <c r="K187" s="11" t="n"/>
       <c r="L187" s="12" t="n"/>
@@ -9696,19 +9694,19 @@
       <c r="O187" s="13" t="n"/>
       <c r="P187" s="7" t="inlineStr">
         <is>
-          <t>Travel day home. Morning run before the flight.</t>
+          <t>Travel mobility.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
@@ -9719,22 +9717,24 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — long aerobic 1,600</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H188" s="8" t="n"/>
+          <t>2,600 yd · 58–76 min</t>
+        </is>
+      </c>
+      <c r="H188" s="8" t="n">
+        <v>2600</v>
+      </c>
       <c r="I188" s="9" t="n"/>
       <c r="J188" s="10" t="n"/>
       <c r="K188" s="11" t="n"/>
@@ -9744,7 +9744,7 @@
       <c r="O188" s="13" t="n"/>
       <c r="P188" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility.</t>
+          <t>Warm-up 300. Main: 1,600 continuous, then 4 × 100 at CSS. Cool-down 300. Home pool.</t>
         </is>
       </c>
     </row>
@@ -9767,24 +9767,22 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E189" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,600</t>
+          <t>Strength B — Bulgarian split squat + hips and core</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2,600 yd · 58–76 min</t>
-        </is>
-      </c>
-      <c r="H189" s="8" t="n">
-        <v>2600</v>
-      </c>
+          <t>45–55 min</t>
+        </is>
+      </c>
+      <c r="H189" s="8" t="n"/>
       <c r="I189" s="9" t="n"/>
       <c r="J189" s="10" t="n"/>
       <c r="K189" s="11" t="n"/>
@@ -9794,19 +9792,19 @@
       <c r="O189" s="13" t="n"/>
       <c r="P189" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,600 continuous, then 4 × 100 at CSS. Cool-down 300. Home pool.</t>
+          <t>Standard Strength B.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
@@ -9817,19 +9815,19 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E190" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Weekend aerobic — ride, hike, or stairs</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>2–3 hr</t>
         </is>
       </c>
       <c r="H190" s="8" t="n"/>
@@ -9842,19 +9840,19 @@
       <c r="O190" s="13" t="n"/>
       <c r="P190" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Winter options: spin bike endurance, a shorter hike, or 45 min on the stairmaster with 20 lb.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
@@ -9865,23 +9863,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E191" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E191" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Weekend aerobic — ride, hike, or stairs</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>2–3 hr</t>
+          <t>50–55 min</t>
         </is>
       </c>
       <c r="H191" s="8" t="n"/>
-      <c r="I191" s="9" t="n"/>
+      <c r="I191" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J191" s="10" t="n"/>
       <c r="K191" s="11" t="n"/>
       <c r="L191" s="12" t="n"/>
@@ -9890,19 +9890,19 @@
       <c r="O191" s="13" t="n"/>
       <c r="P191" s="7" t="inlineStr">
         <is>
-          <t>Winter options: spin bike endurance, a shorter hike, or 45 min on the stairmaster with 20 lb.</t>
+          <t>Back to race distance, easy. The run base is worth keeping through the holidays rather than rebuilding in January.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
@@ -9913,24 +9913,22 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H192" s="8" t="n">
-        <v>1400</v>
-      </c>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="H192" s="8" t="n"/>
       <c r="I192" s="9" t="n"/>
       <c r="J192" s="10" t="n"/>
       <c r="K192" s="11" t="n"/>
@@ -9940,48 +9938,48 @@
       <c r="O192" s="13" t="n"/>
       <c r="P192" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Mobility plus foot intrinsics. Pack for Edmonton.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E193" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Swim — threshold 4 × 300</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>50–55 min</t>
-        </is>
-      </c>
-      <c r="H193" s="8" t="n"/>
-      <c r="I193" s="9" t="n">
-        <v>8</v>
-      </c>
+          <t>2,300 yd · 51–68 min</t>
+        </is>
+      </c>
+      <c r="H193" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I193" s="9" t="n"/>
       <c r="J193" s="10" t="n"/>
       <c r="K193" s="11" t="n"/>
       <c r="L193" s="12" t="n"/>
@@ -9990,42 +9988,42 @@
       <c r="O193" s="13" t="n"/>
       <c r="P193" s="7" t="inlineStr">
         <is>
-          <t>Back to race distance, easy. The run base is worth keeping through the holidays rather than rebuilding in January.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 4 × 300 at CSS on 6:30 — tighter than Week 5's version of this set. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E194" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E194" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H194" s="8" t="n"/>
@@ -10038,19 +10036,19 @@
       <c r="O194" s="13" t="n"/>
       <c r="P194" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics. Pack for Edmonton.</t>
+          <t>Standard Strength A.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
@@ -10061,25 +10059,25 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E195" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 4 × 300</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H195" s="8" t="n">
-        <v>2300</v>
-      </c>
-      <c r="I195" s="9" t="n"/>
+          <t>35 min</t>
+        </is>
+      </c>
+      <c r="H195" s="8" t="n"/>
+      <c r="I195" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J195" s="10" t="n"/>
       <c r="K195" s="11" t="n"/>
       <c r="L195" s="12" t="n"/>
@@ -10088,19 +10086,19 @@
       <c r="O195" s="13" t="n"/>
       <c r="P195" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 4 × 300 at CSS on 6:30 — tighter than Week 5's version of this set. Cool-down 300.</t>
+          <t>Last Seattle run of the year. Soft surface.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
@@ -10111,22 +10109,24 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E196" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H196" s="8" t="n"/>
+          <t>2,800 yd · 62–82 min</t>
+        </is>
+      </c>
+      <c r="H196" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="I196" s="9" t="n"/>
       <c r="J196" s="10" t="n"/>
       <c r="K196" s="11" t="n"/>
@@ -10136,19 +10136,19 @@
       <c r="O196" s="13" t="n"/>
       <c r="P196" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>Warm-up 300. Main: 1,800 continuous, then 4 × 100 at CSS. Cool-down 300. The week's long swim, pulled off Boxing Day to your home pool on your last Seattle day — you know this water, the lane etiquette and the clock, which is exactly what you want for the longest continuous swim of the week.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="H197" s="8" t="n"/>
       <c r="I197" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J197" s="10" t="n"/>
       <c r="K197" s="11" t="n"/>
@@ -10186,19 +10186,19 @@
       <c r="O197" s="13" t="n"/>
       <c r="P197" s="7" t="inlineStr">
         <is>
-          <t>Last Seattle run of the year. Soft surface.</t>
+          <t>Travel day to Edmonton. Indoor track or treadmill given the conditions. CHECK THE GYM'S HOLIDAY HOURS TODAY and shuffle this week's swims to fit them.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
@@ -10236,7 +10236,7 @@
       <c r="O198" s="13" t="n"/>
       <c r="P198" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived. Deliberately the smallest swim of the week on the most disrupted day — fit it around the flight, and if Edmonton's pool hours do not cooperate, this is the one to drop.</t>
         </is>
       </c>
     </row>
@@ -10259,25 +10259,23 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E199" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H199" s="8" t="n"/>
-      <c r="I199" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I199" s="9" t="n"/>
       <c r="J199" s="10" t="n"/>
       <c r="K199" s="11" t="n"/>
       <c r="L199" s="12" t="n"/>
@@ -10286,19 +10284,19 @@
       <c r="O199" s="13" t="n"/>
       <c r="P199" s="7" t="inlineStr">
         <is>
-          <t>Travel day to Edmonton. Indoor track or treadmill given the conditions. CHECK THE GYM'S HOLIDAY HOURS TODAY and shuffle this week's swims to fit them.</t>
+          <t>Travel mobility.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
@@ -10309,22 +10307,24 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E200" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Swim — speed</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H200" s="8" t="n"/>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H200" s="8" t="n">
+        <v>2400</v>
+      </c>
       <c r="I200" s="9" t="n"/>
       <c r="J200" s="10" t="n"/>
       <c r="K200" s="11" t="n"/>
@@ -10334,19 +10334,19 @@
       <c r="O200" s="13" t="n"/>
       <c r="P200" s="7" t="inlineStr">
         <is>
-          <t>Leg day moved up to Wednesday this week so it sits four days clear of Sunday's long run. Standard Strength B — Bulgarian split squats, step-ups, Copenhagen planks.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 24 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300. Christmas Eve — likely reduced pool hours, so go early.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
@@ -10357,19 +10357,19 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E201" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Strength B — Bulgarian split squat + hips and core</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H201" s="8" t="n"/>
@@ -10382,7 +10382,7 @@
       <c r="O201" s="13" t="n"/>
       <c r="P201" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility.</t>
+          <t>Leg day on Christmas Eve, which puts it three clear days before Sunday's long run — close the gym out early if you need to, but do not push it later into the week or it lands too close to that run. Standard Strength B: Bulgarian split squats, step-ups, Copenhagen planks.</t>
         </is>
       </c>
     </row>
@@ -10405,24 +10405,22 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H202" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H202" s="8" t="n"/>
       <c r="I202" s="9" t="n"/>
       <c r="J202" s="10" t="n"/>
       <c r="K202" s="11" t="n"/>
@@ -10432,19 +10430,19 @@
       <c r="O202" s="13" t="n"/>
       <c r="P202" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 24 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300. Christmas Eve — likely reduced pool hours, so go early.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C203" s="5" t="n">
@@ -10455,19 +10453,19 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E203" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Rest day — walk and stretch</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>20–30 min</t>
         </is>
       </c>
       <c r="H203" s="8" t="n"/>
@@ -10480,19 +10478,19 @@
       <c r="O203" s="13" t="n"/>
       <c r="P203" s="7" t="inlineStr">
         <is>
-          <t>Upper day on Christmas Eve — short and unglamorous, but it is the last pulling session of the block. If the gym closes early, cut to two sets of everything and still do the pull-ups.</t>
+          <t>Christmas Day. Rest, stretch, walk if you feel like it. Nothing structured — this is the one fully off day in the block and taking it properly is part of the plan.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C204" s="5" t="n">
@@ -10503,19 +10501,19 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E204" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — Z2</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="H204" s="8" t="n"/>
@@ -10528,19 +10526,19 @@
       <c r="O204" s="13" t="n"/>
       <c r="P204" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Boxing Day ride, all indoors — Edmonton in late December is not outdoor riding weather. Fifty minutes steady at 130–145 bpm, and an easy one to swap for a ski or a walk with your partner if that is the better use of the morning.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C205" s="5" t="n">
@@ -10551,19 +10549,19 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E205" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>Rest day — walk and stretch</t>
+          <t>Back and biceps</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>20–30 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H205" s="8" t="n"/>
@@ -10576,19 +10574,19 @@
       <c r="O205" s="13" t="n"/>
       <c r="P205" s="7" t="inlineStr">
         <is>
-          <t>Christmas Day. Rest, stretch, walk if you feel like it. Nothing structured — this is the one fully off day in the block and taking it properly is part of the plan.</t>
+          <t>Upper day, and the last pulling session of the block. It sits on Saturday because every weekday this week already carries a swim, and pulling is the one strength session that leaves the legs completely alone the day before an 8 km long run. If the gym closes early, cut to two sets of everything and still do the pull-ups.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C206" s="5" t="n">
@@ -10599,25 +10597,25 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E206" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>2,800 yd · 62–82 min</t>
-        </is>
-      </c>
-      <c r="H206" s="8" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I206" s="9" t="n"/>
+          <t>50–55 min</t>
+        </is>
+      </c>
+      <c r="H206" s="8" t="n"/>
+      <c r="I206" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J206" s="10" t="n"/>
       <c r="K206" s="11" t="n"/>
       <c r="L206" s="12" t="n"/>
@@ -10626,19 +10624,19 @@
       <c r="O206" s="13" t="n"/>
       <c r="P206" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous, then 4 × 100 at CSS. Cool-down 300.</t>
+          <t>Indoor track if the footing is bad, outside if it is clear and you are dressed for it.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C207" s="5" t="n">
@@ -10656,12 +10654,12 @@
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Spin bike — easy Z2</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="H207" s="8" t="n"/>
@@ -10674,7 +10672,7 @@
       <c r="O207" s="13" t="n"/>
       <c r="P207" s="7" t="inlineStr">
         <is>
-          <t>Boxing Day ride, all indoors — Edmonton in late December is not outdoor riding weather. Fifty minutes steady at 130–145 bpm. Legs are fresh because the leg day moved to Wednesday.</t>
+          <t>Easy spin after the long run, same day on purpose: thirty minutes of light pedalling flushes the calves better than sitting still, and it keeps the hard days hard and the easy days easy. Keep it genuinely easy — if it feels like work, stop.</t>
         </is>
       </c>
     </row>
@@ -10697,25 +10695,23 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E208" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>50–55 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H208" s="8" t="n"/>
-      <c r="I208" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I208" s="9" t="n"/>
       <c r="J208" s="10" t="n"/>
       <c r="K208" s="11" t="n"/>
       <c r="L208" s="12" t="n"/>
@@ -10724,45 +10720,47 @@
       <c r="O208" s="13" t="n"/>
       <c r="P208" s="7" t="inlineStr">
         <is>
-          <t>Indoor track if the footing is bad, outside if it is clear and you are dressed for it.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C209" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E209" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — easy Z2</t>
+          <t>Swim — FINAL CSS TEST (400 + 200 TT)</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="H209" s="8" t="n"/>
+          <t>1,600 yd · 36–47 min</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="n">
+        <v>1600</v>
+      </c>
       <c r="I209" s="9" t="n"/>
       <c r="J209" s="10" t="n"/>
       <c r="K209" s="11" t="n"/>
@@ -10772,42 +10770,42 @@
       <c r="O209" s="13" t="n"/>
       <c r="P209" s="7" t="inlineStr">
         <is>
-          <t>Easy spin after the long run, same day on purpose: thirty minutes of light pedalling flushes the calves better than sitting still, and it keeps the hard days hard and the easy days easy. Keep it genuinely easy — if it feels like work, stop.</t>
+          <t>Same protocol as Weeks 1 and 8. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. This is the block's headline number. Compare all three tests side by side — Week 1, Week 8, and today.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C210" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E210" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Strength A — RDL + posterior chain</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>45–55 min</t>
         </is>
       </c>
       <c r="H210" s="8" t="n"/>
@@ -10820,19 +10818,19 @@
       <c r="O210" s="13" t="n"/>
       <c r="P210" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics.</t>
+          <t>Last Strength A of the year. Log the RDL and split squat loads next to the Week 1 numbers.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C211" s="5" t="n">
@@ -10843,25 +10841,25 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E211" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>Swim — FINAL CSS TEST (400 + 200 TT)</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>1,600 yd · 36–47 min</t>
-        </is>
-      </c>
-      <c r="H211" s="8" t="n">
-        <v>1600</v>
-      </c>
-      <c r="I211" s="9" t="n"/>
+          <t>35–40 min</t>
+        </is>
+      </c>
+      <c r="H211" s="8" t="n"/>
+      <c r="I211" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J211" s="10" t="n"/>
       <c r="K211" s="11" t="n"/>
       <c r="L211" s="12" t="n"/>
@@ -10870,19 +10868,19 @@
       <c r="O211" s="13" t="n"/>
       <c r="P211" s="7" t="inlineStr">
         <is>
-          <t>Same protocol as Weeks 1 and 8. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. This is the block's headline number. Compare all three tests side by side — Week 1, Week 8, and today.</t>
+          <t>Easy. Indoor track if needed.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C212" s="5" t="n">
@@ -10893,22 +10891,24 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E212" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H212" s="8" t="n"/>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H212" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="I212" s="9" t="n"/>
       <c r="J212" s="10" t="n"/>
       <c r="K212" s="11" t="n"/>
@@ -10918,7 +10918,7 @@
       <c r="O212" s="13" t="n"/>
       <c r="P212" s="7" t="inlineStr">
         <is>
-          <t>Last Strength A of the year. Log the RDL and split squat loads next to the Week 1 numbers.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
@@ -10941,25 +10941,23 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E213" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>35–40 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H213" s="8" t="n"/>
-      <c r="I213" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I213" s="9" t="n"/>
       <c r="J213" s="10" t="n"/>
       <c r="K213" s="11" t="n"/>
       <c r="L213" s="12" t="n"/>
@@ -10968,19 +10966,19 @@
       <c r="O213" s="13" t="n"/>
       <c r="P213" s="7" t="inlineStr">
         <is>
-          <t>Easy. Indoor track if needed.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C214" s="5" t="n">
@@ -10998,16 +10996,16 @@
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Swim — speed</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
+          <t>2,000 yd · 44–59 min</t>
         </is>
       </c>
       <c r="H214" s="8" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="I214" s="9" t="n"/>
       <c r="J214" s="10" t="n"/>
@@ -11018,19 +11016,19 @@
       <c r="O214" s="13" t="n"/>
       <c r="P214" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C215" s="5" t="n">
@@ -11041,19 +11039,19 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E215" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — easy aerobic (optional)</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H215" s="8" t="n"/>
@@ -11066,7 +11064,7 @@
       <c r="O215" s="13" t="n"/>
       <c r="P215" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Optional. Skip it without guilt if the legs feel the long run coming tomorrow.</t>
         </is>
       </c>
     </row>
@@ -11089,24 +11087,22 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H216" s="8" t="n">
-        <v>2000</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H216" s="8" t="n"/>
       <c r="I216" s="9" t="n"/>
       <c r="J216" s="10" t="n"/>
       <c r="K216" s="11" t="n"/>
@@ -11116,19 +11112,19 @@
       <c r="O216" s="13" t="n"/>
       <c r="P216" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous. Cool-down 300.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C217" s="5" t="n">
@@ -11139,23 +11135,25 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E217" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E217" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — easy aerobic (optional)</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>55–62 min</t>
         </is>
       </c>
       <c r="H217" s="8" t="n"/>
-      <c r="I217" s="9" t="n"/>
+      <c r="I217" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J217" s="10" t="n"/>
       <c r="K217" s="11" t="n"/>
       <c r="L217" s="12" t="n"/>
@@ -11164,19 +11162,19 @@
       <c r="O217" s="13" t="n"/>
       <c r="P217" s="7" t="inlineStr">
         <is>
-          <t>Optional. Skip it without guilt if the legs feel the long run coming tomorrow.</t>
+          <t>Last run of the block, and the last run of the year. Easy effort, soft surface, orthotics in. Fifteen weeks ago 5 km was your entire week.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C218" s="5" t="n">
@@ -11187,22 +11185,24 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E218" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — long aerobic 2,000</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H218" s="8" t="n"/>
+          <t>2,600 yd · 58–76 min</t>
+        </is>
+      </c>
+      <c r="H218" s="8" t="n">
+        <v>2600</v>
+      </c>
       <c r="I218" s="9" t="n"/>
       <c r="J218" s="10" t="n"/>
       <c r="K218" s="11" t="n"/>
@@ -11212,7 +11212,7 @@
       <c r="O218" s="13" t="n"/>
       <c r="P218" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Warm-up 300. Main: 2,000 continuous at the new aerobic pace. Cool-down 300. Fifteen weeks ago a 1,000 was the long swim. Finish the year with double it.</t>
         </is>
       </c>
     </row>
@@ -11235,25 +11235,23 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E219" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>55–62 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H219" s="8" t="n"/>
-      <c r="I219" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I219" s="9" t="n"/>
       <c r="J219" s="10" t="n"/>
       <c r="K219" s="11" t="n"/>
       <c r="L219" s="12" t="n"/>
@@ -11262,124 +11260,26 @@
       <c r="O219" s="13" t="n"/>
       <c r="P219" s="7" t="inlineStr">
         <is>
-          <t>Last run of the block, and the last run of the year. Easy effort, soft surface, orthotics in. Fifteen weeks ago 5 km was your entire week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B220" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C220" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D220" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E220" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
-        </is>
-      </c>
-      <c r="F220" s="7" t="inlineStr">
-        <is>
-          <t>Swim — long aerobic 2,000</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>2,600 yd · 58–76 min</t>
-        </is>
-      </c>
-      <c r="H220" s="8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="I220" s="9" t="n"/>
-      <c r="J220" s="10" t="n"/>
-      <c r="K220" s="11" t="n"/>
-      <c r="L220" s="12" t="n"/>
-      <c r="M220" s="10" t="n"/>
-      <c r="N220" s="10" t="n"/>
-      <c r="O220" s="13" t="n"/>
-      <c r="P220" s="7" t="inlineStr">
-        <is>
-          <t>Warm-up 300. Main: 2,000 continuous at the new aerobic pace. Cool-down 300. Fifteen weeks ago a 1,000 was the long swim. Finish the year with double it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B221" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C221" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D221" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E221" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr">
-        <is>
-          <t>Mobility + lower-leg prehab</t>
-        </is>
-      </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t>25 min</t>
-        </is>
-      </c>
-      <c r="H221" s="8" t="n"/>
-      <c r="I221" s="9" t="n"/>
-      <c r="J221" s="10" t="n"/>
-      <c r="K221" s="11" t="n"/>
-      <c r="L221" s="12" t="n"/>
-      <c r="M221" s="10" t="n"/>
-      <c r="N221" s="10" t="n"/>
-      <c r="O221" s="13" t="n"/>
-      <c r="P221" s="7" t="inlineStr">
-        <is>
           <t>Final mobility session of the block. Then sit down and plan the January Victoria 70.3 build — including whether Rainier and Victoria can actually coexist.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P221"/>
+  <autoFilter ref="A4:P219"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:P221">
+  <conditionalFormatting sqref="A5:P219">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="Y"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J221" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N,skipped,moved"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N221" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="N5:N219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -14479,7 +14379,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Down week. Flying home plus four swims in four days — running gives way.</t>
+          <t>Down week. Flying home plus three swims in three days — running gives way.</t>
         </is>
       </c>
     </row>

--- a/Abid — Fall 2026 Training Block.xlsx
+++ b/Abid — Fall 2026 Training Block.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Log'!$A$4:$P$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Log'!$A$4:$P$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P219"/>
+  <dimension ref="A1:P209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H63" s="8" t="n"/>
@@ -3630,7 +3630,7 @@
       <c r="O63" s="13" t="n"/>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>First full-body session — the hamstring day and the pulling day merged into one, run as supersets so it fits in about 45 minutes. Start the RDL at last Monday's load and the pull-ups at last week's reps; the only new thing today is the pairing. If time is tight, trim the C block, never the tibialis raises.</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Full body B — single-leg + press</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H70" s="8" t="n"/>
@@ -3974,7 +3974,7 @@
       <c r="O70" s="13" t="n"/>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Second full-body session — the quad day and the pressing day merged. Run first, lift after. The split squat stays heavier than Monday's; the seated calf raise is the soleus and gets the bigger calf dose of the week.</t>
         </is>
       </c>
     </row>
@@ -4047,19 +4047,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E72" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H72" s="8" t="n"/>
@@ -4072,19 +4072,19 @@
       <c r="O72" s="13" t="n"/>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>Pulling day. Do this after the long swim, not before — a fatigued lat rows fine but swims badly. If the pull-ups are gone by now, switch to lat pull-downs and chase the same rep target.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month. Friday used to carry the upper-body lift as well; with strength down to two sessions, that time is simply back.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
@@ -4095,23 +4095,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Long run — 5 km</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>35–38 min</t>
         </is>
       </c>
       <c r="H73" s="8" t="n"/>
-      <c r="I73" s="9" t="n"/>
+      <c r="I73" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="11" t="n"/>
       <c r="L73" s="12" t="n"/>
@@ -4120,7 +4122,7 @@
       <c r="O73" s="13" t="n"/>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Third run of the week and the longest of the three, but still short and easy. On Saturday this week because tomorrow is the flight — normally the long run floats between Saturday and Sunday around whatever the flex slot is doing. Run it before the ride or hike, not after.</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4152,12 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Weekend aerobic — long ride or hike</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2.5–3.5 hr</t>
+          <t>1.5–2.5 hr</t>
         </is>
       </c>
       <c r="H74" s="8" t="n"/>
@@ -4168,7 +4170,7 @@
       <c r="O74" s="13" t="n"/>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>Pack 15 lb if hiking.</t>
+          <t>Shorter than usual — you fly tomorrow and the long run is already in the legs. A relaxed ride or hike, or skip it entirely if packing eats the afternoon. Pack 15 lb if hiking.</t>
         </is>
       </c>
     </row>
@@ -4191,25 +4193,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Travel mobility</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>35–38 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H75" s="8" t="n"/>
-      <c r="I75" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I75" s="9" t="n"/>
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="11" t="n"/>
       <c r="L75" s="12" t="n"/>
@@ -4218,45 +4218,47 @@
       <c r="O75" s="13" t="n"/>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>Third run of the week, easy. Longest of the three but still short.</t>
+          <t>Flight to New York. Mobility plus foot intrinsics before you leave, calf raises and ankle circles in the terminal. Pack running shoes, bands, goggles and a swim cap.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
           <t>build1</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — threshold 3 × (6 × 100), Chinatown YMCA</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="n"/>
+          <t>3,000 yd · 67–88 min</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>3000</v>
+      </c>
       <c r="I76" s="9" t="n"/>
       <c r="J76" s="10" t="n"/>
       <c r="K76" s="11" t="n"/>
@@ -4266,7 +4268,7 @@
       <c r="O76" s="13" t="n"/>
       <c r="P76" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics. Pack for New York — running shoes, bands, goggles.</t>
+          <t>Warm-up 500. Drill 400 as 8 × 50, each drill twice: front scull / single-arm / closed-fist / catch-up. Snorkel and fins if you packed them. Main: 3 rounds of 6 × 100 at CSS on 2:15, 1 min between rounds (1,800 total). Cool-down 300. Chinatown YMCA, 273 Bowery at E Houston — 25 yd, about a 14-minute walk. Go 6:30–9 am, when five lanes are open; lessons cut it to three from 9 to 11. Call 212-912-2460 first to confirm the day-pass price and that it includes lap swim, and bring a home YMCA card if you have one. Backup: Asphalt Green Battery Park City, $35 at the desk, five lanes 7–9 am.</t>
         </is>
       </c>
     </row>
@@ -4289,24 +4291,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Swim — big front-load #1</t>
+          <t>Bands + bodyweight circuit</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>3,200 yd · 71–94 min</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="n">
-        <v>3200</v>
-      </c>
+          <t>40 min</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n"/>
       <c r="I77" s="9" t="n"/>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="11" t="n"/>
@@ -4316,19 +4316,19 @@
       <c r="O77" s="13" t="n"/>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 500. Drill 400 as 8 × 50, each drill twice: front scull / single-arm / closed-fist / catch-up. Snorkel and fins throughout. Main: 3 rounds of 6 × 100 at CSS on 2:15, 1 min between rounds (1,800 total). Cool-down 500. Long session, but you have five days out of the water coming — bank it.</t>
+          <t>Travel circuit A — hinge + pull, the stand-in for Full body A. 3 rounds: single-leg RDL 10/leg, split squat 10/leg, band row 15, band pull-apart 15, straight-leg calf raise 20, tibialis raise 20, dead bug 10/side. If the day pass covers the Y weight room, do it there after the swim with dumbbells; otherwise bands at the apartment.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
@@ -4339,23 +4339,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E78" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="H78" s="8" t="n"/>
-      <c r="I78" s="9" t="n"/>
+      <c r="I78" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J78" s="10" t="n"/>
       <c r="K78" s="11" t="n"/>
       <c r="L78" s="12" t="n"/>
@@ -4364,7 +4366,7 @@
       <c r="O78" s="13" t="n"/>
       <c r="P78" s="7" t="inlineStr">
         <is>
-          <t>Full session before travel.</t>
+          <t>First New York run, two days after the flight. The East River esplanade is a few blocks east of Attorney St — flat and paved, so keep it easy and the cadence high.</t>
         </is>
       </c>
     </row>
@@ -4387,24 +4389,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Swim — big front-load #2</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>3,200 yd · 71–94 min</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="n">
-        <v>3200</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n"/>
       <c r="I79" s="9" t="n"/>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="11" t="n"/>
@@ -4414,19 +4414,19 @@
       <c r="O79" s="13" t="n"/>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400. Main: 1,600 continuous aerobic, then 8 × 50 on 1:05. Cool-down 400. Morning session — flight is this evening. Two 3,000+ swims back to back keeps the weekly streak intact at 6,400 yd.</t>
+          <t>Travel mobility: hips, calves, thoracic spine. Flights make the ankles stiff — knee-to-wall check.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
@@ -4437,19 +4437,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Easy shakeout walk</t>
+          <t>Bands + bodyweight circuit</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H80" s="8" t="n"/>
@@ -4462,7 +4462,7 @@
       <c r="O80" s="13" t="n"/>
       <c r="P80" s="7" t="inlineStr">
         <is>
-          <t>Not a run — you already have a 3,000 yd swim in the legs today and a flight tonight. Twenty-five minutes of brisk walking to move blood through the calves before you sit for six hours. Run volume this week is capped at 14 km and all of it happens in New York.</t>
+          <t>Travel circuit B — single-leg + press, the stand-in for Full body B. 3 rounds: rear-foot-elevated split squat 10/leg (back foot on a chair or bed), step-up 10/leg, push-up 12–15, band row 15, bent-knee calf raise 25 (the soleus dose, hold a bag for load), Copenhagen plank 20 s/side, banded lateral walk 15/side.</t>
         </is>
       </c>
     </row>
@@ -4485,25 +4485,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H81" s="8" t="n"/>
-      <c r="I81" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I81" s="9" t="n"/>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="11" t="n"/>
       <c r="L81" s="12" t="n"/>
@@ -4512,19 +4510,19 @@
       <c r="O81" s="13" t="n"/>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>First New York morning after a late landing. Keep it short and easy — this is travel recovery, not training.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
@@ -4535,22 +4533,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — long aerobic 1,600, Chinatown YMCA</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H82" s="8" t="n"/>
+          <t>3,200 yd · 71–94 min</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>3200</v>
+      </c>
       <c r="I82" s="9" t="n"/>
       <c r="J82" s="10" t="n"/>
       <c r="K82" s="11" t="n"/>
@@ -4560,7 +4560,7 @@
       <c r="O82" s="13" t="n"/>
       <c r="P82" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility: hips, calves, thoracic spine. Long flights make the ankles stiff.</t>
+          <t>Warm-up 400. Drill 400. Main: 1,600 continuous aerobic, then 8 × 50 on 1:05. Cool-down 400. Morning again — lessons cut the Y to three lanes from 4 to 7:30 pm on Thursdays. Two swims at 6,200 yd keep the weekly streak intact; the next swim is Wednesday in Seattle.</t>
         </is>
       </c>
     </row>
@@ -4610,19 +4610,19 @@
       <c r="O83" s="13" t="n"/>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>New York running is the best part of this trip. Central Park reservoir loop is 2.5 km of soft cinder — ideal surface for your shins.</t>
+          <t>Swim in the morning, run later. If you are uptown anyway, the Central Park reservoir loop is 2.5 km of soft cinder, the best surface in Manhattan for your shins. Otherwise the esplanade again.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
@@ -4633,19 +4633,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Bands + bodyweight circuit</t>
+          <t>Rest + mobility</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H84" s="8" t="n"/>
@@ -4658,19 +4658,19 @@
       <c r="O84" s="13" t="n"/>
       <c r="P84" s="7" t="inlineStr">
         <is>
-          <t>Gym-optional: 3 rounds of banded RDL 15, split squat 10/leg, banded lateral walk 15/side, Copenhagen plank 20 s/side, calf raise 20, tibialis raise 20, dead bug 10/side.</t>
+          <t>Rest day: no training, just walk the city. Full mobility: hips, calves, thoracic spine, foot intrinsics. Fresh legs for tomorrow's long run.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
@@ -4681,23 +4681,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Bands + bodyweight circuit</t>
+          <t>Long run — 6 km</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>42–48 min</t>
         </is>
       </c>
       <c r="H85" s="8" t="n"/>
-      <c r="I85" s="9" t="n"/>
+      <c r="I85" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="11" t="n"/>
       <c r="L85" s="12" t="n"/>
@@ -4706,19 +4708,19 @@
       <c r="O85" s="13" t="n"/>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>Second travel circuit of the week. Hotel room or hotel gym, bands only. 3 rounds of banded RDL 15, split squat 10/leg, banded lateral walk 15/side, Copenhagen plank 20 s/side, calf raise 20, tibialis raise 20, dead bug 10/side. Five days without a pool or a bike means strength is the one quality you can actually hold here — do not skip it.</t>
+          <t>Longest run of the week. Central Park fills up with marathon-weekend setup, so stay downtown — East River esplanade, easy pace, cadence 175–180. Sunday is the flex slot, so it does not float this week.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
@@ -4741,7 +4743,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H86" s="8" t="n"/>
@@ -4754,19 +4756,19 @@
       <c r="O86" s="13" t="n"/>
       <c r="P86" s="7" t="inlineStr">
         <is>
-          <t>Full mobility: hips, calves, thoracic spine, foot intrinsics. Knee-to-wall check — travel weeks are when ankle range quietly disappears.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
@@ -4777,25 +4779,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E87" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Long run — 6 km</t>
+          <t>Weekend flex — Citi Bike or long walk</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>42–48 min</t>
+          <t>1–2 hr</t>
         </is>
       </c>
       <c r="H87" s="8" t="n"/>
-      <c r="I87" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="I87" s="9" t="n"/>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="11" t="n"/>
       <c r="L87" s="12" t="n"/>
@@ -4804,19 +4804,19 @@
       <c r="O87" s="13" t="n"/>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>Longest run of the week. Central Park bridle path or the reservoir — stay on the soft surfaces, avoid the paved loop.</t>
+          <t>Marathon Sunday. Walk up to First Avenue to watch the race come through, or take a Citi Bike up the Hudson River Greenway — easy either way. No run: three runs and 14 km is this week's cap, and you already hit it.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
@@ -4852,46 +4852,48 @@
       <c r="O88" s="13" t="n"/>
       <c r="P88" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
           <t>build1</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Walk + mobility</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30–32 min</t>
         </is>
       </c>
       <c r="H89" s="8" t="n"/>
-      <c r="I89" s="9" t="n"/>
+      <c r="I89" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="11" t="n"/>
       <c r="L89" s="12" t="n"/>
@@ -4900,7 +4902,7 @@
       <c r="O89" s="13" t="n"/>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>Easy 30–40 min walk plus mobility and foot intrinsics. Deliberately not a run — three runs and 14 km is the cap this week, and you already hit it.</t>
+          <t>Last full New York morning.</t>
         </is>
       </c>
     </row>
@@ -4923,25 +4925,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Bands + bodyweight circuit</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>30–32 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H90" s="8" t="n"/>
-      <c r="I90" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I90" s="9" t="n"/>
       <c r="J90" s="10" t="n"/>
       <c r="K90" s="11" t="n"/>
       <c r="L90" s="12" t="n"/>
@@ -4950,19 +4950,19 @@
       <c r="O90" s="13" t="n"/>
       <c r="P90" s="7" t="inlineStr">
         <is>
-          <t>Last full New York morning.</t>
+          <t>Travel circuit A again, 3 rounds — same as last Monday. Travel strength is about frequency, not load.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
@@ -4973,19 +4973,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E91" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Bands + bodyweight circuit</t>
+          <t>Travel mobility</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H91" s="8" t="n"/>
@@ -4998,19 +4998,19 @@
       <c r="O91" s="13" t="n"/>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>Same circuit as last Thursday, 3 rounds. Travel strength is about frequency, not load.</t>
+          <t>Travel day — mobility only, no run. Calf raises in the terminal, ankle circles on the plane. This is a planned down week: 3 runs and 12 km total.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
@@ -5021,22 +5021,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility</t>
+          <t>Swim — easy re-entry</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H92" s="8" t="n"/>
+          <t>1,800 yd · 40–53 min</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>1800</v>
+      </c>
       <c r="I92" s="9" t="n"/>
       <c r="J92" s="10" t="n"/>
       <c r="K92" s="11" t="n"/>
@@ -5046,7 +5048,7 @@
       <c r="O92" s="13" t="n"/>
       <c r="P92" s="7" t="inlineStr">
         <is>
-          <t>Travel day — mobility only, no run. Calf raises in the terminal, ankle circles on the plane. This is a planned down week: 3 runs and 12 km total.</t>
+          <t>Warm-up 300. Drill 500 as 10 × 50, each drill twice: 6-1-6 / breaststroke timing / front scull / single-arm / closed-fist — rebuild the feel before asking for pace. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. Main 8 × 100 on 2:30 aerobic. Cool-down 200. NO PADDLES this week; five days out of the water means the shoulders get eased back in.</t>
         </is>
       </c>
     </row>
@@ -5069,24 +5071,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Swim — easy re-entry</t>
+          <t>Easy spin</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>1,800 yd · 40–53 min</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="n">
-        <v>1800</v>
-      </c>
+          <t>40 min</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="n"/>
       <c r="I93" s="9" t="n"/>
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="11" t="n"/>
@@ -5096,7 +5096,7 @@
       <c r="O93" s="13" t="n"/>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 500 as 10 × 50, each drill twice: 6-1-6 / breaststroke timing / front scull / single-arm / closed-fist — rebuild the feel before asking for pace. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. Main 8 × 100 on 2:30 aerobic. Cool-down 200. NO PADDLES this week; six days out of the water means the shoulders get eased back in.</t>
+          <t>Zone 2, legs turning over after travel.</t>
         </is>
       </c>
     </row>
@@ -5119,19 +5119,19 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Easy spin</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H94" s="8" t="n"/>
@@ -5144,19 +5144,19 @@
       <c r="O94" s="13" t="n"/>
       <c r="P94" s="7" t="inlineStr">
         <is>
-          <t>Zone 2, legs turning over after travel.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
@@ -5167,22 +5167,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — technique + threshold</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="n"/>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>2400</v>
+      </c>
       <c r="I95" s="9" t="n"/>
       <c r="J95" s="10" t="n"/>
       <c r="K95" s="11" t="n"/>
@@ -5192,7 +5194,7 @@
       <c r="O95" s="13" t="n"/>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Warm-up 300. Drill 500 as 10 × 50, each drill twice: catch-up / 6-1-6 / 3/5/3 breathing / left-breathing single-arm / breathe-3. Fins throughout; snorkel off for everything except catch-up. This is the ladder's graduation test — five weeks after the left side sank in the Oct 2 long swim, breathe-3 reappears, but only as a 50 with rest on either end. The question to answer honestly: do the hips stay up for a full 50? If yes, the ladder worked and Week 10 puts it back inside continuous swimming. If no, drop back to left-breathing single-arm and there is no cost to doing so. Main 12 × 50 on 1:15 aerobic, every third one fast. Then 6 × 100 at CSS on 2:15 — this is the week's threshold work, moved here off the old Friday slot so the weekend stays free. Then 4 × 50 breaststroke. Cool-down 200.</t>
         </is>
       </c>
     </row>
@@ -5215,24 +5217,22 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Swim — technique + threshold</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H96" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>40–45 min</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="n"/>
       <c r="I96" s="9" t="n"/>
       <c r="J96" s="10" t="n"/>
       <c r="K96" s="11" t="n"/>
@@ -5242,19 +5242,19 @@
       <c r="O96" s="13" t="n"/>
       <c r="P96" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 500 as 10 × 50, each drill twice: catch-up / 6-1-6 / 3/5/3 breathing / left-breathing single-arm / breathe-3. Fins throughout; snorkel off for everything except catch-up. This is the ladder's graduation test — five weeks after the left side sank in the Oct 2 long swim, breathe-3 reappears, but only as a 50 with rest on either end. The question to answer honestly: do the hips stay up for a full 50? If yes, the ladder worked and Week 10 puts it back inside continuous swimming. If no, drop back to left-breathing single-arm and there is no cost to doing so. Main 12 × 50 on 1:15 aerobic, every third one fast. Then 6 × 100 at CSS on 2:15 — this is the week's threshold work, moved here off the old Friday slot so the weekend stays free. Then 4 × 50 breaststroke. Cool-down 200.</t>
+          <t>First full-gym lift since New York. Back the loads off about 10% on the RDL and pull-ups — a week of travel strength is not the same stimulus — and build back from there.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
@@ -5265,22 +5265,24 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E97" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Swim — long aerobic 1,400</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="n"/>
+          <t>2,800 yd · 62–82 min</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="I97" s="9" t="n"/>
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="11" t="n"/>
@@ -5290,7 +5292,7 @@
       <c r="O97" s="13" t="n"/>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>First proper lift in a week. Back the loads off about 10% — you have been doing bands.</t>
+          <t>Warm-up 400. Main: 1,400 continuous, then 6 × 100 at CSS on 2:20. Cool-down 400. Third swim in three days and the biggest of the week — it sits on Friday now rather than Saturday, so the weekend is yours. If the shoulders are heavy, drop the 6 × 100 rather than the continuous swim.</t>
         </is>
       </c>
     </row>
@@ -5313,25 +5315,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,400</t>
+          <t>Easy run — 3 km</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2,800 yd · 62–82 min</t>
-        </is>
-      </c>
-      <c r="H98" s="8" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I98" s="9" t="n"/>
+          <t>22–25 min</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="J98" s="10" t="n"/>
       <c r="K98" s="11" t="n"/>
       <c r="L98" s="12" t="n"/>
@@ -5340,19 +5342,19 @@
       <c r="O98" s="13" t="n"/>
       <c r="P98" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Main: 1,400 continuous, then 6 × 100 at CSS on 2:20. Cool-down 400. Third swim in three days and the biggest of the week — it sits on Friday now rather than Saturday, so the weekend is yours. If the shoulders are heavy, drop the 6 × 100 rather than the continuous swim.</t>
+          <t>Down-week running. Deliberately short.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
@@ -5363,25 +5365,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 3 km</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>22–25 min</t>
+          <t>1.5–2.5 hr</t>
         </is>
       </c>
       <c r="H99" s="8" t="n"/>
-      <c r="I99" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="I99" s="9" t="n"/>
       <c r="J99" s="10" t="n"/>
       <c r="K99" s="11" t="n"/>
       <c r="L99" s="12" t="n"/>
@@ -5390,19 +5390,19 @@
       <c r="O99" s="13" t="n"/>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>Down-week running. Deliberately short.</t>
+          <t>First free weekend after the trip — ride, hike or ski, all easy. It is the week's second ride either way. Down week, so keep it conversational.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
@@ -5413,23 +5413,25 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E100" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Endurance ride</t>
+          <t>Long run — 5 km</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>75 min</t>
+          <t>34–38 min</t>
         </is>
       </c>
       <c r="H100" s="8" t="n"/>
-      <c r="I100" s="9" t="n"/>
+      <c r="I100" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J100" s="10" t="n"/>
       <c r="K100" s="11" t="n"/>
       <c r="L100" s="12" t="n"/>
@@ -5438,7 +5440,7 @@
       <c r="O100" s="13" t="n"/>
       <c r="P100" s="7" t="inlineStr">
         <is>
-          <t>Z2, indoors or out depending on weather. Winter is arriving; start getting comfortable on the spin bike.</t>
+          <t>Easy long run to close a down week. Soft surface. Sunday by default, Saturday if the flex slot wants Sunday. Next week the long run steps up to race distance.</t>
         </is>
       </c>
     </row>
@@ -5461,25 +5463,23 @@
           <t>build1</t>
         </is>
       </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Long run — 5 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>34–38 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H101" s="8" t="n"/>
-      <c r="I101" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I101" s="9" t="n"/>
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="11" t="n"/>
       <c r="L101" s="12" t="n"/>
@@ -5488,45 +5488,47 @@
       <c r="O101" s="13" t="n"/>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>Easy long run to close a down week. Soft surface. Next week the long run steps up to race distance.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>build1</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+          <t>build2</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Swim — CSS RETEST (400 + 200 TT)</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H102" s="8" t="n"/>
+          <t>1,600 yd · 36–47 min</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>1600</v>
+      </c>
       <c r="I102" s="9" t="n"/>
       <c r="J102" s="10" t="n"/>
       <c r="K102" s="11" t="n"/>
@@ -5536,42 +5538,42 @@
       <c r="O102" s="13" t="n"/>
       <c r="P102" s="7" t="inlineStr">
         <is>
-          <t>Upper day, and the first one since New York. After two weeks of bands your pressing strength will feel low — start conservative and rebuild. Nothing here touches the legs, so it sits safely on the same day as the long run.</t>
+          <t>Same protocol as Week 1. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. Recalculate CSS and reset every send-off in the second half of the block. Seven weeks of threshold work should show up here — 4–6 s/100 faster is a good outcome, which from the Week 1 baseline of 1:53 means landing between 1:49 and 1:47. CSS is hypersensitive to the 400: hold the 200 at 3:20, take eight seconds off the 400, and you are already at 1:49. Run it identically to Week 1 or the comparison means nothing, and give both efforts everything — an easy 200 flatters the number.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>build1</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>build2</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H103" s="8" t="n"/>
@@ -5584,19 +5586,19 @@
       <c r="O103" s="13" t="n"/>
       <c r="P103" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics.</t>
+          <t>Full body A on retest day — swim first, lift after, and the order matters: the CSS number is the one that cannot be redone.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
@@ -5607,25 +5609,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Swim — CSS RETEST (400 + 200 TT)</t>
+          <t>Easy run — 3 km</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>1,600 yd · 36–47 min</t>
-        </is>
-      </c>
-      <c r="H104" s="8" t="n">
-        <v>1600</v>
-      </c>
-      <c r="I104" s="9" t="n"/>
+          <t>22–25 min</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="J104" s="10" t="n"/>
       <c r="K104" s="11" t="n"/>
       <c r="L104" s="12" t="n"/>
@@ -5634,19 +5636,19 @@
       <c r="O104" s="13" t="n"/>
       <c r="P104" s="7" t="inlineStr">
         <is>
-          <t>Same protocol as Week 1. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. Recalculate CSS and reset every send-off in the second half of the block. Seven weeks of threshold work should show up here — 4–6 s/100 faster is a good outcome, which from the Week 1 baseline of 1:53 means landing between 1:49 and 1:47. CSS is hypersensitive to the 400: hold the 200 at 3:20, take eight seconds off the 400, and you are already at 1:49. Run it identically to Week 1 or the comparison means nothing, and give both efforts everything — an easy 200 flatters the number.</t>
+          <t>Easy. The long run is this weekend and it is the big one this week.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
@@ -5657,22 +5659,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E105" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="n"/>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="I105" s="9" t="n"/>
       <c r="J105" s="10" t="n"/>
       <c r="K105" s="11" t="n"/>
@@ -5682,7 +5686,7 @@
       <c r="O105" s="13" t="n"/>
       <c r="P105" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
@@ -5705,25 +5709,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 3 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>22–25 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H106" s="8" t="n"/>
-      <c r="I106" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="I106" s="9" t="n"/>
       <c r="J106" s="10" t="n"/>
       <c r="K106" s="11" t="n"/>
       <c r="L106" s="12" t="n"/>
@@ -5732,19 +5734,19 @@
       <c r="O106" s="13" t="n"/>
       <c r="P106" s="7" t="inlineStr">
         <is>
-          <t>Easy. The long run is Sunday and it is the big one this week.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
@@ -5762,16 +5764,16 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Swim — speed 6 × (4 × 50)</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
+          <t>2,300 yd · 51–68 min</t>
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="I107" s="9" t="n"/>
       <c r="J107" s="10" t="n"/>
@@ -5782,19 +5784,19 @@
       <c r="O107" s="13" t="n"/>
       <c r="P107" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Paddles 400 pull. Main: 6 rounds of 4 × 50 on 1:00, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200. Tighter send-off than Week 5 — this is where density shows up.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
@@ -5805,19 +5807,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — 20 min FTP RETEST</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="H108" s="8" t="n"/>
@@ -5830,19 +5832,19 @@
       <c r="O108" s="13" t="n"/>
       <c r="P108" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Same protocol as Week 2: 15 min warm-up with 3 × 1 min builds, 20 min all-out, 10 min easy. Same Keiser, because the number only compares to itself. Six weeks of sweet spot from a base this low usually returns 5–10%, so 195 W is a good outcome and 205 W a strong one. The one thing to do differently: pace it evenly. Last time you opened at 205 and finished at 180, which is why 186 W was probably a slight underestimate — open at your target instead of at what feels good in minute two, and let the last five minutes be the ones that hurt. Re-cut every bike watt target in the second half of the block off whatever this gives.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
@@ -5853,25 +5855,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 6 × (4 × 50)</t>
+          <t>Quality run — 6 × 1 min (≈5 km)</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="n">
-        <v>2300</v>
-      </c>
-      <c r="I109" s="9" t="n"/>
+          <t>32–35 min</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J109" s="10" t="n"/>
       <c r="K109" s="11" t="n"/>
       <c r="L109" s="12" t="n"/>
@@ -5880,19 +5882,19 @@
       <c r="O109" s="13" t="n"/>
       <c r="P109" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Paddles 400 pull. Main: 6 rounds of 4 × 50 on 1:00, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200. Tighter send-off than Week 5 — this is where density shows up.</t>
+          <t>Warm-up 10 min easy. Then 6 × 1 min at 5k effort with 2 min easy jog between. Cool-down 10 min. Short reps on a track or soft trail — first real intensity of the block, and it stays short on purpose.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
@@ -5903,19 +5905,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — 20 min FTP RETEST</t>
+          <t>Full body B — single-leg + press</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H110" s="8" t="n"/>
@@ -5928,19 +5930,19 @@
       <c r="O110" s="13" t="n"/>
       <c r="P110" s="7" t="inlineStr">
         <is>
-          <t>Same protocol as Week 2: 15 min warm-up with 3 × 1 min builds, 20 min all-out, 10 min easy. Same Keiser, because the number only compares to itself. Six weeks of sweet spot from a base this low usually returns 5–10%, so 195 W is a good outcome and 205 W a strong one. The one thing to do differently: pace it evenly. Last time you opened at 205 and finished at 180, which is why 186 W was probably a slight underestimate — open at your target instead of at what feels good in minute two, and let the last five minutes be the ones that hurt. Re-cut every bike watt target in the second half of the block off whatever this gives.</t>
+          <t>Run first, lift after — the intervals want fresh legs, the lift does not mind tired ones. Friday is a swim day, so there is a clear day before the long run either way it floats.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
@@ -5951,25 +5953,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Quality run — 6 × 1 min (≈5 km)</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>32–35 min</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>3,000 yd · 67–88 min</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I111" s="9" t="n"/>
       <c r="J111" s="10" t="n"/>
       <c r="K111" s="11" t="n"/>
       <c r="L111" s="12" t="n"/>
@@ -5978,19 +5980,19 @@
       <c r="O111" s="13" t="n"/>
       <c r="P111" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 10 min easy. Then 6 × 1 min at 5k effort with 2 min easy jog between. Cool-down 10 min. Short reps on a track or soft trail — first real intensity of the block, and it stays short on purpose.</t>
+          <t>Warm-up 300. Main: 1,800 continuous at the NEW aerobic pace from Monday's retest, then 6 × 100 at the new CSS on the new send-off. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
@@ -6001,19 +6003,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H112" s="8" t="n"/>
@@ -6026,19 +6028,19 @@
       <c r="O112" s="13" t="n"/>
       <c r="P112" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
@@ -6049,24 +6051,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>3,000 yd · 67–88 min</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="n">
-        <v>3000</v>
-      </c>
+          <t>2–3 hr</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n"/>
       <c r="I113" s="9" t="n"/>
       <c r="J113" s="10" t="n"/>
       <c r="K113" s="11" t="n"/>
@@ -6076,19 +6076,19 @@
       <c r="O113" s="13" t="n"/>
       <c r="P113" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous at the NEW aerobic pace from Monday's retest, then 6 × 100 at the new CSS on the new send-off. Cool-down 300.</t>
+          <t>Your pick of ride, hike or ski, and it counts as the week's second ride either way. If it is a hike, carry 20 lb — that is the fortnight's Rainier pack work, done outdoors instead of on the stairmaster. The long run floats: take it today and the flex slot tomorrow if the weather says so.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
@@ -6099,23 +6099,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>50–55 min</t>
         </is>
       </c>
       <c r="H114" s="8" t="n"/>
-      <c r="I114" s="9" t="n"/>
+      <c r="I114" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J114" s="10" t="n"/>
       <c r="K114" s="11" t="n"/>
       <c r="L114" s="12" t="n"/>
@@ -6124,19 +6126,19 @@
       <c r="O114" s="13" t="n"/>
       <c r="P114" s="7" t="inlineStr">
         <is>
-          <t>Pulling day. Rows and pull-downs after a long aerobic swim — the lats are warm, so quality is usually good here. Keep the seated row strict; no torso swing.</t>
+          <t>Race distance for the first time. Easy pace throughout, soft surface, cadence 175–180. Sunday by default, Saturday if the flex slot wants Sunday. If the shins are tight the next morning and still tight 48 hours later, next week's long run gets cut.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
@@ -6159,7 +6161,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H115" s="8" t="n"/>
@@ -6172,45 +6174,47 @@
       <c r="O115" s="13" t="n"/>
       <c r="P115" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Thorough post-long-run mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Stairmaster + 20 lb pack</t>
+          <t>Swim — threshold 6 × 200</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>45–50 min</t>
-        </is>
-      </c>
-      <c r="H116" s="8" t="n"/>
+          <t>2,300 yd · 51–68 min</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I116" s="9" t="n"/>
       <c r="J116" s="10" t="n"/>
       <c r="K116" s="11" t="n"/>
@@ -6220,42 +6224,42 @@
       <c r="O116" s="13" t="n"/>
       <c r="P116" s="7" t="inlineStr">
         <is>
-          <t>Biweekly Rainier maintenance, now at 20 lb.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 6 × 200 at the new CSS on 4:25 (adjust to the retest). Cool-down 300. 1,200 yd of threshold — the biggest threshold block of the block.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H117" s="8" t="n"/>
@@ -6268,23 +6272,23 @@
       <c r="O117" s="13" t="n"/>
       <c r="P117" s="7" t="inlineStr">
         <is>
-          <t>Second ride of the week, easy Z2 at 130–145 bpm. Off Tuesday now — it was sitting the day before the FTP retest, which is the one place an easy ride is not free. Pure aerobic volume, not a workout, so swap it for an outdoor ride with your partner if the weather allows.</t>
+          <t>Full body A. This is a big week; if you are flat, cut a set rather than skipping.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
@@ -6298,17 +6302,17 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Easy run — 3 km</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>50–55 min</t>
+          <t>22–25 min</t>
         </is>
       </c>
       <c r="H118" s="8" t="n"/>
       <c r="I118" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J118" s="10" t="n"/>
       <c r="K118" s="11" t="n"/>
@@ -6318,45 +6322,47 @@
       <c r="O118" s="13" t="n"/>
       <c r="P118" s="7" t="inlineStr">
         <is>
-          <t>Race distance for the first time. Easy pace throughout, soft surface, cadence 175–180. If the shins are tight the next morning and still tight 48 hours later, next week's long run gets cut.</t>
+          <t>Easy. Save it for the weekend.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="n"/>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="I119" s="9" t="n"/>
       <c r="J119" s="10" t="n"/>
       <c r="K119" s="11" t="n"/>
@@ -6366,19 +6372,19 @@
       <c r="O119" s="13" t="n"/>
       <c r="P119" s="7" t="inlineStr">
         <is>
-          <t>Thorough post-long-run mobility plus foot intrinsics.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
@@ -6389,24 +6395,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 6 × 200</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="n">
-        <v>2300</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="n"/>
       <c r="I120" s="9" t="n"/>
       <c r="J120" s="10" t="n"/>
       <c r="K120" s="11" t="n"/>
@@ -6416,19 +6420,19 @@
       <c r="O120" s="13" t="n"/>
       <c r="P120" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 6 × 200 at the new CSS on 4:25 (adjust to the retest). Cool-down 300. 1,200 yd of threshold — the biggest threshold block of the block.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
@@ -6439,22 +6443,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E121" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Swim — speed 30 × 50</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="n"/>
+          <t>2,600 yd · 58–76 min</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>2600</v>
+      </c>
       <c r="I121" s="9" t="n"/>
       <c r="J121" s="10" t="n"/>
       <c r="K121" s="11" t="n"/>
@@ -6464,19 +6470,19 @@
       <c r="O121" s="13" t="n"/>
       <c r="P121" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A. This is a big week; if you are flat, cut a set rather than skipping.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Paddles 400. Main: 30 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200. Long 50s set — the goal is that number 30 looks like number 1.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
@@ -6487,25 +6493,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E122" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 3 km</t>
+          <t>Spin bike — sweet spot 4 × 12 min</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>22–25 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="H122" s="8" t="n"/>
-      <c r="I122" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="I122" s="9" t="n"/>
       <c r="J122" s="10" t="n"/>
       <c r="K122" s="11" t="n"/>
       <c r="L122" s="12" t="n"/>
@@ -6514,19 +6518,19 @@
       <c r="O122" s="13" t="n"/>
       <c r="P122" s="7" t="inlineStr">
         <is>
-          <t>Easy. Save it for Sunday.</t>
+          <t>4 × 12 min at the NEW sweet-spot watts from Wednesday's retest, 4 min easy. Long sweet-spot blocks are the most useful 70.3 preparation you can do indoors.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
@@ -6537,25 +6541,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E123" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Quality run — 4 × 3 min (≈5 km)</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I123" s="9" t="n"/>
+          <t>35 min</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J123" s="10" t="n"/>
       <c r="K123" s="11" t="n"/>
       <c r="L123" s="12" t="n"/>
@@ -6564,19 +6568,19 @@
       <c r="O123" s="13" t="n"/>
       <c r="P123" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Warm-up 10 min. Then 4 × 3 min at 5-mile race effort (roughly 4:55–5:10/km) with 2 min easy between. Cool-down 10 min. First taste of race pace.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
@@ -6587,19 +6591,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Full body B — single-leg + press</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H124" s="8" t="n"/>
@@ -6612,19 +6616,19 @@
       <c r="O124" s="13" t="n"/>
       <c r="P124" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Full body B, after the run. Peak week — hold the loads where they were rather than chasing a PR, so the 10 km long run gets the legs.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
@@ -6642,16 +6646,16 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 30 × 50</t>
+          <t>Swim — long aerobic 2,000</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>2,600 yd · 58–76 min</t>
+          <t>3,200 yd · 71–94 min</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="I125" s="9" t="n"/>
       <c r="J125" s="10" t="n"/>
@@ -6662,19 +6666,19 @@
       <c r="O125" s="13" t="n"/>
       <c r="P125" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Paddles 400. Main: 30 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200. Long 50s set — the goal is that number 30 looks like number 1.</t>
+          <t>Warm-up 300. Main: 2,000 continuous, then 6 × 100 at CSS. Cool-down 300. Two thousand yards without stopping. Compare the HR drift to the Week 1 1,000 — this is the headline number for whether the plateau broke.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
@@ -6685,19 +6689,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E126" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — sweet spot 4 × 12 min</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H126" s="8" t="n"/>
@@ -6710,19 +6714,19 @@
       <c r="O126" s="13" t="n"/>
       <c r="P126" s="7" t="inlineStr">
         <is>
-          <t>4 × 12 min at the NEW sweet-spot watts from Wednesday's retest, 4 min easy. Long sweet-spot blocks are the most useful 70.3 preparation you can do indoors.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
@@ -6733,25 +6737,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E127" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Quality run — 4 × 3 min (≈5 km)</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2–3 hr</t>
         </is>
       </c>
       <c r="H127" s="8" t="n"/>
-      <c r="I127" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I127" s="9" t="n"/>
       <c r="J127" s="10" t="n"/>
       <c r="K127" s="11" t="n"/>
       <c r="L127" s="12" t="n"/>
@@ -6760,19 +6762,19 @@
       <c r="O127" s="13" t="n"/>
       <c r="P127" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 10 min. Then 4 × 3 min at 5-mile race effort (roughly 4:55–5:10/km) with 2 min easy between. Cool-down 10 min. First taste of race pace.</t>
+          <t>Ride, hike or ski — keep it aerobic. Big week, so err easy and short, and if the long run is today, the flex slot moves to Sunday.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
@@ -6783,23 +6785,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E128" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Long run — 10 km</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>62–68 min</t>
         </is>
       </c>
       <c r="H128" s="8" t="n"/>
-      <c r="I128" s="9" t="n"/>
+      <c r="I128" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="J128" s="10" t="n"/>
       <c r="K128" s="11" t="n"/>
       <c r="L128" s="12" t="n"/>
@@ -6808,19 +6812,19 @@
       <c r="O128" s="13" t="n"/>
       <c r="P128" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Peak long run, comfortably over race distance. Easy pace, soft surface. This is the run that makes Dec 5 feel short — and the last long one before the race.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
@@ -6831,24 +6835,22 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 2,000</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>3,200 yd · 71–94 min</t>
-        </is>
-      </c>
-      <c r="H129" s="8" t="n">
-        <v>3200</v>
-      </c>
+          <t>25 min</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="n"/>
       <c r="I129" s="9" t="n"/>
       <c r="J129" s="10" t="n"/>
       <c r="K129" s="11" t="n"/>
@@ -6858,45 +6860,47 @@
       <c r="O129" s="13" t="n"/>
       <c r="P129" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 2,000 continuous, then 6 × 100 at CSS. Cool-down 300. Two thousand yards without stopping. Compare the HR drift to the Week 1 1,000 — this is the headline number for whether the plateau broke.</t>
+          <t>Full mobility. Pack for Edmonton.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E130" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Swim — threshold 3 × 400</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H130" s="8" t="n"/>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="n">
+        <v>2400</v>
+      </c>
       <c r="I130" s="9" t="n"/>
       <c r="J130" s="10" t="n"/>
       <c r="K130" s="11" t="n"/>
@@ -6906,42 +6910,42 @@
       <c r="O130" s="13" t="n"/>
       <c r="P130" s="7" t="inlineStr">
         <is>
-          <t>Upper day in the peak week. Everything else this week is loaded, so hold the loads where they were rather than chasing a PR — the point is to keep the pressing pattern alive, not to add fatigue before a 10 km long run on Sunday.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 3 × 400 at CSS on 8:45. Cool-down 400. Longest threshold reps of the block — essentially a rehearsal for the 70.3 swim distance, broken.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H131" s="8" t="n"/>
@@ -6954,46 +6958,48 @@
       <c r="O131" s="13" t="n"/>
       <c r="P131" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Full body A, last lift in your home gym before Edmonton.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E132" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Weekend aerobic — ride or hike</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>2.5–3 hr</t>
+          <t>28–30 min</t>
         </is>
       </c>
       <c r="H132" s="8" t="n"/>
-      <c r="I132" s="9" t="n"/>
+      <c r="I132" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J132" s="10" t="n"/>
       <c r="K132" s="11" t="n"/>
       <c r="L132" s="12" t="n"/>
@@ -7002,48 +7008,48 @@
       <c r="O132" s="13" t="n"/>
       <c r="P132" s="7" t="inlineStr">
         <is>
-          <t>Keep it aerobic. Big week, so err easy.</t>
+          <t>Last Seattle run before the flight. Soft surface.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E133" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Long run — 10 km</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>62–68 min</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="n"/>
-      <c r="I133" s="9" t="n">
-        <v>10</v>
-      </c>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I133" s="9" t="n"/>
       <c r="J133" s="10" t="n"/>
       <c r="K133" s="11" t="n"/>
       <c r="L133" s="12" t="n"/>
@@ -7052,23 +7058,23 @@
       <c r="O133" s="13" t="n"/>
       <c r="P133" s="7" t="inlineStr">
         <is>
-          <t>Peak long run, comfortably over race distance. Easy pace, soft surface. This is the run that makes Dec 5 feel short — and the last long one before the race.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
@@ -7087,7 +7093,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H134" s="8" t="n"/>
@@ -7100,19 +7106,19 @@
       <c r="O134" s="13" t="n"/>
       <c r="P134" s="7" t="inlineStr">
         <is>
-          <t>Full mobility. Pack for Edmonton.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
@@ -7130,16 +7136,16 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 3 × 400</t>
+          <t>Swim — speed (Edmonton)</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
+          <t>2,100 yd · 47–62 min</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="I135" s="9" t="n"/>
       <c r="J135" s="10" t="n"/>
@@ -7150,19 +7156,19 @@
       <c r="O135" s="13" t="n"/>
       <c r="P135" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 3 × 400 at CSS on 8:45. Cool-down 400. Longest threshold reps of the block — essentially a rehearsal for the 70.3 swim distance, broken.</t>
+          <t>Travel day. Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 200. Fit it around the flight — same gym, so no adaptation needed.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
@@ -7173,19 +7179,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E136" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H136" s="8" t="n"/>
@@ -7198,19 +7204,19 @@
       <c r="O136" s="13" t="n"/>
       <c r="P136" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>Travel mobility.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
@@ -7221,25 +7227,23 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E137" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Spin bike — Z2</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>28–30 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H137" s="8" t="n"/>
-      <c r="I137" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I137" s="9" t="n"/>
       <c r="J137" s="10" t="n"/>
       <c r="K137" s="11" t="n"/>
       <c r="L137" s="12" t="n"/>
@@ -7248,19 +7252,19 @@
       <c r="O137" s="13" t="n"/>
       <c r="P137" s="7" t="inlineStr">
         <is>
-          <t>Last Seattle run before the flight. Soft surface.</t>
+          <t>Second ride of the week, easy. Edmonton is icy in late November, so all riding this week is indoors. Forty minutes at 130–145 bpm is enough to hold the aerobic base.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
@@ -7271,25 +7275,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E138" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I138" s="9" t="n"/>
+          <t>28–30 min</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J138" s="10" t="n"/>
       <c r="K138" s="11" t="n"/>
       <c r="L138" s="12" t="n"/>
@@ -7298,19 +7302,19 @@
       <c r="O138" s="13" t="n"/>
       <c r="P138" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Indoor track or treadmill. Edmonton in late November is icy and dark — this is the week to accept the treadmill rather than risk a fall.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
@@ -7321,19 +7325,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Full body B — single-leg + press</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H139" s="8" t="n"/>
@@ -7346,19 +7350,19 @@
       <c r="O139" s="13" t="n"/>
       <c r="P139" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Full body B in the Edmonton gym. Same equipment, so nothing needs substituting — find the Smith machine and the box before you start.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
@@ -7376,16 +7380,16 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed (Edmonton)</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2,100 yd · 47–62 min</t>
+          <t>3,000 yd · 67–88 min</t>
         </is>
       </c>
       <c r="H140" s="8" t="n">
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="I140" s="9" t="n"/>
       <c r="J140" s="10" t="n"/>
@@ -7396,19 +7400,19 @@
       <c r="O140" s="13" t="n"/>
       <c r="P140" s="7" t="inlineStr">
         <is>
-          <t>Travel day. Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 200. Fit it around the flight — same gym, so no adaptation needed.</t>
+          <t>Warm-up 300. Main: 1,800 continuous, then 6 × 100 at CSS. Cool-down 300. Left breathing returns to continuous swimming here, eight weeks after Oct 2 and only if the Week 7 graduation test went well — one 25 breathing left at the start of every 300, and nothing more. Twenty-five yards is short enough that you can bail onto your right side before anything sinks, which is the whole reason the dose is that small. If the hips drop even once, stop doing it for the rest of the swim and keep it in drills a while longer; the 1,800 is the session and the breathing is a passenger.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
@@ -7419,19 +7423,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — Z2</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="H141" s="8" t="n"/>
@@ -7444,19 +7448,19 @@
       <c r="O141" s="13" t="n"/>
       <c r="P141" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility.</t>
+          <t>Easy aerobic hour on the spin bike.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
@@ -7467,19 +7471,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E142" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1.5–2.5 hr</t>
         </is>
       </c>
       <c r="H142" s="8" t="n"/>
@@ -7492,19 +7496,19 @@
       <c r="O142" s="13" t="n"/>
       <c r="P142" s="7" t="inlineStr">
         <is>
-          <t>Second ride of the week, easy. Edmonton is icy in late November, so all riding this week is indoors. Forty minutes at 130–145 bpm is enough to hold the aerobic base.</t>
+          <t>Edmonton edition: a cross-country ski if there is snow, a long winter walk with 20 lb in the pack (the fortnight's Rainier work), or a long indoor spin if it is brutal out. Counts as a ride either way.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
@@ -7522,17 +7526,17 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Long run — 7 km</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>28–30 min</t>
+          <t>45–50 min</t>
         </is>
       </c>
       <c r="H143" s="8" t="n"/>
       <c r="I143" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J143" s="10" t="n"/>
       <c r="K143" s="11" t="n"/>
@@ -7542,19 +7546,19 @@
       <c r="O143" s="13" t="n"/>
       <c r="P143" s="7" t="inlineStr">
         <is>
-          <t>Indoor track or treadmill. Edmonton in late November is icy and dark — this is the week to accept the treadmill rather than risk a fall.</t>
+          <t>Down-week long run, shorter than last week on purpose. Indoor track if the footing is bad. Floats to Saturday if the flex slot wants Sunday.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
@@ -7565,19 +7569,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E144" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H144" s="8" t="n"/>
@@ -7590,23 +7594,23 @@
       <c r="O144" s="13" t="n"/>
       <c r="P144" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
@@ -7620,16 +7624,16 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Swim — threshold 10 × 100 (Edmonton)</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>3,000 yd · 67–88 min</t>
+          <t>2,000 yd · 44–59 min</t>
         </is>
       </c>
       <c r="H145" s="8" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I145" s="9" t="n"/>
       <c r="J145" s="10" t="n"/>
@@ -7640,42 +7644,42 @@
       <c r="O145" s="13" t="n"/>
       <c r="P145" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous, then 6 × 100 at CSS. Cool-down 300. Left breathing returns to continuous swimming here, eight weeks after Oct 2 and only if the Week 7 graduation test went well — one 25 breathing left at the start of every 300, and nothing more. Twenty-five yards is short enough that you can bail onto your right side before anything sinks, which is the whole reason the dose is that small. If the hips drop even once, stop doing it for the rest of the swim and keep it in drills a while longer; the 1,800 is the session and the breathing is a passenger.</t>
+          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 10 × 100 at CSS on 2:10 — the tightest send-off yet. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E146" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H146" s="8" t="n"/>
@@ -7688,46 +7692,48 @@
       <c r="O146" s="13" t="n"/>
       <c r="P146" s="7" t="inlineStr">
         <is>
-          <t>Easy aerobic hour on the spin bike.</t>
+          <t>The only lift of race week, and a full one. Normal loads — a 5 mile race does not need a strength taper, it just needs Monday to be the last time the legs are loaded.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Stairmaster + 20 lb pack</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H147" s="8" t="n"/>
-      <c r="I147" s="9" t="n"/>
+      <c r="I147" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J147" s="10" t="n"/>
       <c r="K147" s="11" t="n"/>
       <c r="L147" s="12" t="n"/>
@@ -7736,42 +7742,42 @@
       <c r="O147" s="13" t="n"/>
       <c r="P147" s="7" t="inlineStr">
         <is>
-          <t>Biweekly Rainier maintenance.</t>
+          <t>Travel day back to Seattle. Easy shakeout, whenever it fits.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E148" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H148" s="8" t="n"/>
@@ -7784,48 +7790,48 @@
       <c r="O148" s="13" t="n"/>
       <c r="P148" s="7" t="inlineStr">
         <is>
-          <t>Upper day, in the Edmonton gym. Every weekday this week is already at the two-session cap, so the pressing day lands here — it is the one strength session that does nothing to the legs, which is what makes it safe the day before a 7 km long run.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E149" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Long run — 7 km</t>
+          <t>Swim — speed</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>45–50 min</t>
-        </is>
-      </c>
-      <c r="H149" s="8" t="n"/>
-      <c r="I149" s="9" t="n">
-        <v>7</v>
-      </c>
+          <t>2,000 yd · 44–59 min</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I149" s="9" t="n"/>
       <c r="J149" s="10" t="n"/>
       <c r="K149" s="11" t="n"/>
       <c r="L149" s="12" t="n"/>
@@ -7834,42 +7840,42 @@
       <c r="O149" s="13" t="n"/>
       <c r="P149" s="7" t="inlineStr">
         <is>
-          <t>Down-week long run, shorter than last week on purpose. Indoor track if the footing is bad.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull / 6-1-6. Fins throughout; snorkel off for breaststroke timing and 6-1-6. Main: 16 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
           <t>build2</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Spin bike — easy Z2</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="H150" s="8" t="n"/>
@@ -7882,19 +7888,19 @@
       <c r="O150" s="13" t="n"/>
       <c r="P150" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics.</t>
+          <t>Keep it aerobic this week; no threshold work with a race on Saturday.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
@@ -7905,25 +7911,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E151" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 10 × 100 (Edmonton)</t>
+          <t>Race primer — 4 × 90 s (≈4 km)</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I151" s="9" t="n"/>
+          <t>28 min</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="n"/>
+      <c r="I151" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J151" s="10" t="n"/>
       <c r="K151" s="11" t="n"/>
       <c r="L151" s="12" t="n"/>
@@ -7932,19 +7938,19 @@
       <c r="O151" s="13" t="n"/>
       <c r="P151" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 10 × 100 at CSS on 2:10 — the tightest send-off yet. Cool-down 300.</t>
+          <t>Warm-up 10 min. Then 4 × 90 s at 5-mile race pace with 90 s easy between. Cool-down 8 min. Short, sharp, and well short of fatiguing — this wakes the legs up rather than tiring them.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
@@ -7955,22 +7961,24 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E152" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H152" s="8" t="n"/>
+          <t>1,600 yd · 36–47 min</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="n">
+        <v>1600</v>
+      </c>
       <c r="I152" s="9" t="n"/>
       <c r="J152" s="10" t="n"/>
       <c r="K152" s="11" t="n"/>
@@ -7980,19 +7988,19 @@
       <c r="O152" s="13" t="n"/>
       <c r="P152" s="7" t="inlineStr">
         <is>
-          <t>Last full Strength A before the race. Normal loads — a 5 mile race does not need a strength taper.</t>
+          <t>About 1,600 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
@@ -8003,25 +8011,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E153" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Swim — easy aerobic</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="n"/>
-      <c r="I153" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>1,700 yd · 38–50 min</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I153" s="9" t="n"/>
       <c r="J153" s="10" t="n"/>
       <c r="K153" s="11" t="n"/>
       <c r="L153" s="12" t="n"/>
@@ -8030,19 +8038,19 @@
       <c r="O153" s="13" t="n"/>
       <c r="P153" s="7" t="inlineStr">
         <is>
-          <t>Travel day back to Seattle. Easy shakeout, whenever it fits.</t>
+          <t>Warm-up 300. Main 1,000 easy continuous. 4 × 50 breaststroke. Cool-down 200. Genuinely easy — you race tomorrow.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
@@ -8065,7 +8073,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H154" s="8" t="n"/>
@@ -8078,19 +8086,19 @@
       <c r="O154" s="13" t="n"/>
       <c r="P154" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Mobility and foot intrinsics. Lay out race kit; run in the orthotics you have trained in, not new ones.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
@@ -8101,25 +8109,25 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E155" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed</t>
+          <t>RACE — Redmond Reindeer Romp 5 mile (8 km)</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H155" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I155" s="9" t="n"/>
+          <t>55–65 min</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="n"/>
+      <c r="I155" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J155" s="10" t="n"/>
       <c r="K155" s="11" t="n"/>
       <c r="L155" s="12" t="n"/>
@@ -8128,19 +8136,19 @@
       <c r="O155" s="13" t="n"/>
       <c r="P155" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull / 6-1-6. Fins throughout; snorkel off for breaststroke timing and 6-1-6. Main: 16 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
+          <t>Warm-up 1.5 km easy with 3 strides. Race: go out at 5:10/km for the first mile and let it come down — the classic error here is a first mile 20 s too fast. Target roughly 40–42 min if the shins are quiet; if they are not, run it as a steady effort and enjoy the morning. Cool-down 1 km.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
@@ -8151,19 +8159,19 @@
           <t>build2</t>
         </is>
       </c>
-      <c r="E156" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — easy Z2</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H156" s="8" t="n"/>
@@ -8176,48 +8184,48 @@
       <c r="O156" s="13" t="n"/>
       <c r="P156" s="7" t="inlineStr">
         <is>
-          <t>Keep it aerobic this week; no threshold work with a race on Saturday.</t>
+          <t>Thorough post-race mobility. Calves and shins will be the sorest — be gentle, and do not stretch into compartment pain. The old Sunday recovery swim is gone with the rest of the weekend swims; four swims and about 7,300 yd already clear the streak in a race week, and the day after 8 km is a day the legs want off their feet rather than another session.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E157" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Race primer — 4 × 90 s (≈4 km)</t>
+          <t>Swim — threshold 8 × 150</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>28 min</t>
-        </is>
-      </c>
-      <c r="H157" s="8" t="n"/>
-      <c r="I157" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I157" s="9" t="n"/>
       <c r="J157" s="10" t="n"/>
       <c r="K157" s="11" t="n"/>
       <c r="L157" s="12" t="n"/>
@@ -8226,47 +8234,45 @@
       <c r="O157" s="13" t="n"/>
       <c r="P157" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 10 min. Then 4 × 90 s at 5-mile race pace with 90 s easy between. Cool-down 8 min. Short, sharp, and well short of fatiguing — this wakes the legs up rather than tiring them.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: closed-fist / sighting / breaststroke timing / stroke-count ladder. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 8 × 150 at CSS on 3:20. Cool-down 400. Post-race, so the legs are tired but the shoulders are fine — swimming is the perfect recovery training.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Easy spin</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>1,600 yd · 36–47 min</t>
-        </is>
-      </c>
-      <c r="H158" s="8" t="n">
-        <v>1600</v>
-      </c>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="n"/>
       <c r="I158" s="9" t="n"/>
       <c r="J158" s="10" t="n"/>
       <c r="K158" s="11" t="n"/>
@@ -8276,27 +8282,27 @@
       <c r="O158" s="13" t="n"/>
       <c r="P158" s="7" t="inlineStr">
         <is>
-          <t>About 1,600 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
+          <t>Flush the legs after Saturday. No strength this week's start — let the race settle.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -8306,16 +8312,16 @@
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Swim — easy aerobic</t>
+          <t>Swim — speed + breaststroke</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>1,700 yd · 38–50 min</t>
+          <t>2,000 yd · 44–59 min</t>
         </is>
       </c>
       <c r="H159" s="8" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="I159" s="9" t="n"/>
       <c r="J159" s="10" t="n"/>
@@ -8326,46 +8332,48 @@
       <c r="O159" s="13" t="n"/>
       <c r="P159" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main 1,000 easy continuous. 4 × 50 breaststroke. Cool-down 200. Genuinely easy — you race tomorrow.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: front scull / 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous — the Week 12 checkpoint. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E160" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Chest and shoulders</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>28 min</t>
         </is>
       </c>
       <c r="H160" s="8" t="n"/>
-      <c r="I160" s="9" t="n"/>
+      <c r="I160" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J160" s="10" t="n"/>
       <c r="K160" s="11" t="n"/>
       <c r="L160" s="12" t="n"/>
@@ -8374,45 +8382,47 @@
       <c r="O160" s="13" t="n"/>
       <c r="P160" s="7" t="inlineStr">
         <is>
-          <t>Upper day the day before a race, deliberately. Nothing here loads the legs, so it costs you nothing on Saturday — but skip the last set of everything and leave the gym feeling like you could have done more. If in doubt, skip it entirely; the race matters more than one session.</t>
+          <t>First run back after the race. Easy, short, soft surface.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — long aerobic 1,400</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H161" s="8" t="n"/>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="n">
+        <v>2400</v>
+      </c>
       <c r="I161" s="9" t="n"/>
       <c r="J161" s="10" t="n"/>
       <c r="K161" s="11" t="n"/>
@@ -8422,48 +8432,46 @@
       <c r="O161" s="13" t="n"/>
       <c r="P161" s="7" t="inlineStr">
         <is>
-          <t>Mobility and foot intrinsics. Lay out race kit; run in the orthotics you have trained in, not new ones.</t>
+          <t>Warm-up 300. Main: 1,400 continuous, then 4 × 100 at CSS. Cool-down 300. Morning session — flight is at 4:30 pm. Three swims brings the week to about 6,800 yd, so the streak holds through the trip.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E162" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>RACE — Redmond Reindeer Romp 5 mile (8 km)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>55–65 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H162" s="8" t="n"/>
-      <c r="I162" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I162" s="9" t="n"/>
       <c r="J162" s="10" t="n"/>
       <c r="K162" s="11" t="n"/>
       <c r="L162" s="12" t="n"/>
@@ -8472,46 +8480,48 @@
       <c r="O162" s="13" t="n"/>
       <c r="P162" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 1.5 km easy with 3 strides. Race: go out at 5:10/km for the first mile and let it come down — the classic error here is a first mile 20 s too fast. Target roughly 40–42 min if the shins are quiet; if they are not, run it as a steady effort and enjoy the morning. Cool-down 1 km.</t>
+          <t>Pre-flight mobility.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>build2</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="E163" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="H163" s="8" t="n"/>
-      <c r="I163" s="9" t="n"/>
+      <c r="I163" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J163" s="10" t="n"/>
       <c r="K163" s="11" t="n"/>
       <c r="L163" s="12" t="n"/>
@@ -8520,19 +8530,19 @@
       <c r="O163" s="13" t="n"/>
       <c r="P163" s="7" t="inlineStr">
         <is>
-          <t>Thorough post-race mobility. Calves and shins will be the sorest — be gentle, and do not stretch into compartment pain. The old Sunday recovery swim is gone with the rest of the weekend swims; four swims and about 7,300 yd already clear the streak in a race week, and the day after 8 km is a day the legs want off their feet rather than another session.</t>
+          <t>Orlando, wedding day one. Get it done early — Florida in December is pleasant at 7 am and the day will get away from you. Easy pace.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
@@ -8543,24 +8553,22 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 8 × 150</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H164" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H164" s="8" t="n"/>
       <c r="I164" s="9" t="n"/>
       <c r="J164" s="10" t="n"/>
       <c r="K164" s="11" t="n"/>
@@ -8570,19 +8578,19 @@
       <c r="O164" s="13" t="n"/>
       <c r="P164" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: closed-fist / sighting / breaststroke timing / stroke-count ladder. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 8 × 150 at CSS on 3:20. Cool-down 400. Post-race, so the legs are tired but the shoulders are fine — swimming is the perfect recovery training.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
@@ -8593,19 +8601,19 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E165" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E165" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Easy spin</t>
+          <t>Bands + bodyweight circuit</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>25 min</t>
         </is>
       </c>
       <c r="H165" s="8" t="n"/>
@@ -8618,19 +8626,19 @@
       <c r="O165" s="13" t="n"/>
       <c r="P165" s="7" t="inlineStr">
         <is>
-          <t>Flush the legs after Saturday. No strength this week's start — let the race settle.</t>
+          <t>Orlando, wedding day two. Short bands-and-bodyweight session in the room before the day starts: 2 rounds of banded RDL 15, split squat 10/leg, banded lateral walk 15/side, calf raise 20, tibialis raise 20, dead bug 10/side. Twenty-five minutes, no equipment, and it keeps the lower-leg work unbroken through the one week that would otherwise lose it.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
@@ -8641,24 +8649,22 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed + breaststroke</t>
+          <t>Walk + mobility</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H166" s="8" t="n">
-        <v>2000</v>
-      </c>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="H166" s="8" t="n"/>
       <c r="I166" s="9" t="n"/>
       <c r="J166" s="10" t="n"/>
       <c r="K166" s="11" t="n"/>
@@ -8668,19 +8674,19 @@
       <c r="O166" s="13" t="n"/>
       <c r="P166" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: front scull / 6-1-6 / closed-fist / sighting. Fins throughout; snorkel off for 6-1-6 and sighting. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous — the Week 12 checkpoint. Cool-down 300.</t>
+          <t>Mobility and a walk rather than a run — you ran yesterday and the week's third run is Sunday in Miami. Three runs, 15 km, is the cap for a travel week.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
@@ -8691,25 +8697,23 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E167" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E167" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Hotel gym / bodyweight circuit</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>28 min</t>
+          <t>35–40 min</t>
         </is>
       </c>
       <c r="H167" s="8" t="n"/>
-      <c r="I167" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="I167" s="9" t="n"/>
       <c r="J167" s="10" t="n"/>
       <c r="K167" s="11" t="n"/>
       <c r="L167" s="12" t="n"/>
@@ -8718,19 +8722,19 @@
       <c r="O167" s="13" t="n"/>
       <c r="P167" s="7" t="inlineStr">
         <is>
-          <t>First run back after the race. Easy, short, soft surface.</t>
+          <t>Miami. 3 rounds of split squat 10/leg, banded RDL 15, calf raise 20, tibialis raise 20, Copenhagen plank 20 s/side, dead bug 10/side, plank 45 s. If the hotel gym has weights, swap in RDLs.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
@@ -8741,24 +8745,22 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,400</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H168" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="H168" s="8" t="n"/>
       <c r="I168" s="9" t="n"/>
       <c r="J168" s="10" t="n"/>
       <c r="K168" s="11" t="n"/>
@@ -8768,19 +8770,19 @@
       <c r="O168" s="13" t="n"/>
       <c r="P168" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,400 continuous, then 4 × 100 at CSS. Cool-down 300. Morning session — flight is at 4:30 pm. Three swims brings the week to about 6,800 yd, so the streak holds through the trip.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
@@ -8791,23 +8793,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E169" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Easy run — 6 km</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H169" s="8" t="n"/>
-      <c r="I169" s="9" t="n"/>
+      <c r="I169" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="J169" s="10" t="n"/>
       <c r="K169" s="11" t="n"/>
       <c r="L169" s="12" t="n"/>
@@ -8816,19 +8820,19 @@
       <c r="O169" s="13" t="n"/>
       <c r="P169" s="7" t="inlineStr">
         <is>
-          <t>Pre-flight mobility.</t>
+          <t>Miami. Beach path or boardwalk, easy. If the hotel has a pool worth swimming in, an easy 800–1,000 yd afterwards is a bonus, not a requirement.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
@@ -8839,25 +8843,23 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E170" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H170" s="8" t="n"/>
-      <c r="I170" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I170" s="9" t="n"/>
       <c r="J170" s="10" t="n"/>
       <c r="K170" s="11" t="n"/>
       <c r="L170" s="12" t="n"/>
@@ -8866,45 +8868,47 @@
       <c r="O170" s="13" t="n"/>
       <c r="P170" s="7" t="inlineStr">
         <is>
-          <t>Orlando, wedding day one. Get it done early — Florida in December is pleasant at 7 am and the day will get away from you. Easy pace.</t>
+          <t>Mobility and foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — threshold 5 × 200</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H171" s="8" t="n"/>
+          <t>2,000 yd · 44–59 min</t>
+        </is>
+      </c>
+      <c r="H171" s="8" t="n">
+        <v>2000</v>
+      </c>
       <c r="I171" s="9" t="n"/>
       <c r="J171" s="10" t="n"/>
       <c r="K171" s="11" t="n"/>
@@ -8914,23 +8918,23 @@
       <c r="O171" s="13" t="n"/>
       <c r="P171" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for breaststroke timing. Main: 5 × 200 at CSS on 4:25. Cool-down 300. Back in a pool after four days off — ease into the first 200.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C172" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
@@ -8944,12 +8948,12 @@
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Bands + bodyweight circuit</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H172" s="8" t="n"/>
@@ -8962,46 +8966,48 @@
       <c r="O172" s="13" t="n"/>
       <c r="P172" s="7" t="inlineStr">
         <is>
-          <t>Orlando, wedding day two. Short bands-and-bodyweight session in the room before the day starts: 2 rounds of banded RDL 15, split squat 10/leg, banded lateral walk 15/side, calf raise 20, tibialis raise 20, dead bug 10/side. Twenty-five minutes, no equipment, and it keeps the lower-leg work unbroken through the one week that would otherwise lose it.</t>
+          <t>First full lift since race week. Back the loads off slightly and rebuild.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E173" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Walk + mobility</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="H173" s="8" t="n"/>
-      <c r="I173" s="9" t="n"/>
+      <c r="I173" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J173" s="10" t="n"/>
       <c r="K173" s="11" t="n"/>
       <c r="L173" s="12" t="n"/>
@@ -9010,42 +9016,42 @@
       <c r="O173" s="13" t="n"/>
       <c r="P173" s="7" t="inlineStr">
         <is>
-          <t>Mobility and a walk rather than a run — you ran yesterday and the week's third run is Sunday in Miami. Three runs, 15 km, is the cap for a travel week.</t>
+          <t>North Carolina. Explore — trails if there are any nearby.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C174" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E174" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Hotel gym / bodyweight circuit</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>35–40 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H174" s="8" t="n"/>
@@ -9058,45 +9064,47 @@
       <c r="O174" s="13" t="n"/>
       <c r="P174" s="7" t="inlineStr">
         <is>
-          <t>Miami. 3 rounds of split squat 10/leg, banded RDL 15, calf raise 20, tibialis raise 20, Copenhagen plank 20 s/side, dead bug 10/side, plank 45 s. If the hotel gym has weights, swap in RDLs.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C175" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — speed 20 × 50</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H175" s="8" t="n"/>
+          <t>2,200 yd · 49–65 min</t>
+        </is>
+      </c>
+      <c r="H175" s="8" t="n">
+        <v>2200</v>
+      </c>
       <c r="I175" s="9" t="n"/>
       <c r="J175" s="10" t="n"/>
       <c r="K175" s="11" t="n"/>
@@ -9106,48 +9114,46 @@
       <c r="O175" s="13" t="n"/>
       <c r="P175" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E176" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E176" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 6 km</t>
+          <t>Spin bike — sweet spot 3 × 10 min</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="H176" s="8" t="n"/>
-      <c r="I176" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="I176" s="9" t="n"/>
       <c r="J176" s="10" t="n"/>
       <c r="K176" s="11" t="n"/>
       <c r="L176" s="12" t="n"/>
@@ -9156,46 +9162,48 @@
       <c r="O176" s="13" t="n"/>
       <c r="P176" s="7" t="inlineStr">
         <is>
-          <t>Miami. Beach path or boardwalk, easy. If the hotel has a pool worth swimming in, an easy 800–1,000 yd afterwards is a bonus, not a requirement.</t>
+          <t>3 × 10 min at sweet spot, 4 min easy between.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C177" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E177" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="H177" s="8" t="n"/>
-      <c r="I177" s="9" t="n"/>
+      <c r="I177" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J177" s="10" t="n"/>
       <c r="K177" s="11" t="n"/>
       <c r="L177" s="12" t="n"/>
@@ -9204,19 +9212,19 @@
       <c r="O177" s="13" t="n"/>
       <c r="P177" s="7" t="inlineStr">
         <is>
-          <t>Mobility and foot intrinsics.</t>
+          <t>Travel day home. Morning run before the flight.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
@@ -9234,16 +9242,16 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 5 × 200</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2,000 yd · 44–59 min</t>
+          <t>1,400 yd · 31–41 min</t>
         </is>
       </c>
       <c r="H178" s="8" t="n">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="I178" s="9" t="n"/>
       <c r="J178" s="10" t="n"/>
@@ -9254,19 +9262,19 @@
       <c r="O178" s="13" t="n"/>
       <c r="P178" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 300 as 6 × 50, each drill twice: breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for breaststroke timing. Main: 5 × 200 at CSS on 4:25. Cool-down 300. Back in a pool after four days off — ease into the first 200.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived. This moved off Saturday with the rest of the weekend swims, so it lands on a travel morning — if the flight is early, this is the most droppable session of the week. Let it go rather than rushing it.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C179" s="5" t="n">
@@ -9277,19 +9285,19 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E179" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H179" s="8" t="n"/>
@@ -9302,19 +9310,19 @@
       <c r="O179" s="13" t="n"/>
       <c r="P179" s="7" t="inlineStr">
         <is>
-          <t>First full lift since race week. Back the loads off slightly and rebuild.</t>
+          <t>Travel mobility.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C180" s="5" t="n">
@@ -9325,25 +9333,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E180" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Swim — long aerobic 1,600</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
-        </is>
-      </c>
-      <c r="H180" s="8" t="n"/>
-      <c r="I180" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>2,600 yd · 58–76 min</t>
+        </is>
+      </c>
+      <c r="H180" s="8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I180" s="9" t="n"/>
       <c r="J180" s="10" t="n"/>
       <c r="K180" s="11" t="n"/>
       <c r="L180" s="12" t="n"/>
@@ -9352,19 +9360,19 @@
       <c r="O180" s="13" t="n"/>
       <c r="P180" s="7" t="inlineStr">
         <is>
-          <t>North Carolina. Explore — trails if there are any nearby.</t>
+          <t>Warm-up 300. Main: 1,600 continuous, then 4 × 100 at CSS. Cool-down 300. Home pool.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C181" s="5" t="n">
@@ -9382,12 +9390,12 @@
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Full body B — single-leg + press</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>40–45 min</t>
         </is>
       </c>
       <c r="H181" s="8" t="n"/>
@@ -9400,19 +9408,19 @@
       <c r="O181" s="13" t="n"/>
       <c r="P181" s="7" t="inlineStr">
         <is>
-          <t>Upper day. The North Carolina gym has full equipment, so nothing needs substituting. Pulling pairs well with an easy run and keeps Friday's Strength B on fresh legs.</t>
+          <t>Full body B, back in the home gym. It sits on Friday this week because Thursday is the travel day — so keep the long run on Sunday rather than floating it to Saturday, the day after a leg session.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C182" s="5" t="n">
@@ -9425,17 +9433,17 @@
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>mobility</t>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>2–3 hr</t>
         </is>
       </c>
       <c r="H182" s="8" t="n"/>
@@ -9448,19 +9456,19 @@
       <c r="O182" s="13" t="n"/>
       <c r="P182" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>Winter options: a ride if the roads are dry, a shorter hike with 20 lb, the first ski day of the season if the passes have opened, or a long spin indoors.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C183" s="5" t="n">
@@ -9471,25 +9479,25 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E183" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 20 × 50</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>2,200 yd · 49–65 min</t>
-        </is>
-      </c>
-      <c r="H183" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I183" s="9" t="n"/>
+          <t>50–55 min</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="n"/>
+      <c r="I183" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J183" s="10" t="n"/>
       <c r="K183" s="11" t="n"/>
       <c r="L183" s="12" t="n"/>
@@ -9498,19 +9506,19 @@
       <c r="O183" s="13" t="n"/>
       <c r="P183" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300.</t>
+          <t>Back to race distance, easy. The run base is worth keeping through the holidays rather than rebuilding in January.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C184" s="5" t="n">
@@ -9521,19 +9529,19 @@
           <t>travel</t>
         </is>
       </c>
-      <c r="E184" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — sweet spot 3 × 10 min</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="H184" s="8" t="n"/>
@@ -9546,48 +9554,48 @@
       <c r="O184" s="13" t="n"/>
       <c r="P184" s="7" t="inlineStr">
         <is>
-          <t>3 × 10 min at sweet spot, 4 min easy between.</t>
+          <t>Mobility plus foot intrinsics. Pack for Edmonton.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C185" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E185" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Swim — threshold 4 × 300</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="H185" s="8" t="n"/>
-      <c r="I185" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>2,300 yd · 51–68 min</t>
+        </is>
+      </c>
+      <c r="H185" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I185" s="9" t="n"/>
       <c r="J185" s="10" t="n"/>
       <c r="K185" s="11" t="n"/>
       <c r="L185" s="12" t="n"/>
@@ -9596,47 +9604,45 @@
       <c r="O185" s="13" t="n"/>
       <c r="P185" s="7" t="inlineStr">
         <is>
-          <t>Travel day home. Morning run before the flight.</t>
+          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 4 × 300 at CSS on 6:30 — tighter than Week 5's version of this set. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C186" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E186" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H186" s="8" t="n">
-        <v>1400</v>
-      </c>
+          <t>40–45 min</t>
+        </is>
+      </c>
+      <c r="H186" s="8" t="n"/>
       <c r="I186" s="9" t="n"/>
       <c r="J186" s="10" t="n"/>
       <c r="K186" s="11" t="n"/>
@@ -9646,46 +9652,48 @@
       <c r="O186" s="13" t="n"/>
       <c r="P186" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived. This moved off Saturday with the rest of the weekend swims, so it lands on a travel morning — if the flight is early, this is the most droppable session of the week. Let it go rather than rushing it.</t>
+          <t>Full body A, last lift in the home gym this year.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E187" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E187" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="H187" s="8" t="n"/>
-      <c r="I187" s="9" t="n"/>
+      <c r="I187" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J187" s="10" t="n"/>
       <c r="K187" s="11" t="n"/>
       <c r="L187" s="12" t="n"/>
@@ -9694,27 +9702,27 @@
       <c r="O187" s="13" t="n"/>
       <c r="P187" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility.</t>
+          <t>Last Seattle run of the year. Soft surface.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C188" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>winterbase</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -9724,16 +9732,16 @@
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,600</t>
+          <t>Swim — long aerobic 1,800</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>2,600 yd · 58–76 min</t>
+          <t>2,800 yd · 62–82 min</t>
         </is>
       </c>
       <c r="H188" s="8" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="I188" s="9" t="n"/>
       <c r="J188" s="10" t="n"/>
@@ -9744,46 +9752,48 @@
       <c r="O188" s="13" t="n"/>
       <c r="P188" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,600 continuous, then 4 × 100 at CSS. Cool-down 300. Home pool.</t>
+          <t>Warm-up 300. Main: 1,800 continuous, then 4 × 100 at CSS. Cool-down 300. The week's long swim, pulled off Boxing Day to your home pool on your last Seattle day — you know this water, the lane etiquette and the clock, which is exactly what you want for the longest continuous swim of the week.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E189" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E189" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Easy run — 4 km</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="H189" s="8" t="n"/>
-      <c r="I189" s="9" t="n"/>
+      <c r="I189" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J189" s="10" t="n"/>
       <c r="K189" s="11" t="n"/>
       <c r="L189" s="12" t="n"/>
@@ -9792,45 +9802,47 @@
       <c r="O189" s="13" t="n"/>
       <c r="P189" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength B.</t>
+          <t>Travel day to Edmonton. Indoor track or treadmill given the conditions. CHECK THE GYM'S HOLIDAY HOURS TODAY and shuffle this week's swims to fit them.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C190" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>cardio</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Weekend aerobic — ride, hike, or stairs</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>2–3 hr</t>
-        </is>
-      </c>
-      <c r="H190" s="8" t="n"/>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H190" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="I190" s="9" t="n"/>
       <c r="J190" s="10" t="n"/>
       <c r="K190" s="11" t="n"/>
@@ -9840,48 +9852,46 @@
       <c r="O190" s="13" t="n"/>
       <c r="P190" s="7" t="inlineStr">
         <is>
-          <t>Winter options: spin bike endurance, a shorter hike, or 45 min on the stairmaster with 20 lb.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived. Deliberately the smallest swim of the week on the most disrupted day — fit it around the flight, and if Edmonton's pool hours do not cooperate, this is the one to drop.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E191" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>50–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H191" s="8" t="n"/>
-      <c r="I191" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I191" s="9" t="n"/>
       <c r="J191" s="10" t="n"/>
       <c r="K191" s="11" t="n"/>
       <c r="L191" s="12" t="n"/>
@@ -9890,45 +9900,47 @@
       <c r="O191" s="13" t="n"/>
       <c r="P191" s="7" t="inlineStr">
         <is>
-          <t>Back to race distance, easy. The run base is worth keeping through the holidays rather than rebuilding in January.</t>
+          <t>Travel mobility.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C192" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="E192" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+          <t>winterbase</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — speed</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H192" s="8" t="n"/>
+          <t>2,400 yd · 53–71 min</t>
+        </is>
+      </c>
+      <c r="H192" s="8" t="n">
+        <v>2400</v>
+      </c>
       <c r="I192" s="9" t="n"/>
       <c r="J192" s="10" t="n"/>
       <c r="K192" s="11" t="n"/>
@@ -9938,19 +9950,19 @@
       <c r="O192" s="13" t="n"/>
       <c r="P192" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics. Pack for Edmonton.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 24 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300. Christmas Eve — likely reduced pool hours, so go early.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C193" s="5" t="n">
@@ -9961,24 +9973,22 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E193" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Swim — threshold 4 × 300</t>
+          <t>Full body B — single-leg + press</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>2,300 yd · 51–68 min</t>
-        </is>
-      </c>
-      <c r="H193" s="8" t="n">
-        <v>2300</v>
-      </c>
+          <t>40–45 min</t>
+        </is>
+      </c>
+      <c r="H193" s="8" t="n"/>
       <c r="I193" s="9" t="n"/>
       <c r="J193" s="10" t="n"/>
       <c r="K193" s="11" t="n"/>
@@ -9988,19 +9998,19 @@
       <c r="O193" s="13" t="n"/>
       <c r="P193" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 400. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Main: 4 × 300 at CSS on 6:30 — tighter than Week 5's version of this set. Cool-down 300.</t>
+          <t>Full body B on Christmas Eve, which puts it three clear days before the long run — close the gym out early if you need to, but do not push it later into the week or it lands too close to that run.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C194" s="5" t="n">
@@ -10011,19 +10021,19 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E194" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H194" s="8" t="n"/>
@@ -10036,19 +10046,19 @@
       <c r="O194" s="13" t="n"/>
       <c r="P194" s="7" t="inlineStr">
         <is>
-          <t>Standard Strength A.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C195" s="5" t="n">
@@ -10059,25 +10069,23 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E195" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 5 km</t>
+          <t>Rest day — walk and stretch</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20–30 min</t>
         </is>
       </c>
       <c r="H195" s="8" t="n"/>
-      <c r="I195" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I195" s="9" t="n"/>
       <c r="J195" s="10" t="n"/>
       <c r="K195" s="11" t="n"/>
       <c r="L195" s="12" t="n"/>
@@ -10086,19 +10094,19 @@
       <c r="O195" s="13" t="n"/>
       <c r="P195" s="7" t="inlineStr">
         <is>
-          <t>Last Seattle run of the year. Soft surface.</t>
+          <t>Christmas Day. Rest, stretch, walk if you feel like it. Nothing structured — this is the one fully off day in the block and taking it properly is part of the plan.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C196" s="5" t="n">
@@ -10109,24 +10117,22 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>cardio</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Swim — long aerobic 1,800</t>
+          <t>Weekend flex — ride, hike or ski</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>2,800 yd · 62–82 min</t>
-        </is>
-      </c>
-      <c r="H196" s="8" t="n">
-        <v>2800</v>
-      </c>
+          <t>1.5–2.5 hr</t>
+        </is>
+      </c>
+      <c r="H196" s="8" t="n"/>
       <c r="I196" s="9" t="n"/>
       <c r="J196" s="10" t="n"/>
       <c r="K196" s="11" t="n"/>
@@ -10136,19 +10142,19 @@
       <c r="O196" s="13" t="n"/>
       <c r="P196" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Main: 1,800 continuous, then 4 × 100 at CSS. Cool-down 300. The week's long swim, pulled off Boxing Day to your home pool on your last Seattle day — you know this water, the lane etiquette and the clock, which is exactly what you want for the longest continuous swim of the week.</t>
+          <t>Boxing Day. A cross-country ski or a winter walk with your partner if there is snow and daylight, or a long indoor spin at 130–145 bpm if there is not — Edmonton in late December is not outdoor riding weather. Counts as the week's ride either way.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C197" s="5" t="n">
@@ -10166,17 +10172,17 @@
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Easy run — 4 km</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>50–55 min</t>
         </is>
       </c>
       <c r="H197" s="8" t="n"/>
       <c r="I197" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J197" s="10" t="n"/>
       <c r="K197" s="11" t="n"/>
@@ -10186,19 +10192,19 @@
       <c r="O197" s="13" t="n"/>
       <c r="P197" s="7" t="inlineStr">
         <is>
-          <t>Travel day to Edmonton. Indoor track or treadmill given the conditions. CHECK THE GYM'S HOLIDAY HOURS TODAY and shuffle this week's swims to fit them.</t>
+          <t>Indoor track if the footing is bad, outside if it is clear and you are dressed for it. Floats to Saturday if Sunday is the better day to be out.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C198" s="5" t="n">
@@ -10209,24 +10215,22 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Technique swim (short)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H198" s="8" t="n">
-        <v>1400</v>
-      </c>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="H198" s="8" t="n"/>
       <c r="I198" s="9" t="n"/>
       <c r="J198" s="10" t="n"/>
       <c r="K198" s="11" t="n"/>
@@ -10236,45 +10240,47 @@
       <c r="O198" s="13" t="n"/>
       <c r="P198" s="7" t="inlineStr">
         <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived. Deliberately the smallest swim of the week on the most disrupted day — fit it around the flight, and if Edmonton's pool hours do not cooperate, this is the one to drop.</t>
+          <t>Mobility plus foot intrinsics.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C199" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E199" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — FINAL CSS TEST (400 + 200 TT)</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H199" s="8" t="n"/>
+          <t>1,600 yd · 36–47 min</t>
+        </is>
+      </c>
+      <c r="H199" s="8" t="n">
+        <v>1600</v>
+      </c>
       <c r="I199" s="9" t="n"/>
       <c r="J199" s="10" t="n"/>
       <c r="K199" s="11" t="n"/>
@@ -10284,47 +10290,45 @@
       <c r="O199" s="13" t="n"/>
       <c r="P199" s="7" t="inlineStr">
         <is>
-          <t>Travel mobility.</t>
+          <t>Same protocol as Weeks 1 and 8. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. This is the block's headline number. Compare all three tests side by side — Week 1, Week 8, and today.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C200" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E200" s="14" t="inlineStr">
+        <is>
+          <t>strength</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>2,400 yd · 53–71 min</t>
-        </is>
-      </c>
-      <c r="H200" s="8" t="n">
-        <v>2400</v>
-      </c>
+          <t>40–45 min</t>
+        </is>
+      </c>
+      <c r="H200" s="8" t="n"/>
       <c r="I200" s="9" t="n"/>
       <c r="J200" s="10" t="n"/>
       <c r="K200" s="11" t="n"/>
@@ -10334,46 +10338,48 @@
       <c r="O200" s="13" t="n"/>
       <c r="P200" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: sighting / breaststroke timing / stroke-count ladder / front scull. Fins throughout; snorkel off for sighting and breaststroke timing. Main: 24 × 50 on 1:05 alternating. 4 × 50 breaststroke. Cool-down 300. Christmas Eve — likely reduced pool hours, so go early.</t>
+          <t>Last full-body session of the year. Log the RDL and split squat loads next to the Week 1 numbers.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C201" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E201" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E201" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
+          <t>Easy run — 5 km</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>35–40 min</t>
         </is>
       </c>
       <c r="H201" s="8" t="n"/>
-      <c r="I201" s="9" t="n"/>
+      <c r="I201" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="J201" s="10" t="n"/>
       <c r="K201" s="11" t="n"/>
       <c r="L201" s="12" t="n"/>
@@ -10382,45 +10388,47 @@
       <c r="O201" s="13" t="n"/>
       <c r="P201" s="7" t="inlineStr">
         <is>
-          <t>Leg day on Christmas Eve, which puts it three clear days before Sunday's long run — close the gym out early if you need to, but do not push it later into the week or it lands too close to that run. Standard Strength B: Bulgarian split squats, step-ups, Copenhagen planks.</t>
+          <t>Easy. Indoor track if needed.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C202" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Technique swim (short)</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H202" s="8" t="n"/>
+          <t>1,400 yd · 31–41 min</t>
+        </is>
+      </c>
+      <c r="H202" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="I202" s="9" t="n"/>
       <c r="J202" s="10" t="n"/>
       <c r="K202" s="11" t="n"/>
@@ -10430,23 +10438,23 @@
       <c r="O202" s="13" t="n"/>
       <c r="P202" s="7" t="inlineStr">
         <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
+          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C203" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
@@ -10460,12 +10468,12 @@
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>Rest day — walk and stretch</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>20–30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H203" s="8" t="n"/>
@@ -10478,45 +10486,47 @@
       <c r="O203" s="13" t="n"/>
       <c r="P203" s="7" t="inlineStr">
         <is>
-          <t>Christmas Day. Rest, stretch, walk if you feel like it. Nothing structured — this is the one fully off day in the block and taking it properly is part of the plan.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C204" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E204" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — Z2</t>
+          <t>Swim — speed</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>50 min</t>
-        </is>
-      </c>
-      <c r="H204" s="8" t="n"/>
+          <t>2,000 yd · 44–59 min</t>
+        </is>
+      </c>
+      <c r="H204" s="8" t="n">
+        <v>2000</v>
+      </c>
       <c r="I204" s="9" t="n"/>
       <c r="J204" s="10" t="n"/>
       <c r="K204" s="11" t="n"/>
@@ -10526,42 +10536,42 @@
       <c r="O204" s="13" t="n"/>
       <c r="P204" s="7" t="inlineStr">
         <is>
-          <t>Boxing Day ride, all indoors — Edmonton in late December is not outdoor riding weather. Fifty minutes steady at 130–145 bpm, and an easy one to swap for a ski or a walk with your partner if that is the better use of the morning.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous. Cool-down 300.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C205" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E205" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
+      <c r="E205" s="16" t="inlineStr">
+        <is>
+          <t>bike</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>Back and biceps</t>
+          <t>Spin bike — easy aerobic (optional)</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>45–55 min</t>
+          <t>40 min</t>
         </is>
       </c>
       <c r="H205" s="8" t="n"/>
@@ -10574,48 +10584,46 @@
       <c r="O205" s="13" t="n"/>
       <c r="P205" s="7" t="inlineStr">
         <is>
-          <t>Upper day, and the last pulling session of the block. It sits on Saturday because every weekday this week already carries a swim, and pulling is the one strength session that leaves the legs completely alone the day before an 8 km long run. If the gym closes early, cut to two sets of everything and still do the pull-ups.</t>
+          <t>Optional. Skip it without guilt if the legs feel the long run coming tomorrow.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C206" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E206" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>Long run — 8 km</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>50–55 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="H206" s="8" t="n"/>
-      <c r="I206" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="I206" s="9" t="n"/>
       <c r="J206" s="10" t="n"/>
       <c r="K206" s="11" t="n"/>
       <c r="L206" s="12" t="n"/>
@@ -10624,46 +10632,48 @@
       <c r="O206" s="13" t="n"/>
       <c r="P206" s="7" t="inlineStr">
         <is>
-          <t>Indoor track if the footing is bad, outside if it is clear and you are dressed for it.</t>
+          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E207" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
+      <c r="E207" s="15" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>Spin bike — easy Z2</t>
+          <t>Long run — 8 km</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>55–62 min</t>
         </is>
       </c>
       <c r="H207" s="8" t="n"/>
-      <c r="I207" s="9" t="n"/>
+      <c r="I207" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="J207" s="10" t="n"/>
       <c r="K207" s="11" t="n"/>
       <c r="L207" s="12" t="n"/>
@@ -10672,45 +10682,47 @@
       <c r="O207" s="13" t="n"/>
       <c r="P207" s="7" t="inlineStr">
         <is>
-          <t>Easy spin after the long run, same day on purpose: thirty minutes of light pedalling flushes the calves better than sitting still, and it keeps the hard days hard and the easy days easy. Keep it genuinely easy — if it feels like work, stop.</t>
+          <t>Last run of the block, and the last run of the year. Easy effort, soft surface, orthotics in. Fifteen weeks ago 5 km was your entire week.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C208" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>swim</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Mobility + lower-leg prehab</t>
+          <t>Swim — long aerobic 2,000</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="H208" s="8" t="n"/>
+          <t>2,600 yd · 58–76 min</t>
+        </is>
+      </c>
+      <c r="H208" s="8" t="n">
+        <v>2600</v>
+      </c>
       <c r="I208" s="9" t="n"/>
       <c r="J208" s="10" t="n"/>
       <c r="K208" s="11" t="n"/>
@@ -10720,19 +10732,19 @@
       <c r="O208" s="13" t="n"/>
       <c r="P208" s="7" t="inlineStr">
         <is>
-          <t>Mobility plus foot intrinsics.</t>
+          <t>Warm-up 300. Main: 2,000 continuous at the new aerobic pace. Cool-down 300. Fifteen weeks ago a 1,000 was the long swim. Finish the year with double it.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C209" s="5" t="n">
@@ -10743,24 +10755,22 @@
           <t>winterbase</t>
         </is>
       </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>mobility</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>Swim — FINAL CSS TEST (400 + 200 TT)</t>
+          <t>Mobility + lower-leg prehab</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>1,600 yd · 36–47 min</t>
-        </is>
-      </c>
-      <c r="H209" s="8" t="n">
-        <v>1600</v>
-      </c>
+          <t>25 min</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="n"/>
       <c r="I209" s="9" t="n"/>
       <c r="J209" s="10" t="n"/>
       <c r="K209" s="11" t="n"/>
@@ -10770,516 +10780,26 @@
       <c r="O209" s="13" t="n"/>
       <c r="P209" s="7" t="inlineStr">
         <is>
-          <t>Same protocol as Weeks 1 and 8. Warm-up 400, build 4 × 50, 400 all-out, 5 min rest, 200 all-out, cool-down 400. This is the block's headline number. Compare all three tests side by side — Week 1, Week 8, and today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-28</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E210" s="14" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>Strength A — RDL + posterior chain</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr">
-        <is>
-          <t>45–55 min</t>
-        </is>
-      </c>
-      <c r="H210" s="8" t="n"/>
-      <c r="I210" s="9" t="n"/>
-      <c r="J210" s="10" t="n"/>
-      <c r="K210" s="11" t="n"/>
-      <c r="L210" s="12" t="n"/>
-      <c r="M210" s="10" t="n"/>
-      <c r="N210" s="10" t="n"/>
-      <c r="O210" s="13" t="n"/>
-      <c r="P210" s="7" t="inlineStr">
-        <is>
-          <t>Last Strength A of the year. Log the RDL and split squat loads next to the Week 1 numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C211" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D211" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E211" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>Easy run — 5 km</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr">
-        <is>
-          <t>35–40 min</t>
-        </is>
-      </c>
-      <c r="H211" s="8" t="n"/>
-      <c r="I211" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J211" s="10" t="n"/>
-      <c r="K211" s="11" t="n"/>
-      <c r="L211" s="12" t="n"/>
-      <c r="M211" s="10" t="n"/>
-      <c r="N211" s="10" t="n"/>
-      <c r="O211" s="13" t="n"/>
-      <c r="P211" s="7" t="inlineStr">
-        <is>
-          <t>Easy. Indoor track if needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr">
-        <is>
-          <t>Technique swim (short)</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>1,400 yd · 31–41 min</t>
-        </is>
-      </c>
-      <c r="H212" s="8" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I212" s="9" t="n"/>
-      <c r="J212" s="10" t="n"/>
-      <c r="K212" s="11" t="n"/>
-      <c r="L212" s="12" t="n"/>
-      <c r="M212" s="10" t="n"/>
-      <c r="N212" s="10" t="n"/>
-      <c r="O212" s="13" t="n"/>
-      <c r="P212" s="7" t="inlineStr">
-        <is>
-          <t>About 1,400 yd total, all easy. No clock, no main set. Snorkel and fins for the first half — catch-up, fingertip drag and front scull, rotating through them — then easy 50s holding the feel. This session exists to raise frequency and keep the stroke fresh — leave the pool fresher than you arrived.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C213" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E213" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
-        </is>
-      </c>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>Mobility + lower-leg prehab</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H213" s="8" t="n"/>
-      <c r="I213" s="9" t="n"/>
-      <c r="J213" s="10" t="n"/>
-      <c r="K213" s="11" t="n"/>
-      <c r="L213" s="12" t="n"/>
-      <c r="M213" s="10" t="n"/>
-      <c r="N213" s="10" t="n"/>
-      <c r="O213" s="13" t="n"/>
-      <c r="P213" s="7" t="inlineStr">
-        <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C214" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E214" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
-        </is>
-      </c>
-      <c r="F214" s="7" t="inlineStr">
-        <is>
-          <t>Swim — speed</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>2,000 yd · 44–59 min</t>
-        </is>
-      </c>
-      <c r="H214" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I214" s="9" t="n"/>
-      <c r="J214" s="10" t="n"/>
-      <c r="K214" s="11" t="n"/>
-      <c r="L214" s="12" t="n"/>
-      <c r="M214" s="10" t="n"/>
-      <c r="N214" s="10" t="n"/>
-      <c r="O214" s="13" t="n"/>
-      <c r="P214" s="7" t="inlineStr">
-        <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Main: 20 × 50 on 1:05 alternating. Then 200 breaststroke continuous. Cool-down 300.</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C215" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E215" s="16" t="inlineStr">
-        <is>
-          <t>bike</t>
-        </is>
-      </c>
-      <c r="F215" s="7" t="inlineStr">
-        <is>
-          <t>Spin bike — easy aerobic (optional)</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t>40 min</t>
-        </is>
-      </c>
-      <c r="H215" s="8" t="n"/>
-      <c r="I215" s="9" t="n"/>
-      <c r="J215" s="10" t="n"/>
-      <c r="K215" s="11" t="n"/>
-      <c r="L215" s="12" t="n"/>
-      <c r="M215" s="10" t="n"/>
-      <c r="N215" s="10" t="n"/>
-      <c r="O215" s="13" t="n"/>
-      <c r="P215" s="7" t="inlineStr">
-        <is>
-          <t>Optional. Skip it without guilt if the legs feel the long run coming tomorrow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C216" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E216" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
-        </is>
-      </c>
-      <c r="F216" s="7" t="inlineStr">
-        <is>
-          <t>Mobility + lower-leg prehab</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="H216" s="8" t="n"/>
-      <c r="I216" s="9" t="n"/>
-      <c r="J216" s="10" t="n"/>
-      <c r="K216" s="11" t="n"/>
-      <c r="L216" s="12" t="n"/>
-      <c r="M216" s="10" t="n"/>
-      <c r="N216" s="10" t="n"/>
-      <c r="O216" s="13" t="n"/>
-      <c r="P216" s="7" t="inlineStr">
-        <is>
-          <t>Ankle dorsiflexion (knee-to-wall), calf and soleus stretch, hip flexors, thoracic rotation, and 3 × 20 tibialis raises. Ten minutes of this beats an hour once a month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C217" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E217" s="15" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="F217" s="7" t="inlineStr">
-        <is>
-          <t>Long run — 8 km</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr">
-        <is>
-          <t>55–62 min</t>
-        </is>
-      </c>
-      <c r="H217" s="8" t="n"/>
-      <c r="I217" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J217" s="10" t="n"/>
-      <c r="K217" s="11" t="n"/>
-      <c r="L217" s="12" t="n"/>
-      <c r="M217" s="10" t="n"/>
-      <c r="N217" s="10" t="n"/>
-      <c r="O217" s="13" t="n"/>
-      <c r="P217" s="7" t="inlineStr">
-        <is>
-          <t>Last run of the block, and the last run of the year. Easy effort, soft surface, orthotics in. Fifteen weeks ago 5 km was your entire week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B218" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C218" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D218" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E218" s="6" t="inlineStr">
-        <is>
-          <t>swim</t>
-        </is>
-      </c>
-      <c r="F218" s="7" t="inlineStr">
-        <is>
-          <t>Swim — long aerobic 2,000</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr">
-        <is>
-          <t>2,600 yd · 58–76 min</t>
-        </is>
-      </c>
-      <c r="H218" s="8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="I218" s="9" t="n"/>
-      <c r="J218" s="10" t="n"/>
-      <c r="K218" s="11" t="n"/>
-      <c r="L218" s="12" t="n"/>
-      <c r="M218" s="10" t="n"/>
-      <c r="N218" s="10" t="n"/>
-      <c r="O218" s="13" t="n"/>
-      <c r="P218" s="7" t="inlineStr">
-        <is>
-          <t>Warm-up 300. Main: 2,000 continuous at the new aerobic pace. Cool-down 300. Fifteen weeks ago a 1,000 was the long swim. Finish the year with double it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B219" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C219" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D219" s="5" t="inlineStr">
-        <is>
-          <t>winterbase</t>
-        </is>
-      </c>
-      <c r="E219" s="5" t="inlineStr">
-        <is>
-          <t>mobility</t>
-        </is>
-      </c>
-      <c r="F219" s="7" t="inlineStr">
-        <is>
-          <t>Mobility + lower-leg prehab</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>25 min</t>
-        </is>
-      </c>
-      <c r="H219" s="8" t="n"/>
-      <c r="I219" s="9" t="n"/>
-      <c r="J219" s="10" t="n"/>
-      <c r="K219" s="11" t="n"/>
-      <c r="L219" s="12" t="n"/>
-      <c r="M219" s="10" t="n"/>
-      <c r="N219" s="10" t="n"/>
-      <c r="O219" s="13" t="n"/>
-      <c r="P219" s="7" t="inlineStr">
-        <is>
           <t>Final mobility session of the block. Then sit down and plan the January Victoria 70.3 build — including whether Rainier and Victoria can actually coexist.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P219"/>
+  <autoFilter ref="A4:P209"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:P219">
+  <conditionalFormatting sqref="A5:P209">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="Y"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N,skipped,moved"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="N5:N209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -11679,7 +11199,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>New York — swims front-loaded</t>
+          <t>New York — city week</t>
         </is>
       </c>
       <c r="D10" s="17">
@@ -14343,7 +13863,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>New York. Low other load makes this a good run week.</t>
+          <t>New York all week. Two swims, no bike — running carries the week, long run Saturday.</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14043,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Run-only taper. Swim, bike, and strength continue exactly as normal.</t>
+          <t>Run-only taper. Swim and bike continue as normal; strength drops to Monday's full-body session only.</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14208,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Soleus is the shin-splint muscle: bent-knee calf raises matter more than straight-leg ones. Both are in every strength session.</t>
+          <t>Soleus is the shin-splint muscle: bent-knee calf raises matter more than straight-leg ones. Full body A carries the straight-leg standing raise, Full body B the bent-knee seated raise at the bigger dose.</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -14794,14 +14314,14 @@
     <row r="4">
       <c r="A4" s="28" t="inlineStr">
         <is>
-          <t>Strength A — RDL + posterior chain</t>
+          <t>Full body A — hinge + pull</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Hamstrings, glutes, gastrocnemius, anti-rotation core.</t>
+          <t>Hamstrings, glutes, gastrocnemius, lats, rear shoulder.</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14410,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Barbell Romanian deadlift — 4 × 6–8, 3 s eccentric</t>
+          <t>Warm-up · banded lateral walk 2 × 15 per side, then two ramp-up sets of the first lift</t>
         </is>
       </c>
       <c r="B7" s="44" t="n"/>
@@ -14912,7 +14432,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Smith Bulgarian split squat — 3 × 8 per leg</t>
+          <t>A1 · Barbell Romanian deadlift — 4 × 6–8, 3 s eccentric</t>
         </is>
       </c>
       <c r="B8" s="44" t="n"/>
@@ -14934,7 +14454,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Hamstring curl — 3 × 12</t>
+          <t>A2 · Weighted pull-up or lat pulldown — 4 × 6–8</t>
         </is>
       </c>
       <c r="B9" s="44" t="n"/>
@@ -14956,7 +14476,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Standing calf raise (straight leg) — 4 × 12, 3 s down</t>
+          <t>B1 · Smith Bulgarian split squat — 3 × 8 per leg</t>
         </is>
       </c>
       <c r="B10" s="44" t="n"/>
@@ -14978,7 +14498,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Tibialis raise — 3 × 20</t>
+          <t>B2 · Straight-arm pulldown — 3 × 12</t>
         </is>
       </c>
       <c r="B11" s="44" t="n"/>
@@ -15000,7 +14520,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Pallof press — 3 × 12 per side</t>
+          <t>C · Standing calf raise (straight leg) — 3 × 12, 3 s down</t>
         </is>
       </c>
       <c r="B12" s="44" t="n"/>
@@ -15022,7 +14542,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Dead bug — 3 × 10 per side</t>
+          <t>C · Tibialis raise — 3 × 20</t>
         </is>
       </c>
       <c r="B13" s="44" t="n"/>
@@ -15041,150 +14561,150 @@
       <c r="O13" s="44" t="n"/>
       <c r="P13" s="44" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Strength B — Bulgarian split squat + hips and core</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Quads, single-leg stability, hip abductors, soleus.</t>
-        </is>
-      </c>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C · Pallof press — 3 × 12 per side</t>
+        </is>
+      </c>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
+      <c r="I14" s="44" t="n"/>
+      <c r="J14" s="44" t="n"/>
+      <c r="K14" s="44" t="n"/>
+      <c r="L14" s="44" t="n"/>
+      <c r="M14" s="44" t="n"/>
+      <c r="N14" s="44" t="n"/>
+      <c r="O14" s="44" t="n"/>
+      <c r="P14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>C · Face pull — 3 × 15</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+      <c r="H15" s="44" t="n"/>
+      <c r="I15" s="44" t="n"/>
+      <c r="J15" s="44" t="n"/>
+      <c r="K15" s="44" t="n"/>
+      <c r="L15" s="44" t="n"/>
+      <c r="M15" s="44" t="n"/>
+      <c r="N15" s="44" t="n"/>
+      <c r="O15" s="44" t="n"/>
+      <c r="P15" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Full body B — single-leg + press</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Quads, single-leg stability, soleus, adductors, chest, rotator cuff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Exercise</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Goblet or back squat — 4 × 8</t>
-        </is>
-      </c>
-      <c r="B19" s="44" t="n"/>
-      <c r="C19" s="44" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="44" t="n"/>
-      <c r="H19" s="44" t="n"/>
-      <c r="I19" s="44" t="n"/>
-      <c r="J19" s="44" t="n"/>
-      <c r="K19" s="44" t="n"/>
-      <c r="L19" s="44" t="n"/>
-      <c r="M19" s="44" t="n"/>
-      <c r="N19" s="44" t="n"/>
-      <c r="O19" s="44" t="n"/>
-      <c r="P19" s="44" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Smith Bulgarian split squat — 4 × 8 per leg, heavier than the hamstring day</t>
-        </is>
-      </c>
-      <c r="B20" s="44" t="n"/>
-      <c r="C20" s="44" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="44" t="n"/>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="44" t="n"/>
-      <c r="I20" s="44" t="n"/>
-      <c r="J20" s="44" t="n"/>
-      <c r="K20" s="44" t="n"/>
-      <c r="L20" s="44" t="n"/>
-      <c r="M20" s="44" t="n"/>
-      <c r="N20" s="44" t="n"/>
-      <c r="O20" s="44" t="n"/>
-      <c r="P20" s="44" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Box step-up (18 in) — 3 × 10 per leg</t>
+          <t>Warm-up · banded lateral walk 2 × 15 per side, then two ramp-up sets of the first lift</t>
         </is>
       </c>
       <c r="B21" s="44" t="n"/>
@@ -15206,7 +14726,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Seated calf raise (bent knee / soleus) — 4 × 15</t>
+          <t>A1 · Smith Bulgarian split squat — 4 × 8 per leg, heavier than Full body A</t>
         </is>
       </c>
       <c r="B22" s="44" t="n"/>
@@ -15228,7 +14748,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Copenhagen plank — 3 × 20–30 s per side</t>
+          <t>A2 · Dumbbell bench press — 4 × 8</t>
         </is>
       </c>
       <c r="B23" s="44" t="n"/>
@@ -15250,7 +14770,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Banded lateral walk — 3 × 15 per side</t>
+          <t>B1 · Box step-up (18 in) — 3 × 10 per leg</t>
         </is>
       </c>
       <c r="B24" s="44" t="n"/>
@@ -15272,7 +14792,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Side plank with hip abduction — 3 × 10 per side</t>
+          <t>B2 · Chest-supported row — 3 × 10</t>
         </is>
       </c>
       <c r="B25" s="44" t="n"/>
@@ -15291,194 +14811,194 @@
       <c r="O25" s="44" t="n"/>
       <c r="P25" s="44" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>C · Seated calf raise (bent knee / soleus) — 4 × 15</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="44" t="n"/>
+      <c r="H26" s="44" t="n"/>
+      <c r="I26" s="44" t="n"/>
+      <c r="J26" s="44" t="n"/>
+      <c r="K26" s="44" t="n"/>
+      <c r="L26" s="44" t="n"/>
+      <c r="M26" s="44" t="n"/>
+      <c r="N26" s="44" t="n"/>
+      <c r="O26" s="44" t="n"/>
+      <c r="P26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>C · Tibialis raise — 3 × 20</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="44" t="n"/>
+      <c r="H27" s="44" t="n"/>
+      <c r="I27" s="44" t="n"/>
+      <c r="J27" s="44" t="n"/>
+      <c r="K27" s="44" t="n"/>
+      <c r="L27" s="44" t="n"/>
+      <c r="M27" s="44" t="n"/>
+      <c r="N27" s="44" t="n"/>
+      <c r="O27" s="44" t="n"/>
+      <c r="P27" s="44" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Back and biceps</t>
-        </is>
-      </c>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>C · Copenhagen plank — 3 × 20–30 s per side</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
+      <c r="G28" s="44" t="n"/>
+      <c r="H28" s="44" t="n"/>
+      <c r="I28" s="44" t="n"/>
+      <c r="J28" s="44" t="n"/>
+      <c r="K28" s="44" t="n"/>
+      <c r="L28" s="44" t="n"/>
+      <c r="M28" s="44" t="n"/>
+      <c r="N28" s="44" t="n"/>
+      <c r="O28" s="44" t="n"/>
+      <c r="P28" s="44" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Lats, mid-back, biceps, grip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>C · Cable or band external rotation — 3 × 15 per side</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+      <c r="F29" s="44" t="n"/>
+      <c r="G29" s="44" t="n"/>
+      <c r="H29" s="44" t="n"/>
+      <c r="I29" s="44" t="n"/>
+      <c r="J29" s="44" t="n"/>
+      <c r="K29" s="44" t="n"/>
+      <c r="L29" s="44" t="n"/>
+      <c r="M29" s="44" t="n"/>
+      <c r="N29" s="44" t="n"/>
+      <c r="O29" s="44" t="n"/>
+      <c r="P29" s="44" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Bands + bodyweight circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Full body with no barbell and no machines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Exercise</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="O34" s="3" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="P30" s="3" t="inlineStr">
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Weighted pull-up or lat pulldown — 4 × 6–8</t>
-        </is>
-      </c>
-      <c r="B31" s="44" t="n"/>
-      <c r="C31" s="44" t="n"/>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="44" t="n"/>
-      <c r="F31" s="44" t="n"/>
-      <c r="G31" s="44" t="n"/>
-      <c r="H31" s="44" t="n"/>
-      <c r="I31" s="44" t="n"/>
-      <c r="J31" s="44" t="n"/>
-      <c r="K31" s="44" t="n"/>
-      <c r="L31" s="44" t="n"/>
-      <c r="M31" s="44" t="n"/>
-      <c r="N31" s="44" t="n"/>
-      <c r="O31" s="44" t="n"/>
-      <c r="P31" s="44" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Chest-supported row — 3 × 10</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="n"/>
-      <c r="C32" s="44" t="n"/>
-      <c r="D32" s="44" t="n"/>
-      <c r="E32" s="44" t="n"/>
-      <c r="F32" s="44" t="n"/>
-      <c r="G32" s="44" t="n"/>
-      <c r="H32" s="44" t="n"/>
-      <c r="I32" s="44" t="n"/>
-      <c r="J32" s="44" t="n"/>
-      <c r="K32" s="44" t="n"/>
-      <c r="L32" s="44" t="n"/>
-      <c r="M32" s="44" t="n"/>
-      <c r="N32" s="44" t="n"/>
-      <c r="O32" s="44" t="n"/>
-      <c r="P32" s="44" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Straight-arm pulldown — 3 × 12</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="n"/>
-      <c r="C33" s="44" t="n"/>
-      <c r="D33" s="44" t="n"/>
-      <c r="E33" s="44" t="n"/>
-      <c r="F33" s="44" t="n"/>
-      <c r="G33" s="44" t="n"/>
-      <c r="H33" s="44" t="n"/>
-      <c r="I33" s="44" t="n"/>
-      <c r="J33" s="44" t="n"/>
-      <c r="K33" s="44" t="n"/>
-      <c r="L33" s="44" t="n"/>
-      <c r="M33" s="44" t="n"/>
-      <c r="N33" s="44" t="n"/>
-      <c r="O33" s="44" t="n"/>
-      <c r="P33" s="44" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Face pull — 3 × 15</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="n"/>
-      <c r="C34" s="44" t="n"/>
-      <c r="D34" s="44" t="n"/>
-      <c r="E34" s="44" t="n"/>
-      <c r="F34" s="44" t="n"/>
-      <c r="G34" s="44" t="n"/>
-      <c r="H34" s="44" t="n"/>
-      <c r="I34" s="44" t="n"/>
-      <c r="J34" s="44" t="n"/>
-      <c r="K34" s="44" t="n"/>
-      <c r="L34" s="44" t="n"/>
-      <c r="M34" s="44" t="n"/>
-      <c r="N34" s="44" t="n"/>
-      <c r="O34" s="44" t="n"/>
-      <c r="P34" s="44" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Dumbbell curl — 3 × 10</t>
+          <t>Banded Romanian deadlift — 3 × 15</t>
         </is>
       </c>
       <c r="B35" s="44" t="n"/>
@@ -15500,7 +15020,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Hanging knee raise — 3 × 12</t>
+          <t>Split squat — 3 × 12 per leg</t>
         </is>
       </c>
       <c r="B36" s="44" t="n"/>
@@ -15519,483 +15039,115 @@
       <c r="O36" s="44" t="n"/>
       <c r="P36" s="44" t="n"/>
     </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Single-leg calf raise — 3 × 15 per leg</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="n"/>
+      <c r="C37" s="44" t="n"/>
+      <c r="D37" s="44" t="n"/>
+      <c r="E37" s="44" t="n"/>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="44" t="n"/>
+      <c r="H37" s="44" t="n"/>
+      <c r="I37" s="44" t="n"/>
+      <c r="J37" s="44" t="n"/>
+      <c r="K37" s="44" t="n"/>
+      <c r="L37" s="44" t="n"/>
+      <c r="M37" s="44" t="n"/>
+      <c r="N37" s="44" t="n"/>
+      <c r="O37" s="44" t="n"/>
+      <c r="P37" s="44" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Tibialis raise — 3 × 20</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="n"/>
+      <c r="C38" s="44" t="n"/>
+      <c r="D38" s="44" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="44" t="n"/>
+      <c r="H38" s="44" t="n"/>
+      <c r="I38" s="44" t="n"/>
+      <c r="J38" s="44" t="n"/>
+      <c r="K38" s="44" t="n"/>
+      <c r="L38" s="44" t="n"/>
+      <c r="M38" s="44" t="n"/>
+      <c r="N38" s="44" t="n"/>
+      <c r="O38" s="44" t="n"/>
+      <c r="P38" s="44" t="n"/>
+    </row>
     <row r="39">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>Chest and shoulders</t>
-        </is>
-      </c>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Band row — 3 × 15</t>
+        </is>
+      </c>
+      <c r="B39" s="44" t="n"/>
+      <c r="C39" s="44" t="n"/>
+      <c r="D39" s="44" t="n"/>
+      <c r="E39" s="44" t="n"/>
+      <c r="F39" s="44" t="n"/>
+      <c r="G39" s="44" t="n"/>
+      <c r="H39" s="44" t="n"/>
+      <c r="I39" s="44" t="n"/>
+      <c r="J39" s="44" t="n"/>
+      <c r="K39" s="44" t="n"/>
+      <c r="L39" s="44" t="n"/>
+      <c r="M39" s="44" t="n"/>
+      <c r="N39" s="44" t="n"/>
+      <c r="O39" s="44" t="n"/>
+      <c r="P39" s="44" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Chest, delts, rotator cuff, anti-extension core.</t>
-        </is>
-      </c>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Push-up — 3 × 12</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="n"/>
+      <c r="C40" s="44" t="n"/>
+      <c r="D40" s="44" t="n"/>
+      <c r="E40" s="44" t="n"/>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="44" t="n"/>
+      <c r="H40" s="44" t="n"/>
+      <c r="I40" s="44" t="n"/>
+      <c r="J40" s="44" t="n"/>
+      <c r="K40" s="44" t="n"/>
+      <c r="L40" s="44" t="n"/>
+      <c r="M40" s="44" t="n"/>
+      <c r="N40" s="44" t="n"/>
+      <c r="O40" s="44" t="n"/>
+      <c r="P40" s="44" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Exercise</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Barbell or dumbbell bench press — 4 × 8</t>
-        </is>
-      </c>
-      <c r="B42" s="44" t="n"/>
-      <c r="C42" s="44" t="n"/>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="44" t="n"/>
-      <c r="F42" s="44" t="n"/>
-      <c r="G42" s="44" t="n"/>
-      <c r="H42" s="44" t="n"/>
-      <c r="I42" s="44" t="n"/>
-      <c r="J42" s="44" t="n"/>
-      <c r="K42" s="44" t="n"/>
-      <c r="L42" s="44" t="n"/>
-      <c r="M42" s="44" t="n"/>
-      <c r="N42" s="44" t="n"/>
-      <c r="O42" s="44" t="n"/>
-      <c r="P42" s="44" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Incline dumbbell press — 3 × 10</t>
-        </is>
-      </c>
-      <c r="B43" s="44" t="n"/>
-      <c r="C43" s="44" t="n"/>
-      <c r="D43" s="44" t="n"/>
-      <c r="E43" s="44" t="n"/>
-      <c r="F43" s="44" t="n"/>
-      <c r="G43" s="44" t="n"/>
-      <c r="H43" s="44" t="n"/>
-      <c r="I43" s="44" t="n"/>
-      <c r="J43" s="44" t="n"/>
-      <c r="K43" s="44" t="n"/>
-      <c r="L43" s="44" t="n"/>
-      <c r="M43" s="44" t="n"/>
-      <c r="N43" s="44" t="n"/>
-      <c r="O43" s="44" t="n"/>
-      <c r="P43" s="44" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Overhead press — 3 × 8</t>
-        </is>
-      </c>
-      <c r="B44" s="44" t="n"/>
-      <c r="C44" s="44" t="n"/>
-      <c r="D44" s="44" t="n"/>
-      <c r="E44" s="44" t="n"/>
-      <c r="F44" s="44" t="n"/>
-      <c r="G44" s="44" t="n"/>
-      <c r="H44" s="44" t="n"/>
-      <c r="I44" s="44" t="n"/>
-      <c r="J44" s="44" t="n"/>
-      <c r="K44" s="44" t="n"/>
-      <c r="L44" s="44" t="n"/>
-      <c r="M44" s="44" t="n"/>
-      <c r="N44" s="44" t="n"/>
-      <c r="O44" s="44" t="n"/>
-      <c r="P44" s="44" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Dumbbell lateral raise — 3 × 12</t>
-        </is>
-      </c>
-      <c r="B45" s="44" t="n"/>
-      <c r="C45" s="44" t="n"/>
-      <c r="D45" s="44" t="n"/>
-      <c r="E45" s="44" t="n"/>
-      <c r="F45" s="44" t="n"/>
-      <c r="G45" s="44" t="n"/>
-      <c r="H45" s="44" t="n"/>
-      <c r="I45" s="44" t="n"/>
-      <c r="J45" s="44" t="n"/>
-      <c r="K45" s="44" t="n"/>
-      <c r="L45" s="44" t="n"/>
-      <c r="M45" s="44" t="n"/>
-      <c r="N45" s="44" t="n"/>
-      <c r="O45" s="44" t="n"/>
-      <c r="P45" s="44" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Cable or band external rotation — 3 × 15 per side</t>
-        </is>
-      </c>
-      <c r="B46" s="44" t="n"/>
-      <c r="C46" s="44" t="n"/>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="44" t="n"/>
-      <c r="F46" s="44" t="n"/>
-      <c r="G46" s="44" t="n"/>
-      <c r="H46" s="44" t="n"/>
-      <c r="I46" s="44" t="n"/>
-      <c r="J46" s="44" t="n"/>
-      <c r="K46" s="44" t="n"/>
-      <c r="L46" s="44" t="n"/>
-      <c r="M46" s="44" t="n"/>
-      <c r="N46" s="44" t="n"/>
-      <c r="O46" s="44" t="n"/>
-      <c r="P46" s="44" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Ab wheel or plank walkout — 3 × 8</t>
-        </is>
-      </c>
-      <c r="B47" s="44" t="n"/>
-      <c r="C47" s="44" t="n"/>
-      <c r="D47" s="44" t="n"/>
-      <c r="E47" s="44" t="n"/>
-      <c r="F47" s="44" t="n"/>
-      <c r="G47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
-      <c r="I47" s="44" t="n"/>
-      <c r="J47" s="44" t="n"/>
-      <c r="K47" s="44" t="n"/>
-      <c r="L47" s="44" t="n"/>
-      <c r="M47" s="44" t="n"/>
-      <c r="N47" s="44" t="n"/>
-      <c r="O47" s="44" t="n"/>
-      <c r="P47" s="44" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>Bands + bodyweight circuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Full body with no barbell and no machines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Exercise</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Banded Romanian deadlift — 3 × 15</t>
-        </is>
-      </c>
-      <c r="B53" s="44" t="n"/>
-      <c r="C53" s="44" t="n"/>
-      <c r="D53" s="44" t="n"/>
-      <c r="E53" s="44" t="n"/>
-      <c r="F53" s="44" t="n"/>
-      <c r="G53" s="44" t="n"/>
-      <c r="H53" s="44" t="n"/>
-      <c r="I53" s="44" t="n"/>
-      <c r="J53" s="44" t="n"/>
-      <c r="K53" s="44" t="n"/>
-      <c r="L53" s="44" t="n"/>
-      <c r="M53" s="44" t="n"/>
-      <c r="N53" s="44" t="n"/>
-      <c r="O53" s="44" t="n"/>
-      <c r="P53" s="44" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Split squat — 3 × 12 per leg</t>
-        </is>
-      </c>
-      <c r="B54" s="44" t="n"/>
-      <c r="C54" s="44" t="n"/>
-      <c r="D54" s="44" t="n"/>
-      <c r="E54" s="44" t="n"/>
-      <c r="F54" s="44" t="n"/>
-      <c r="G54" s="44" t="n"/>
-      <c r="H54" s="44" t="n"/>
-      <c r="I54" s="44" t="n"/>
-      <c r="J54" s="44" t="n"/>
-      <c r="K54" s="44" t="n"/>
-      <c r="L54" s="44" t="n"/>
-      <c r="M54" s="44" t="n"/>
-      <c r="N54" s="44" t="n"/>
-      <c r="O54" s="44" t="n"/>
-      <c r="P54" s="44" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Single-leg calf raise — 3 × 15 per leg</t>
-        </is>
-      </c>
-      <c r="B55" s="44" t="n"/>
-      <c r="C55" s="44" t="n"/>
-      <c r="D55" s="44" t="n"/>
-      <c r="E55" s="44" t="n"/>
-      <c r="F55" s="44" t="n"/>
-      <c r="G55" s="44" t="n"/>
-      <c r="H55" s="44" t="n"/>
-      <c r="I55" s="44" t="n"/>
-      <c r="J55" s="44" t="n"/>
-      <c r="K55" s="44" t="n"/>
-      <c r="L55" s="44" t="n"/>
-      <c r="M55" s="44" t="n"/>
-      <c r="N55" s="44" t="n"/>
-      <c r="O55" s="44" t="n"/>
-      <c r="P55" s="44" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Tibialis raise — 3 × 20</t>
-        </is>
-      </c>
-      <c r="B56" s="44" t="n"/>
-      <c r="C56" s="44" t="n"/>
-      <c r="D56" s="44" t="n"/>
-      <c r="E56" s="44" t="n"/>
-      <c r="F56" s="44" t="n"/>
-      <c r="G56" s="44" t="n"/>
-      <c r="H56" s="44" t="n"/>
-      <c r="I56" s="44" t="n"/>
-      <c r="J56" s="44" t="n"/>
-      <c r="K56" s="44" t="n"/>
-      <c r="L56" s="44" t="n"/>
-      <c r="M56" s="44" t="n"/>
-      <c r="N56" s="44" t="n"/>
-      <c r="O56" s="44" t="n"/>
-      <c r="P56" s="44" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Band row — 3 × 15</t>
-        </is>
-      </c>
-      <c r="B57" s="44" t="n"/>
-      <c r="C57" s="44" t="n"/>
-      <c r="D57" s="44" t="n"/>
-      <c r="E57" s="44" t="n"/>
-      <c r="F57" s="44" t="n"/>
-      <c r="G57" s="44" t="n"/>
-      <c r="H57" s="44" t="n"/>
-      <c r="I57" s="44" t="n"/>
-      <c r="J57" s="44" t="n"/>
-      <c r="K57" s="44" t="n"/>
-      <c r="L57" s="44" t="n"/>
-      <c r="M57" s="44" t="n"/>
-      <c r="N57" s="44" t="n"/>
-      <c r="O57" s="44" t="n"/>
-      <c r="P57" s="44" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Push-up — 3 × 12</t>
-        </is>
-      </c>
-      <c r="B58" s="44" t="n"/>
-      <c r="C58" s="44" t="n"/>
-      <c r="D58" s="44" t="n"/>
-      <c r="E58" s="44" t="n"/>
-      <c r="F58" s="44" t="n"/>
-      <c r="G58" s="44" t="n"/>
-      <c r="H58" s="44" t="n"/>
-      <c r="I58" s="44" t="n"/>
-      <c r="J58" s="44" t="n"/>
-      <c r="K58" s="44" t="n"/>
-      <c r="L58" s="44" t="n"/>
-      <c r="M58" s="44" t="n"/>
-      <c r="N58" s="44" t="n"/>
-      <c r="O58" s="44" t="n"/>
-      <c r="P58" s="44" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Side plank with hip abduction — 3 × 10 per side</t>
         </is>
       </c>
-      <c r="B59" s="44" t="n"/>
-      <c r="C59" s="44" t="n"/>
-      <c r="D59" s="44" t="n"/>
-      <c r="E59" s="44" t="n"/>
-      <c r="F59" s="44" t="n"/>
-      <c r="G59" s="44" t="n"/>
-      <c r="H59" s="44" t="n"/>
-      <c r="I59" s="44" t="n"/>
-      <c r="J59" s="44" t="n"/>
-      <c r="K59" s="44" t="n"/>
-      <c r="L59" s="44" t="n"/>
-      <c r="M59" s="44" t="n"/>
-      <c r="N59" s="44" t="n"/>
-      <c r="O59" s="44" t="n"/>
-      <c r="P59" s="44" t="n"/>
+      <c r="B41" s="44" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="44" t="n"/>
+      <c r="E41" s="44" t="n"/>
+      <c r="F41" s="44" t="n"/>
+      <c r="G41" s="44" t="n"/>
+      <c r="H41" s="44" t="n"/>
+      <c r="I41" s="44" t="n"/>
+      <c r="J41" s="44" t="n"/>
+      <c r="K41" s="44" t="n"/>
+      <c r="L41" s="44" t="n"/>
+      <c r="M41" s="44" t="n"/>
+      <c r="N41" s="44" t="n"/>
+      <c r="O41" s="44" t="n"/>
+      <c r="P41" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16090,7 +15242,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Orthotics in: running goes to two, then three sessions a week at roughly +10%/wk. Swim threshold volume climbs. The New York week is absorbed as a run-led travel block with swims front-loaded in Seattle before the flight and back-loaded after the return.</t>
+          <t>Orthotics in: running goes to two, then three sessions a week at roughly +10%/wk. Swim threshold volume climbs. The New York trip (Oct 25 – Nov 3) runs as a travel block: two swims at the Chinatown YMCA hold the 6,000 yd floor, band circuits stand in for the lifts, and swims are back-loaded after the return.</t>
         </is>
       </c>
     </row>

--- a/Abid — Fall 2026 Training Block.xlsx
+++ b/Abid — Fall 2026 Training Block.xlsx
@@ -3808,7 +3808,7 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 24 × 50 + first paddles</t>
+          <t>Swim — speed 20 × 50 + first paddles</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -3828,7 +3828,7 @@
       <c r="O67" s="13" t="n"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: closed-fist / catch-up / 6-1-6 / breaststroke timing. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. PADDLES: 400 pull with small paddles and buoy, easy, holding the catch — stop immediately if the shoulder complains. Main: 24 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: closed-fist / catch-up / 6-1-6 / breaststroke timing. Fins throughout; snorkel off for 6-1-6 and breaststroke timing. Pull 200 with small paddles and buoy, easy, holding the catch — first time on paddles, so 200 is plenty; stop immediately if the shoulder complains. Main: 20 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200.</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 6 × (4 × 50)</t>
+          <t>Swim — speed 5 × (4 × 50)</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -5784,7 +5784,7 @@
       <c r="O107" s="13" t="n"/>
       <c r="P107" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Paddles 400 pull. Main: 6 rounds of 4 × 50 on 1:00, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200. Tighter send-off than Week 5 — this is where density shows up.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: stroke-count ladder / front scull / 6-1-6 / closed-fist. Fins throughout; snorkel off for 6-1-6. Pull 200 with small paddles and buoy, easy, holding the catch. Main: 5 rounds of 4 × 50 on 1:00, 45 s between rounds. Then 4 × 50 breaststroke. Cool-down 200. Tighter send-off than Week 5 — this is where density shows up.</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Swim — speed 30 × 50</t>
+          <t>Swim — speed 24 × 50</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6470,7 +6470,7 @@
       <c r="O121" s="13" t="n"/>
       <c r="P121" s="7" t="inlineStr">
         <is>
-          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Paddles 400. Main: 30 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200. Long 50s set — the goal is that number 30 looks like number 1.</t>
+          <t>Warm-up 300. Drill 400 as 8 × 50, each drill twice: 6-1-6 / closed-fist / sighting / breaststroke timing. Fins throughout; snorkel off for 6-1-6, sighting and breaststroke timing. Pull 300 with small paddles and buoy, easy, holding the catch. Main: 24 × 50 on 1:05, alternating aerobic and fast. Then 4 × 50 breaststroke. Cool-down 200. Long 50s set — the goal is that number 24 looks like number 1.</t>
         </is>
       </c>
     </row>
